--- a/AutosurveillanceTemplates/Q_GRAV.xlsx
+++ b/AutosurveillanceTemplates/Q_GRAV.xlsx
@@ -43,7 +43,7 @@
     <definedName name="Type_equipement">PARAM!$C$4:$C$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Q_GRAV!$B$1:$U$69</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -6952,8 +6952,7 @@
       <c r="C27" s="115"/>
       <c r="D27" s="151"/>
       <c r="E27" s="100" t="str">
-        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D27="","",10),IF(AND(H27="",N27=""),"",10))</f>
-        <v/>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D27="","",IF($D$40=Critères!$AT$3,1,10)),IF(AND(H27="",N27=""),"",IF($D$40=Critères!$AT$3,1,10)))</f>
       </c>
       <c r="F27" s="153"/>
       <c r="G27" s="101" t="str">
@@ -6990,16 +6989,13 @@
       <c r="T27" s="117"/>
       <c r="U27" s="74"/>
       <c r="W27" s="236">
-        <f>IF(AND(I27&lt;&gt;"",I27&lt;&gt;"-"), IF(ABS(I27)&gt;E27,1,0),0)</f>
-        <v>0</v>
+        <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P27),ISNUMBER(E27)),IF(ABS(P27)&gt;E27,1,0),0),IF(AND(ISNUMBER(I27),ISNUMBER(E27)),IF(ABS(I27)&gt;E27,1,0),0))</f>
       </c>
       <c r="X27" s="236">
-        <f>IF(AND(M27&lt;&gt;"",M27&lt;&gt;"-"), IF(ABS(M27)&gt;G27,1,0),0)</f>
-        <v>0</v>
+        <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K27),ISNUMBER(G27)),IF(ABS(K27)&gt;G27,1,0),0))</f>
       </c>
       <c r="Y27" s="236">
-        <f>IF(AND(Q27&lt;&gt;"",Q27&lt;&gt;"-"), IF(ABS(Q27)&gt;G27,1,0),0)</f>
-        <v>0</v>
+        <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q27),ISNUMBER(G27)),IF(ABS(Q27)&gt;G27,1,0),0),0)</f>
       </c>
     </row>
     <row r="28" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7007,8 +7003,7 @@
       <c r="C28" s="115"/>
       <c r="D28" s="151"/>
       <c r="E28" s="100" t="str">
-        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D28="","",10),IF(AND(H28="",N28=""),"",10))</f>
-        <v/>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D28="","",IF($D$40=Critères!$AT$3,1,10)),IF(AND(H28="",N28=""),"",IF($D$40=Critères!$AT$3,1,10)))</f>
       </c>
       <c r="F28" s="153"/>
       <c r="G28" s="101" t="str">
@@ -7045,16 +7040,13 @@
       <c r="T28" s="116"/>
       <c r="U28" s="74"/>
       <c r="W28" s="236">
-        <f t="shared" ref="W28:W30" si="4">IF(AND(I28&lt;&gt;"",I28&lt;&gt;"-"), IF(ABS(I28)&gt;E28,1,0),0)</f>
-        <v>0</v>
+        <f t="shared" ref="W28:W30" si="4">IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P28),ISNUMBER(E28)),IF(ABS(P28)&gt;E28,1,0),0),IF(AND(ISNUMBER(I28),ISNUMBER(E28)),IF(ABS(I28)&gt;E28,1,0),0))</f>
       </c>
       <c r="X28" s="236">
-        <f t="shared" ref="X28:X30" si="5">IF(AND(M28&lt;&gt;"",M28&lt;&gt;"-"), IF(ABS(M28)&gt;G28,1,0),0)</f>
-        <v>0</v>
+        <f t="shared" ref="X28:X30" si="5">IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K28),ISNUMBER(G28)),IF(ABS(K28)&gt;G28,1,0),0))</f>
       </c>
       <c r="Y28" s="236">
-        <f t="shared" ref="Y28:Y30" si="6">IF(AND(Q28&lt;&gt;"",Q28&lt;&gt;"-"), IF(ABS(Q28)&gt;G28,1,0),0)</f>
-        <v>0</v>
+        <f t="shared" ref="Y28:Y30" si="6">IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q28),ISNUMBER(G28)),IF(ABS(Q28)&gt;G28,1,0),0),0)</f>
       </c>
     </row>
     <row r="29" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7062,8 +7054,7 @@
       <c r="C29" s="115"/>
       <c r="D29" s="151"/>
       <c r="E29" s="100" t="str">
-        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D29="","",10),IF(AND(H29="",N29=""),"",10))</f>
-        <v/>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D29="","",IF($D$40=Critères!$AT$3,1,10)),IF(AND(H29="",N29=""),"",IF($D$40=Critères!$AT$3,1,10)))</f>
       </c>
       <c r="F29" s="153"/>
       <c r="G29" s="101" t="str">
@@ -7117,8 +7108,7 @@
       <c r="C30" s="115"/>
       <c r="D30" s="152"/>
       <c r="E30" s="146" t="str">
-        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D30="","",10),IF(AND(H30="",N30=""),"",10))</f>
-        <v/>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D30="","",IF($D$40=Critères!$AT$3,1,10)),IF(AND(H30="",N30=""),"",IF($D$40=Critères!$AT$3,1,10)))</f>
       </c>
       <c r="F30" s="154"/>
       <c r="G30" s="147" t="str">
@@ -7189,16 +7179,13 @@
       <c r="T31" s="116"/>
       <c r="U31" s="74"/>
       <c r="W31" s="236" t="str">
-        <f>IF(SUM(D27:D30)&gt;0,IF(SUM(W27:W30)&gt;0,"Non validé","Validé"),"Non contrôlé")</f>
-        <v>Non contrôlé</v>
+        <f>IF(IF($G$18="Mesure comparative en parallèle",COUNT(P27:P30),COUNT(I27:I30))&gt;0,IF(SUM(W27:W30)&gt;0,"Non validé","Validé"),"Non contrôlé")</f>
       </c>
       <c r="X31" s="236" t="str">
-        <f>IF(SUM(F27:F30)&gt;0,IF(SUM(X27:X30)&gt;0,"Non validé","Validé"),"Non contrôlé")</f>
-        <v>Non contrôlé</v>
+        <f>IF($G$18="Mesure comparative en parallèle","-",IF(SUMPRODUCT(ISNUMBER(K27:K30)*ISNUMBER(G27:G30))&gt;0,IF(SUM(X27:X30)&gt;0,"Non validé","Validé"),"Non contrôlé"))</f>
       </c>
       <c r="Y31" s="236" t="str">
-        <f>IF(SUM(F27:F30)&gt;0,IF(SUM(Y27:Y30)&gt;0,"Non validé","Validé"),"Non contrôlé")</f>
-        <v>Non contrôlé</v>
+        <f>IF($G$18="Mesure comparative en parallèle",IF(SUMPRODUCT(ISNUMBER(Q27:Q30)*ISNUMBER(G27:G30))&gt;0,IF(SUM(Y27:Y30)&gt;0,"Non validé","Validé"),"Non contrôlé"),"-")</f>
       </c>
     </row>
     <row r="32" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7227,8 +7214,7 @@
       <c r="T32" s="116"/>
       <c r="U32" s="74"/>
       <c r="X32" s="236" t="str">
-        <f>IF(Y31="Non validé",Y31,X31)</f>
-        <v>Non contrôlé</v>
+        <f>IF($G$18="Mesure comparative en parallèle",Y31,X31)</f>
       </c>
     </row>
     <row r="33" spans="2:37" s="85" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7809,8 +7795,7 @@
       <c r="N48" s="267"/>
       <c r="O48" s="268"/>
       <c r="P48" s="264" t="str">
-        <f>IF(E48="-","Non applicable",IF(OR(D40=Critères!AX3,D40=Critères!BB3),IF(D40=Critères!AX3,W36,"Non contrôlé"),W31))</f>
-        <v>Non contrôlé</v>
+        <f>IF(E48="-","Non applicable",IF(D40=Critères!BB3,"Non contrôlé",W31))</f>
       </c>
       <c r="Q48" s="265"/>
       <c r="R48" s="93">
@@ -7852,8 +7837,7 @@
       <c r="N49" s="267"/>
       <c r="O49" s="268"/>
       <c r="P49" s="264" t="str">
-        <f>IF(E49="-","Non applicable",IF(OR(D40=Critères!AX3,D40=Critères!BB3),"Non contrôlé",X32))</f>
-        <v>Non contrôlé</v>
+        <f>IF(E49="-","Non applicable",IF(D40=Critères!BB3,"Non contrôlé",X32))</f>
       </c>
       <c r="Q49" s="265"/>
       <c r="R49" s="93">

--- a/AutosurveillanceTemplates/Q_GRAV.xlsx
+++ b/AutosurveillanceTemplates/Q_GRAV.xlsx
@@ -6891,23 +6891,31 @@
     <row r="26" spans="2:25" ht="65.099999999999994" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B26" s="73"/>
       <c r="C26" s="115"/>
-      <c r="D26" s="106" t="s">
-        <v>338</v>
-      </c>
-      <c r="E26" s="107" t="s">
-        <v>251</v>
-      </c>
-      <c r="F26" s="107" t="s">
-        <v>339</v>
+      <c r="D26" s="106" t="str">
+        <f>IF($D$40="Clapet","Angle simulé (°)","Hauteur simulée (mm)")</f>
+        <v>Hauteur simulée (mm)</v>
+      </c>
+      <c r="E26" s="107" t="str">
+        <f>IF($D$40="Clapet","EMT sur l'angle"&amp;CHAR(10)&amp;"(°)","EMT sur la hauteur"&amp;CHAR(10)&amp;"(mm)")</f>
+        <v>EMT sur la hauteur
+(mm)</v>
+      </c>
+      <c r="F26" s="107" t="str">
+        <f>IF($D$40="Clapet","Débit attendu / Angle simulé"&amp;CHAR(10)&amp;"(m3/h)","Débit attendu / Hauteur simulée"&amp;CHAR(10)&amp;"(m3/h)")</f>
+        <v>Débit attendu / Hauteur simulée
+(m3/h)</v>
       </c>
       <c r="G26" s="108" t="s">
         <v>250</v>
       </c>
-      <c r="H26" s="106" t="s">
-        <v>208</v>
-      </c>
-      <c r="I26" s="107" t="s">
-        <v>255</v>
+      <c r="H26" s="106" t="str">
+        <f>IF($D$40="Clapet","Angle lu (°)","Hauteur lue (mm)")</f>
+        <v>Hauteur lue (mm)</v>
+      </c>
+      <c r="I26" s="107" t="str">
+        <f>IF($D$40="Clapet","Écart"&amp;CHAR(10)&amp;"Angle lu (°)","Écart"&amp;CHAR(10)&amp;"Hauteur lue (mm)")</f>
+        <v>Écart
+Hauteur lue (mm)</v>
       </c>
       <c r="J26" s="107" t="s">
         <v>246</v>
@@ -6915,20 +6923,25 @@
       <c r="K26" s="107" t="s">
         <v>256</v>
       </c>
-      <c r="L26" s="107" t="s">
-        <v>247</v>
+      <c r="L26" s="107" t="str">
+        <f>IF($D$40="Clapet","Débit attendu / Angle lu (m3/h)","Débit attendu / Hauteur lue (m3/h)")</f>
+        <v>Débit attendu / Hauteur lue (m3/h)</v>
       </c>
       <c r="M26" s="108" t="s">
         <v>257</v>
       </c>
-      <c r="N26" s="106" t="s">
-        <v>208</v>
+      <c r="N26" s="106" t="str">
+        <f>IF($D$40="Clapet","Angle lu (°)","Hauteur lue (mm)")</f>
+        <v>Hauteur lue (mm)</v>
       </c>
       <c r="O26" s="107" t="s">
         <v>246</v>
       </c>
-      <c r="P26" s="107" t="s">
-        <v>258</v>
+      <c r="P26" s="107" t="str">
+        <f>IF($D$40="Clapet","Écart"&amp;CHAR(10)&amp;"Angle"&amp;CHAR(10)&amp;"(°)","Écart"&amp;CHAR(10)&amp;"Hauteur"&amp;CHAR(10)&amp;"(mm)")</f>
+        <v>Écart
+Hauteur
+(mm)</v>
       </c>
       <c r="Q26" s="108" t="s">
         <v>259</v>
@@ -6952,11 +6965,12 @@
       <c r="C27" s="115"/>
       <c r="D27" s="151"/>
       <c r="E27" s="100" t="str">
-        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D27="","",IF($D$40=Critères!$AT$3,1,10)),IF(AND(H27="",N27=""),"",IF($D$40=Critères!$AT$3,1,10)))</f>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D27="","",IF($D$40="Clapet",1,10)),IF(AND(H27="",N27=""),"",IF($D$40="Clapet",1,10)))</f>
+        <v/>
       </c>
       <c r="F27" s="153"/>
       <c r="G27" s="101" t="str">
-        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D27="","",IF(D27&lt;50,"-",IF(D27&lt;150,0.1,0.05))),IF(AND(H27="",N27=""),"",IF(AVERAGE(H27,N27)&lt;50,"-",IF(AVERAGE(H27,N27)&lt;150,0.1,0.05))))</f>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D27="","",IF($D$40="Clapet",0.1,IF(D27&lt;50,"-",IF(D27&lt;150,0.1,0.05)))),IF(AND(H27="",N27=""),"",IF($D$40="Clapet",0.1,IF(AVERAGE(H27,N27)&lt;50,"-",IF(AVERAGE(H27,N27)&lt;150,0.1,0.05)))))</f>
         <v/>
       </c>
       <c r="H27" s="151"/>
@@ -7003,11 +7017,12 @@
       <c r="C28" s="115"/>
       <c r="D28" s="151"/>
       <c r="E28" s="100" t="str">
-        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D28="","",IF($D$40=Critères!$AT$3,1,10)),IF(AND(H28="",N28=""),"",IF($D$40=Critères!$AT$3,1,10)))</f>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D28="","",IF($D$40="Clapet",1,10)),IF(AND(H28="",N28=""),"",IF($D$40="Clapet",1,10)))</f>
+        <v/>
       </c>
       <c r="F28" s="153"/>
       <c r="G28" s="101" t="str">
-        <f t="shared" ref="G28:G30" si="0">IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D28="","",IF(D28&lt;50,"-",IF(D28&lt;150,0.1,0.05))),IF(AND(H28="",N28=""),"",IF(AVERAGE(H28,N28)&lt;50,"-",IF(AVERAGE(H28,N28)&lt;150,0.1,0.05))))</f>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D28="","",IF($D$40="Clapet",0.1,IF(D28&lt;50,"-",IF(D28&lt;150,0.1,0.05)))),IF(AND(H28="",N28=""),"",IF($D$40="Clapet",0.1,IF(AVERAGE(H28,N28)&lt;50,"-",IF(AVERAGE(H28,N28)&lt;150,0.1,0.05)))))</f>
         <v/>
       </c>
       <c r="H28" s="151"/>
@@ -7040,13 +7055,13 @@
       <c r="T28" s="116"/>
       <c r="U28" s="74"/>
       <c r="W28" s="236">
-        <f t="shared" ref="W28:W30" si="4">IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P28),ISNUMBER(E28)),IF(ABS(P28)&gt;E28,1,0),0),IF(AND(ISNUMBER(I28),ISNUMBER(E28)),IF(ABS(I28)&gt;E28,1,0),0))</f>
+        <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P28),ISNUMBER(E28)),IF(ABS(P28)&gt;E28,1,0),0),IF(AND(ISNUMBER(I28),ISNUMBER(E28)),IF(ABS(I28)&gt;E28,1,0),0))</f>
       </c>
       <c r="X28" s="236">
-        <f t="shared" ref="X28:X30" si="5">IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K28),ISNUMBER(G28)),IF(ABS(K28)&gt;G28,1,0),0))</f>
+        <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K28),ISNUMBER(G28)),IF(ABS(K28)&gt;G28,1,0),0))</f>
       </c>
       <c r="Y28" s="236">
-        <f t="shared" ref="Y28:Y30" si="6">IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q28),ISNUMBER(G28)),IF(ABS(Q28)&gt;G28,1,0),0),0)</f>
+        <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q28),ISNUMBER(G28)),IF(ABS(Q28)&gt;G28,1,0),0),0)</f>
       </c>
     </row>
     <row r="29" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7054,11 +7069,12 @@
       <c r="C29" s="115"/>
       <c r="D29" s="151"/>
       <c r="E29" s="100" t="str">
-        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D29="","",IF($D$40=Critères!$AT$3,1,10)),IF(AND(H29="",N29=""),"",IF($D$40=Critères!$AT$3,1,10)))</f>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D29="","",IF($D$40="Clapet",1,10)),IF(AND(H29="",N29=""),"",IF($D$40="Clapet",1,10)))</f>
+        <v/>
       </c>
       <c r="F29" s="153"/>
       <c r="G29" s="101" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D29="","",IF($D$40="Clapet",0.1,IF(D29&lt;50,"-",IF(D29&lt;150,0.1,0.05)))),IF(AND(H29="",N29=""),"",IF($D$40="Clapet",0.1,IF(AVERAGE(H29,N29)&lt;50,"-",IF(AVERAGE(H29,N29)&lt;150,0.1,0.05)))))</f>
         <v/>
       </c>
       <c r="H29" s="151"/>
@@ -7091,16 +7107,13 @@
       <c r="T29" s="116"/>
       <c r="U29" s="74"/>
       <c r="W29" s="236">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P29),ISNUMBER(E29)),IF(ABS(P29)&gt;E29,1,0),0),IF(AND(ISNUMBER(I29),ISNUMBER(E29)),IF(ABS(I29)&gt;E29,1,0),0))</f>
       </c>
       <c r="X29" s="236">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K29),ISNUMBER(G29)),IF(ABS(K29)&gt;G29,1,0),0))</f>
       </c>
       <c r="Y29" s="236">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q29),ISNUMBER(G29)),IF(ABS(Q29)&gt;G29,1,0),0),0)</f>
       </c>
     </row>
     <row r="30" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7108,11 +7121,12 @@
       <c r="C30" s="115"/>
       <c r="D30" s="152"/>
       <c r="E30" s="146" t="str">
-        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D30="","",IF($D$40=Critères!$AT$3,1,10)),IF(AND(H30="",N30=""),"",IF($D$40=Critères!$AT$3,1,10)))</f>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D30="","",IF($D$40="Clapet",1,10)),IF(AND(H30="",N30=""),"",IF($D$40="Clapet",1,10)))</f>
+        <v/>
       </c>
       <c r="F30" s="154"/>
       <c r="G30" s="147" t="str">
-        <f t="shared" si="0"/>
+        <f>IF($G$18&lt;&gt;"Mesure comparative en parallèle",IF(D30="","",IF($D$40="Clapet",0.1,IF(D30&lt;50,"-",IF(D30&lt;150,0.1,0.05)))),IF(AND(H30="",N30=""),"",IF($D$40="Clapet",0.1,IF(AVERAGE(H30,N30)&lt;50,"-",IF(AVERAGE(H30,N30)&lt;150,0.1,0.05)))))</f>
         <v/>
       </c>
       <c r="H30" s="152"/>
@@ -7145,16 +7159,13 @@
       <c r="T30" s="116"/>
       <c r="U30" s="74"/>
       <c r="W30" s="236">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P30),ISNUMBER(E30)),IF(ABS(P30)&gt;E30,1,0),0),IF(AND(ISNUMBER(I30),ISNUMBER(E30)),IF(ABS(I30)&gt;E30,1,0),0))</f>
       </c>
       <c r="X30" s="236">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K30),ISNUMBER(G30)),IF(ABS(K30)&gt;G30,1,0),0))</f>
       </c>
       <c r="Y30" s="236">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q30),ISNUMBER(G30)),IF(ABS(Q30)&gt;G30,1,0),0),0)</f>
       </c>
     </row>
     <row r="31" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7180,12 +7191,15 @@
       <c r="U31" s="74"/>
       <c r="W31" s="236" t="str">
         <f>IF(IF($G$18="Mesure comparative en parallèle",COUNT(P27:P30),COUNT(I27:I30))&gt;0,IF(SUM(W27:W30)&gt;0,"Non validé","Validé"),"Non contrôlé")</f>
+        <v/>
       </c>
       <c r="X31" s="236" t="str">
         <f>IF($G$18="Mesure comparative en parallèle","-",IF(SUMPRODUCT(ISNUMBER(K27:K30)*ISNUMBER(G27:G30))&gt;0,IF(SUM(X27:X30)&gt;0,"Non validé","Validé"),"Non contrôlé"))</f>
+        <v/>
       </c>
       <c r="Y31" s="236" t="str">
         <f>IF($G$18="Mesure comparative en parallèle",IF(SUMPRODUCT(ISNUMBER(Q27:Q30)*ISNUMBER(G27:G30))&gt;0,IF(SUM(Y27:Y30)&gt;0,"Non validé","Validé"),"Non contrôlé"),"-")</f>
+        <v/>
       </c>
     </row>
     <row r="32" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7215,6 +7229,7 @@
       <c r="U32" s="74"/>
       <c r="X32" s="236" t="str">
         <f>IF($G$18="Mesure comparative en parallèle",Y31,X31)</f>
+        <v/>
       </c>
     </row>
     <row r="33" spans="2:37" s="85" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7795,7 +7810,7 @@
       <c r="N48" s="267"/>
       <c r="O48" s="268"/>
       <c r="P48" s="264" t="str">
-        <f>IF(E48="-","Non applicable",IF(D40=Critères!BB3,"Non contrôlé",W31))</f>
+        <f>IF(E48="-","Non applicable",IF(D40="Détecteur de surverse","Non contrôlé",W31))</f>
       </c>
       <c r="Q48" s="265"/>
       <c r="R48" s="93">
@@ -7837,7 +7852,8 @@
       <c r="N49" s="267"/>
       <c r="O49" s="268"/>
       <c r="P49" s="264" t="str">
-        <f>IF(E49="-","Non applicable",IF(D40=Critères!BB3,"Non contrôlé",X32))</f>
+        <f>IF(E49="-","Non applicable",IF(D40="Détecteur de surverse","Non contrôlé",X32))</f>
+        <v/>
       </c>
       <c r="Q49" s="265"/>
       <c r="R49" s="93">

--- a/AutosurveillanceTemplates/Q_GRAV.xlsx
+++ b/AutosurveillanceTemplates/Q_GRAV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA3D779-E81C-4816-AF47-E0869C3B8B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF4C9D0-9B07-40CD-9BBA-5046A49604E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8205" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20595" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Q_GRAV" sheetId="50" r:id="rId1"/>
@@ -31,9 +31,10 @@
     <definedName name="LISTE_1">PARAM!$A$21:$A$23</definedName>
     <definedName name="LISTE_2">PARAM!$B$21:$B$24</definedName>
     <definedName name="LISTE_3">PARAM!$C$21:$C$25</definedName>
-    <definedName name="LISTE_4">PARAM!$D$21:$D$27</definedName>
+    <definedName name="LISTE_4">PARAM!$D$21:$D$25</definedName>
     <definedName name="LISTE_5">PARAM!$F$21:$F$25</definedName>
     <definedName name="LISTE_6">PARAM!$G$21</definedName>
+    <definedName name="LISTE_7">PARAM!$H$21:$H$23</definedName>
     <definedName name="Méthode">PARAM!$A$55:$A$56</definedName>
     <definedName name="Montage_sonde">PARAM!$G$44:$G$47</definedName>
     <definedName name="Q_en_charge">PARAM!$A$30:$A$35</definedName>
@@ -43,7 +44,7 @@
     <definedName name="Type_equipement">PARAM!$C$4:$C$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Q_GRAV!$B$1:$U$69</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="348">
   <si>
     <t>Code</t>
   </si>
@@ -1122,9 +1123,6 @@
     <t>Équipement de contrôle installé</t>
   </si>
   <si>
-    <t>Hauteur lue (mm)</t>
-  </si>
-  <si>
     <t>Hauteur de contrôle (mm)</t>
   </si>
   <si>
@@ -1503,30 +1501,6 @@
   </si>
   <si>
     <r>
-      <t>Débit attendu / Hauteur lue (m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/h)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Volume lu 
 (m</t>
     </r>
@@ -1579,10 +1553,6 @@
 (%)</t>
   </si>
   <si>
-    <t>EMT sur la hauteur
-(mm)</t>
-  </si>
-  <si>
     <r>
       <t>Volume attendu (m</t>
     </r>
@@ -1655,26 +1625,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>É</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>cart
-Hauteur lue (mm)</t>
-    </r>
-  </si>
-  <si>
     <t>Écart
 Débit lu
 (%)</t>
@@ -1683,11 +1633,6 @@
     <t>Écart
 Débit attendu 
 (%)</t>
-  </si>
-  <si>
-    <t>Écart
-Hauteur
-(mm)</t>
   </si>
   <si>
     <t>Écart
@@ -2118,160 +2063,47 @@
     <t>Valeurs simulées</t>
   </si>
   <si>
-    <t>Hauteur simulée (mm)</t>
-  </si>
-  <si>
-    <r>
-      <t>Débit attendu / Hauteur simulée
-(m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/h)</t>
-    </r>
-  </si>
-  <si>
-    <t>Si une mesure comparative de la vitesse est impossible, est ce qu'il existe un contrôle de cohérence des données qui atteste d'un bon fonctionnement (EMT ± 10 %) ?
-Par ailleurs, est ce que l'exploitant fait réaliser un contrôle électronique du débitmètre, ou un recalibrage sur banc d'essai des capteurs ? Le rapport atteste-t-il d'un bon fonctionnement ?</t>
+    <t>Loi hydraulique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Vous pouvez insérer ici une image présentant la loi hydraulique utilisée</t>
+  </si>
+  <si>
+    <t>LISTE_7</t>
+  </si>
+  <si>
+    <t>Entre 10 et 20%</t>
+  </si>
+  <si>
+    <t>Non validé (&gt;20%)</t>
+  </si>
+  <si>
+    <t>Une attention particulière devra être apportée en cas de modification significative des débits, de l'ajout d'un stabilisateur d'écoulement, d'un clapet ou d'un filet à l'exutoire, etc...).
+Les traces de mises en charges peuvent être un indice pour évaluer ce critère.
+En l'absence d'écoulement saisir "Non contrôlé"</t>
+  </si>
+  <si>
+    <t>Une attention particulière devra être apportée en cas de modification significative des débits, de l'ajout d'un clapet ou d'un filet à l'exutoire, etc...).
+Les traces de mises en charges peuvent être un indice pour évaluer ce critère.
+En l'absence d'écoulement saisir "Non contrôlé".  Cette question n'est pas rédhibitoire et il n'est pas demandé de faire une seconde visite, avec écoulement, pour y répondre</t>
+  </si>
+  <si>
+    <t>Une attention particulière devra être apportée en cas de modification significative des débits, de l'ajout d'un clapet ou d'un filet à l'exutoire, etc...).
+Les traces de mises en charges peuvent être un indice pour évaluer ce critère.
+En l'absence d'écoulement saisir "Non contrôlé"</t>
+  </si>
+  <si>
+    <t>En l'absence d'écoulement saisir "Non contrôlé"</t>
+  </si>
+  <si>
+    <t>Les traces de mises en charges peuvent être un indice pour évaluer ce critère.
+En l'absence d'écoulement saisir "Non contrôlé"
+Si impossibilité de se prononcer ou de doute saisir "Validé avec réserve"</t>
   </si>
   <si>
     <r>
       <t xml:space="preserve">Si une mesure comparative est possible, les écarts entre d'une part les résultats de mesure des </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>débits</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> obtenus à partir des dispositifs en place (si possible sur 3 points représentatifs du fonctionnement habituel </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>≥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 50 mm) et ceux mesurés par l'organisme de contrôle d'autre part, sont-ils cohérents ?
-     EMT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 10% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">pour une hauteur d'eau comprise entre 50 et 150 mm
-     EMT ± 5% pour une hauteur </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>≥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 150 mm</t>
-    </r>
-  </si>
-  <si>
-    <t>Le contrôle consiste à vérifier le débit par jaugeage  à l'aide d'un courantomètre selon la norme NF EN ISO 748</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Si une mesure comparative est possible, les écarts entre d'une part les résultats de mesure des </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>vitesses</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> obtenus à partir des dispositifs en place (si possible sur 3 points représentatifs du fonctionnement habituel, plus le 0 ) et ceux mesurés par l'organisme de contrôle d'autre part, sont-ils cohérents avec les spécifications du constructeur ?</t>
-    </r>
-  </si>
-  <si>
-    <t>Le contrôle consiste à vérifier le paramétrage exact de la loi telle que décrite dans l'étude de modélisation indiquée dans le manuel d'autosurveillance.
-Le nombre de points paramétrés de la courbe de conversion doit également être cohérent avec la gamme des valeurs mesurées.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Les écarts entre d'une part les résultats de mesure des </t>
     </r>
     <r>
       <rPr>
@@ -2359,35 +2191,46 @@
     </r>
   </si>
   <si>
-    <t>Les traces de mises en charges peuvent être un indice pour évaluer ce critère.
-En l'absence d'écoulement saisir "Non contrôlé".
-Si impossibilité de se prononcer ou de doute saisir "Validé avec réserve".</t>
-  </si>
-  <si>
-    <t>Une attention particulière devra être apportée en cas de modification significative des débits, de l'ajout d'un clapet ou d'un filet à l'exutoire, etc...).
-Les traces de mises en charges peuvent être un indice pour évaluer ce critère.
-En l'absence d'écoulement saisir "Non contrôlé".
-Si impossibilité de se prononcer ou de doute saisir "Validé avec réserve".</t>
-  </si>
-  <si>
-    <t>Une attention particulière devra être apportée en cas de modification significative des débits, de l'ajout d'un clapet ou d'un filet à l'exutoire, etc...).
-Les traces de mises en charges peuvent être un indice pour évaluer ce critère.
-En l'absence d'écoulement saisir "Non contrôlé". 
-Si impossibilité de se prononcer ou de doute saisir "Validé avec réserve".
-Cette question n'est pas rédhibitoire et il n'est pas demandé de réaliser une seconde visite, avec écoulement, pour y répondre</t>
-  </si>
-  <si>
-    <t>Une attention particulière devra être apportée en cas de modification significative des débits, de l'ajout d'un stabilisateur d'écoulement, d'un clapet ou d'un filet à l'exutoire, etc...).
-Les traces de mises en charges peuvent être un indice pour évaluer ce critère.
-En l'absence d'écoulement saisir "Non contrôlé".
-Si impossibilité de se prononcer ou de doute saisir "Validé avec réserve".</t>
-  </si>
-  <si>
-    <t>Loi hydraulique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Vous pouvez insérer ici une image présentant la loi hydraulique utilisée</t>
+    <t>Le contrôle consiste à vérifier le paramétrage exacte de la loi telle que décrite dans le manuel d'autosurveillance.
+Le nombre de points paramétrés de la courbe de conversion doit également être cohérent avec la gamme des valeurs mesurées.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Si une mesure comparative est impossible, est ce qu'il existe un contrôle de cohérence des données qui atteste d'un bon fonctionnement (EMT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>±</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>10 %) ?</t>
+    </r>
+  </si>
+  <si>
+    <t>Le contrôle de cohérence peut être établi par rapport aux données des années antérieures ou d'un autre point de mesure ou d'un modèle mathématique.</t>
+  </si>
+  <si>
+    <t>Si une mesure comparative est impossible, est ce que l'exploitant fait réaliser un contrôle électronique du débitmètre, ou un recalibrage sur banc d'essai des capteurs ? Le rapport atteste-t-il d'un bon fonctionnement ?</t>
   </si>
 </sst>
 </file>
@@ -2400,7 +2243,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode=";;;"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="49" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2713,11 +2556,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2727,6 +2565,18 @@
       <b/>
       <sz val="16"/>
       <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF7030A0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF7030A0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2906,7 +2756,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="112">
+  <borders count="111">
     <border>
       <left/>
       <right/>
@@ -4231,19 +4081,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -4323,7 +4160,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="342">
+  <cellXfs count="340">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4921,9 +4758,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4947,19 +4781,19 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="102" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="106" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="107" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="108" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4971,7 +4805,7 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4980,13 +4814,13 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -5001,9 +4835,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="93" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="104" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -5013,9 +4844,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="30" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5033,6 +4861,10 @@
     </xf>
     <xf numFmtId="167" fontId="30" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5321,6 +5153,38 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="110" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5334,47 +5198,14 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="11" borderId="97" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="97" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="110" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6139,8 +5970,8 @@
     <col min="1" max="2" width="2.703125" style="63" customWidth="1"/>
     <col min="3" max="20" width="11.703125" style="63" customWidth="1"/>
     <col min="21" max="21" width="2.703125" style="63" customWidth="1"/>
-    <col min="22" max="22" width="2.703125" style="236" customWidth="1"/>
-    <col min="23" max="30" width="10.703125" style="236"/>
+    <col min="22" max="22" width="2.703125" style="233" customWidth="1"/>
+    <col min="23" max="30" width="10.703125" style="233"/>
     <col min="31" max="37" width="10.703125" style="97"/>
     <col min="38" max="16384" width="10.703125" style="63"/>
   </cols>
@@ -6169,64 +6000,64 @@
     </row>
     <row r="2" spans="2:37" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="78"/>
-      <c r="C2" s="294" t="s">
-        <v>274</v>
-      </c>
-      <c r="D2" s="295"/>
-      <c r="E2" s="295"/>
-      <c r="F2" s="295"/>
-      <c r="G2" s="295"/>
-      <c r="H2" s="295"/>
-      <c r="I2" s="295"/>
-      <c r="J2" s="295"/>
-      <c r="K2" s="295"/>
-      <c r="L2" s="295"/>
-      <c r="M2" s="295"/>
-      <c r="N2" s="295"/>
-      <c r="O2" s="295"/>
-      <c r="P2" s="295"/>
-      <c r="Q2" s="295"/>
-      <c r="R2" s="295"/>
-      <c r="S2" s="295"/>
-      <c r="T2" s="296"/>
+      <c r="C2" s="292" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2" s="293"/>
+      <c r="E2" s="293"/>
+      <c r="F2" s="293"/>
+      <c r="G2" s="293"/>
+      <c r="H2" s="293"/>
+      <c r="I2" s="293"/>
+      <c r="J2" s="293"/>
+      <c r="K2" s="293"/>
+      <c r="L2" s="293"/>
+      <c r="M2" s="293"/>
+      <c r="N2" s="293"/>
+      <c r="O2" s="293"/>
+      <c r="P2" s="293"/>
+      <c r="Q2" s="293"/>
+      <c r="R2" s="293"/>
+      <c r="S2" s="293"/>
+      <c r="T2" s="294"/>
       <c r="U2" s="80"/>
     </row>
     <row r="3" spans="2:37" s="65" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="79"/>
-      <c r="C3" s="290" t="s">
+      <c r="C3" s="288" t="s">
+        <v>219</v>
+      </c>
+      <c r="D3" s="289"/>
+      <c r="E3" s="267"/>
+      <c r="F3" s="267"/>
+      <c r="G3" s="267"/>
+      <c r="H3" s="274" t="s">
+        <v>215</v>
+      </c>
+      <c r="I3" s="275"/>
+      <c r="J3" s="278"/>
+      <c r="K3" s="279"/>
+      <c r="L3" s="279"/>
+      <c r="M3" s="279"/>
+      <c r="N3" s="280"/>
+      <c r="O3" s="289" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="291"/>
-      <c r="E3" s="269"/>
-      <c r="F3" s="269"/>
-      <c r="G3" s="269"/>
-      <c r="H3" s="276" t="s">
-        <v>216</v>
-      </c>
-      <c r="I3" s="277"/>
-      <c r="J3" s="280"/>
-      <c r="K3" s="281"/>
-      <c r="L3" s="281"/>
-      <c r="M3" s="281"/>
-      <c r="N3" s="282"/>
-      <c r="O3" s="291" t="s">
-        <v>221</v>
-      </c>
-      <c r="P3" s="291"/>
-      <c r="Q3" s="291"/>
-      <c r="R3" s="303"/>
-      <c r="S3" s="303"/>
-      <c r="T3" s="304"/>
+      <c r="P3" s="289"/>
+      <c r="Q3" s="289"/>
+      <c r="R3" s="301"/>
+      <c r="S3" s="301"/>
+      <c r="T3" s="302"/>
       <c r="U3" s="81"/>
-      <c r="V3" s="237"/>
-      <c r="W3" s="237"/>
-      <c r="X3" s="237"/>
-      <c r="Y3" s="237"/>
-      <c r="Z3" s="237"/>
-      <c r="AA3" s="237"/>
-      <c r="AB3" s="237"/>
-      <c r="AC3" s="237"/>
-      <c r="AD3" s="237"/>
+      <c r="V3" s="234"/>
+      <c r="W3" s="234"/>
+      <c r="X3" s="234"/>
+      <c r="Y3" s="234"/>
+      <c r="Z3" s="234"/>
+      <c r="AA3" s="234"/>
+      <c r="AB3" s="234"/>
+      <c r="AC3" s="234"/>
+      <c r="AD3" s="234"/>
       <c r="AE3" s="102"/>
       <c r="AF3" s="102"/>
       <c r="AG3" s="102"/>
@@ -6237,40 +6068,40 @@
     </row>
     <row r="4" spans="2:37" s="65" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="79"/>
-      <c r="C4" s="290" t="s">
-        <v>217</v>
-      </c>
-      <c r="D4" s="291"/>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="276" t="s">
-        <v>223</v>
-      </c>
-      <c r="I4" s="277"/>
-      <c r="J4" s="280"/>
-      <c r="K4" s="281"/>
-      <c r="L4" s="281"/>
-      <c r="M4" s="281"/>
-      <c r="N4" s="282"/>
-      <c r="O4" s="291" t="s">
-        <v>226</v>
-      </c>
-      <c r="P4" s="291"/>
-      <c r="Q4" s="291"/>
-      <c r="R4" s="303"/>
-      <c r="S4" s="303"/>
-      <c r="T4" s="304"/>
+      <c r="C4" s="288" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" s="289"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="274" t="s">
+        <v>222</v>
+      </c>
+      <c r="I4" s="275"/>
+      <c r="J4" s="278"/>
+      <c r="K4" s="279"/>
+      <c r="L4" s="279"/>
+      <c r="M4" s="279"/>
+      <c r="N4" s="280"/>
+      <c r="O4" s="289" t="s">
+        <v>225</v>
+      </c>
+      <c r="P4" s="289"/>
+      <c r="Q4" s="289"/>
+      <c r="R4" s="301"/>
+      <c r="S4" s="301"/>
+      <c r="T4" s="302"/>
       <c r="U4" s="81"/>
-      <c r="V4" s="237"/>
-      <c r="W4" s="237"/>
-      <c r="X4" s="237"/>
-      <c r="Y4" s="237"/>
-      <c r="Z4" s="237"/>
-      <c r="AA4" s="237"/>
-      <c r="AB4" s="237"/>
-      <c r="AC4" s="237"/>
-      <c r="AD4" s="237"/>
+      <c r="V4" s="234"/>
+      <c r="W4" s="234"/>
+      <c r="X4" s="234"/>
+      <c r="Y4" s="234"/>
+      <c r="Z4" s="234"/>
+      <c r="AA4" s="234"/>
+      <c r="AB4" s="234"/>
+      <c r="AC4" s="234"/>
+      <c r="AD4" s="234"/>
       <c r="AE4" s="102"/>
       <c r="AF4" s="102"/>
       <c r="AG4" s="102"/>
@@ -6281,40 +6112,40 @@
     </row>
     <row r="5" spans="2:37" s="65" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="79"/>
-      <c r="C5" s="290" t="s">
-        <v>218</v>
-      </c>
-      <c r="D5" s="291"/>
-      <c r="E5" s="269"/>
-      <c r="F5" s="269"/>
-      <c r="G5" s="269"/>
-      <c r="H5" s="276" t="s">
-        <v>224</v>
-      </c>
-      <c r="I5" s="277"/>
-      <c r="J5" s="280"/>
-      <c r="K5" s="281"/>
-      <c r="L5" s="281"/>
-      <c r="M5" s="281"/>
-      <c r="N5" s="282"/>
-      <c r="O5" s="291" t="s">
-        <v>222</v>
-      </c>
-      <c r="P5" s="291"/>
-      <c r="Q5" s="291"/>
-      <c r="R5" s="305"/>
-      <c r="S5" s="305"/>
-      <c r="T5" s="306"/>
+      <c r="C5" s="288" t="s">
+        <v>217</v>
+      </c>
+      <c r="D5" s="289"/>
+      <c r="E5" s="267"/>
+      <c r="F5" s="267"/>
+      <c r="G5" s="267"/>
+      <c r="H5" s="274" t="s">
+        <v>223</v>
+      </c>
+      <c r="I5" s="275"/>
+      <c r="J5" s="278"/>
+      <c r="K5" s="279"/>
+      <c r="L5" s="279"/>
+      <c r="M5" s="279"/>
+      <c r="N5" s="280"/>
+      <c r="O5" s="289" t="s">
+        <v>221</v>
+      </c>
+      <c r="P5" s="289"/>
+      <c r="Q5" s="289"/>
+      <c r="R5" s="303"/>
+      <c r="S5" s="303"/>
+      <c r="T5" s="304"/>
       <c r="U5" s="81"/>
-      <c r="V5" s="237"/>
-      <c r="W5" s="237"/>
-      <c r="X5" s="237"/>
-      <c r="Y5" s="237"/>
-      <c r="Z5" s="237"/>
-      <c r="AA5" s="237"/>
-      <c r="AB5" s="237"/>
-      <c r="AC5" s="237"/>
-      <c r="AD5" s="237"/>
+      <c r="V5" s="234"/>
+      <c r="W5" s="234"/>
+      <c r="X5" s="234"/>
+      <c r="Y5" s="234"/>
+      <c r="Z5" s="234"/>
+      <c r="AA5" s="234"/>
+      <c r="AB5" s="234"/>
+      <c r="AC5" s="234"/>
+      <c r="AD5" s="234"/>
       <c r="AE5" s="102"/>
       <c r="AF5" s="102"/>
       <c r="AG5" s="102"/>
@@ -6325,43 +6156,43 @@
     </row>
     <row r="6" spans="2:37" s="65" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="79"/>
-      <c r="C6" s="292" t="s">
-        <v>219</v>
-      </c>
-      <c r="D6" s="293"/>
-      <c r="E6" s="270"/>
-      <c r="F6" s="270"/>
-      <c r="G6" s="270"/>
-      <c r="H6" s="278" t="s">
-        <v>225</v>
-      </c>
-      <c r="I6" s="279"/>
-      <c r="J6" s="283">
+      <c r="C6" s="290" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="291"/>
+      <c r="E6" s="268"/>
+      <c r="F6" s="268"/>
+      <c r="G6" s="268"/>
+      <c r="H6" s="276" t="s">
+        <v>224</v>
+      </c>
+      <c r="I6" s="277"/>
+      <c r="J6" s="281">
         <f>D40</f>
         <v>0</v>
       </c>
-      <c r="K6" s="284"/>
-      <c r="L6" s="284"/>
-      <c r="M6" s="284"/>
-      <c r="N6" s="285"/>
-      <c r="O6" s="293" t="s">
-        <v>227</v>
-      </c>
-      <c r="P6" s="293"/>
-      <c r="Q6" s="293"/>
-      <c r="R6" s="307"/>
-      <c r="S6" s="307"/>
-      <c r="T6" s="308"/>
+      <c r="K6" s="282"/>
+      <c r="L6" s="282"/>
+      <c r="M6" s="282"/>
+      <c r="N6" s="283"/>
+      <c r="O6" s="291" t="s">
+        <v>226</v>
+      </c>
+      <c r="P6" s="291"/>
+      <c r="Q6" s="291"/>
+      <c r="R6" s="305"/>
+      <c r="S6" s="305"/>
+      <c r="T6" s="306"/>
       <c r="U6" s="81"/>
-      <c r="V6" s="237"/>
-      <c r="W6" s="237"/>
-      <c r="X6" s="237"/>
-      <c r="Y6" s="237"/>
-      <c r="Z6" s="237"/>
-      <c r="AA6" s="237"/>
-      <c r="AB6" s="237"/>
-      <c r="AC6" s="237"/>
-      <c r="AD6" s="237"/>
+      <c r="V6" s="234"/>
+      <c r="W6" s="234"/>
+      <c r="X6" s="234"/>
+      <c r="Y6" s="234"/>
+      <c r="Z6" s="234"/>
+      <c r="AA6" s="234"/>
+      <c r="AB6" s="234"/>
+      <c r="AC6" s="234"/>
+      <c r="AD6" s="234"/>
       <c r="AE6" s="102"/>
       <c r="AF6" s="102"/>
       <c r="AG6" s="102"/>
@@ -6391,15 +6222,15 @@
       <c r="S7" s="66"/>
       <c r="T7" s="66"/>
       <c r="U7" s="72"/>
-      <c r="V7" s="238"/>
-      <c r="W7" s="238"/>
-      <c r="X7" s="238"/>
-      <c r="Y7" s="238"/>
-      <c r="Z7" s="238"/>
-      <c r="AA7" s="238"/>
-      <c r="AB7" s="238"/>
-      <c r="AC7" s="238"/>
-      <c r="AD7" s="238"/>
+      <c r="V7" s="235"/>
+      <c r="W7" s="235"/>
+      <c r="X7" s="235"/>
+      <c r="Y7" s="235"/>
+      <c r="Z7" s="235"/>
+      <c r="AA7" s="235"/>
+      <c r="AB7" s="235"/>
+      <c r="AC7" s="235"/>
+      <c r="AD7" s="235"/>
       <c r="AE7" s="103"/>
       <c r="AF7" s="103"/>
       <c r="AG7" s="103"/>
@@ -6410,36 +6241,36 @@
     </row>
     <row r="8" spans="2:37" s="64" customFormat="1" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="71"/>
-      <c r="C8" s="242" t="s">
-        <v>240</v>
-      </c>
-      <c r="D8" s="243"/>
-      <c r="E8" s="243"/>
-      <c r="F8" s="243"/>
-      <c r="G8" s="243"/>
-      <c r="H8" s="243"/>
-      <c r="I8" s="243"/>
-      <c r="J8" s="243"/>
-      <c r="K8" s="243"/>
-      <c r="L8" s="243"/>
-      <c r="M8" s="243"/>
-      <c r="N8" s="243"/>
-      <c r="O8" s="243"/>
-      <c r="P8" s="243"/>
-      <c r="Q8" s="243"/>
-      <c r="R8" s="243"/>
-      <c r="S8" s="243"/>
-      <c r="T8" s="244"/>
+      <c r="C8" s="240" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="241"/>
+      <c r="E8" s="241"/>
+      <c r="F8" s="241"/>
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="241"/>
+      <c r="K8" s="241"/>
+      <c r="L8" s="241"/>
+      <c r="M8" s="241"/>
+      <c r="N8" s="241"/>
+      <c r="O8" s="241"/>
+      <c r="P8" s="241"/>
+      <c r="Q8" s="241"/>
+      <c r="R8" s="241"/>
+      <c r="S8" s="241"/>
+      <c r="T8" s="242"/>
       <c r="U8" s="72"/>
-      <c r="V8" s="238"/>
-      <c r="W8" s="238"/>
-      <c r="X8" s="238"/>
-      <c r="Y8" s="238"/>
-      <c r="Z8" s="238"/>
-      <c r="AA8" s="238"/>
-      <c r="AB8" s="238"/>
-      <c r="AC8" s="238"/>
-      <c r="AD8" s="238"/>
+      <c r="V8" s="235"/>
+      <c r="W8" s="235"/>
+      <c r="X8" s="235"/>
+      <c r="Y8" s="235"/>
+      <c r="Z8" s="235"/>
+      <c r="AA8" s="235"/>
+      <c r="AB8" s="235"/>
+      <c r="AC8" s="235"/>
+      <c r="AD8" s="235"/>
       <c r="AE8" s="103"/>
       <c r="AF8" s="103"/>
       <c r="AG8" s="103"/>
@@ -6469,15 +6300,15 @@
       <c r="S9" s="66"/>
       <c r="T9" s="112"/>
       <c r="U9" s="72"/>
-      <c r="V9" s="238"/>
-      <c r="W9" s="238"/>
-      <c r="X9" s="238"/>
-      <c r="Y9" s="238"/>
-      <c r="Z9" s="238"/>
-      <c r="AA9" s="238"/>
-      <c r="AB9" s="238"/>
-      <c r="AC9" s="238"/>
-      <c r="AD9" s="238"/>
+      <c r="V9" s="235"/>
+      <c r="W9" s="235"/>
+      <c r="X9" s="235"/>
+      <c r="Y9" s="235"/>
+      <c r="Z9" s="235"/>
+      <c r="AA9" s="235"/>
+      <c r="AB9" s="235"/>
+      <c r="AC9" s="235"/>
+      <c r="AD9" s="235"/>
       <c r="AE9" s="103"/>
       <c r="AF9" s="103"/>
       <c r="AG9" s="103"/>
@@ -6489,172 +6320,172 @@
     <row r="10" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B10" s="73"/>
       <c r="C10" s="113"/>
-      <c r="D10" s="309" t="s">
+      <c r="D10" s="307" t="s">
         <v>206</v>
       </c>
-      <c r="E10" s="310"/>
-      <c r="F10" s="310"/>
-      <c r="G10" s="310"/>
-      <c r="H10" s="310"/>
-      <c r="I10" s="310"/>
-      <c r="J10" s="310"/>
-      <c r="K10" s="310"/>
-      <c r="L10" s="310"/>
-      <c r="M10" s="310"/>
-      <c r="N10" s="310"/>
-      <c r="O10" s="310"/>
-      <c r="P10" s="310"/>
-      <c r="Q10" s="310"/>
-      <c r="R10" s="310"/>
-      <c r="S10" s="311"/>
+      <c r="E10" s="308"/>
+      <c r="F10" s="308"/>
+      <c r="G10" s="308"/>
+      <c r="H10" s="308"/>
+      <c r="I10" s="308"/>
+      <c r="J10" s="308"/>
+      <c r="K10" s="308"/>
+      <c r="L10" s="308"/>
+      <c r="M10" s="308"/>
+      <c r="N10" s="308"/>
+      <c r="O10" s="308"/>
+      <c r="P10" s="308"/>
+      <c r="Q10" s="308"/>
+      <c r="R10" s="308"/>
+      <c r="S10" s="309"/>
       <c r="T10" s="114"/>
       <c r="U10" s="74"/>
     </row>
     <row r="11" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B11" s="73"/>
       <c r="C11" s="115"/>
-      <c r="D11" s="286" t="s">
-        <v>228</v>
-      </c>
-      <c r="E11" s="287"/>
-      <c r="F11" s="288"/>
-      <c r="G11" s="312"/>
-      <c r="H11" s="313"/>
-      <c r="I11" s="313"/>
-      <c r="J11" s="313"/>
-      <c r="K11" s="314"/>
-      <c r="L11" s="286" t="s">
+      <c r="D11" s="284" t="s">
+        <v>227</v>
+      </c>
+      <c r="E11" s="285"/>
+      <c r="F11" s="286"/>
+      <c r="G11" s="310"/>
+      <c r="H11" s="311"/>
+      <c r="I11" s="311"/>
+      <c r="J11" s="311"/>
+      <c r="K11" s="312"/>
+      <c r="L11" s="284" t="s">
         <v>190</v>
       </c>
-      <c r="M11" s="287"/>
-      <c r="N11" s="287"/>
-      <c r="O11" s="288"/>
-      <c r="P11" s="298"/>
-      <c r="Q11" s="299"/>
-      <c r="R11" s="299"/>
-      <c r="S11" s="300"/>
+      <c r="M11" s="285"/>
+      <c r="N11" s="285"/>
+      <c r="O11" s="286"/>
+      <c r="P11" s="296"/>
+      <c r="Q11" s="297"/>
+      <c r="R11" s="297"/>
+      <c r="S11" s="298"/>
       <c r="T11" s="116"/>
       <c r="U11" s="74"/>
     </row>
     <row r="12" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B12" s="73"/>
       <c r="C12" s="115"/>
-      <c r="D12" s="286" t="s">
-        <v>229</v>
-      </c>
-      <c r="E12" s="287"/>
-      <c r="F12" s="288"/>
-      <c r="G12" s="312"/>
-      <c r="H12" s="313"/>
-      <c r="I12" s="313"/>
-      <c r="J12" s="313"/>
-      <c r="K12" s="314"/>
-      <c r="L12" s="286" t="s">
-        <v>238</v>
-      </c>
-      <c r="M12" s="287"/>
-      <c r="N12" s="287"/>
-      <c r="O12" s="288"/>
-      <c r="P12" s="298"/>
-      <c r="Q12" s="299"/>
-      <c r="R12" s="299"/>
-      <c r="S12" s="300"/>
+      <c r="D12" s="284" t="s">
+        <v>228</v>
+      </c>
+      <c r="E12" s="285"/>
+      <c r="F12" s="286"/>
+      <c r="G12" s="310"/>
+      <c r="H12" s="311"/>
+      <c r="I12" s="311"/>
+      <c r="J12" s="311"/>
+      <c r="K12" s="312"/>
+      <c r="L12" s="284" t="s">
+        <v>237</v>
+      </c>
+      <c r="M12" s="285"/>
+      <c r="N12" s="285"/>
+      <c r="O12" s="286"/>
+      <c r="P12" s="296"/>
+      <c r="Q12" s="297"/>
+      <c r="R12" s="297"/>
+      <c r="S12" s="298"/>
       <c r="T12" s="116"/>
       <c r="U12" s="74"/>
-      <c r="X12" s="239"/>
-      <c r="Y12" s="239"/>
+      <c r="X12" s="236"/>
+      <c r="Y12" s="236"/>
     </row>
     <row r="13" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B13" s="73"/>
       <c r="C13" s="115"/>
-      <c r="D13" s="286" t="s">
-        <v>245</v>
-      </c>
-      <c r="E13" s="287"/>
-      <c r="F13" s="288"/>
-      <c r="G13" s="298"/>
-      <c r="H13" s="299"/>
-      <c r="I13" s="299"/>
-      <c r="J13" s="299"/>
-      <c r="K13" s="300"/>
-      <c r="L13" s="289" t="s">
-        <v>230</v>
-      </c>
-      <c r="M13" s="289"/>
-      <c r="N13" s="289"/>
-      <c r="O13" s="289"/>
-      <c r="P13" s="275"/>
-      <c r="Q13" s="275"/>
-      <c r="R13" s="275"/>
-      <c r="S13" s="275"/>
+      <c r="D13" s="284" t="s">
+        <v>244</v>
+      </c>
+      <c r="E13" s="285"/>
+      <c r="F13" s="286"/>
+      <c r="G13" s="296"/>
+      <c r="H13" s="297"/>
+      <c r="I13" s="297"/>
+      <c r="J13" s="297"/>
+      <c r="K13" s="298"/>
+      <c r="L13" s="287" t="s">
+        <v>229</v>
+      </c>
+      <c r="M13" s="287"/>
+      <c r="N13" s="287"/>
+      <c r="O13" s="287"/>
+      <c r="P13" s="273"/>
+      <c r="Q13" s="273"/>
+      <c r="R13" s="273"/>
+      <c r="S13" s="273"/>
       <c r="T13" s="116"/>
       <c r="U13" s="74"/>
     </row>
     <row r="14" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B14" s="73"/>
       <c r="C14" s="115"/>
-      <c r="D14" s="286" t="s">
+      <c r="D14" s="284" t="s">
         <v>188</v>
       </c>
-      <c r="E14" s="287"/>
-      <c r="F14" s="288"/>
-      <c r="G14" s="275"/>
-      <c r="H14" s="275"/>
-      <c r="I14" s="275"/>
-      <c r="J14" s="275"/>
-      <c r="K14" s="275"/>
-      <c r="L14" s="289" t="s">
-        <v>231</v>
-      </c>
-      <c r="M14" s="289"/>
-      <c r="N14" s="289"/>
-      <c r="O14" s="289"/>
-      <c r="P14" s="275"/>
-      <c r="Q14" s="275"/>
-      <c r="R14" s="275"/>
-      <c r="S14" s="275"/>
+      <c r="E14" s="285"/>
+      <c r="F14" s="286"/>
+      <c r="G14" s="273"/>
+      <c r="H14" s="273"/>
+      <c r="I14" s="273"/>
+      <c r="J14" s="273"/>
+      <c r="K14" s="273"/>
+      <c r="L14" s="287" t="s">
+        <v>230</v>
+      </c>
+      <c r="M14" s="287"/>
+      <c r="N14" s="287"/>
+      <c r="O14" s="287"/>
+      <c r="P14" s="273"/>
+      <c r="Q14" s="273"/>
+      <c r="R14" s="273"/>
+      <c r="S14" s="273"/>
       <c r="T14" s="116"/>
       <c r="U14" s="74"/>
     </row>
     <row r="15" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B15" s="73"/>
       <c r="C15" s="115"/>
-      <c r="D15" s="286" t="s">
+      <c r="D15" s="284" t="s">
         <v>189</v>
       </c>
-      <c r="E15" s="287"/>
-      <c r="F15" s="288"/>
-      <c r="G15" s="275"/>
-      <c r="H15" s="275"/>
-      <c r="I15" s="275"/>
-      <c r="J15" s="275"/>
-      <c r="K15" s="275"/>
-      <c r="L15" s="289" t="s">
-        <v>239</v>
-      </c>
-      <c r="M15" s="289"/>
-      <c r="N15" s="289"/>
-      <c r="O15" s="289"/>
-      <c r="P15" s="271"/>
-      <c r="Q15" s="271"/>
-      <c r="R15" s="271"/>
-      <c r="S15" s="271"/>
+      <c r="E15" s="285"/>
+      <c r="F15" s="286"/>
+      <c r="G15" s="273"/>
+      <c r="H15" s="273"/>
+      <c r="I15" s="273"/>
+      <c r="J15" s="273"/>
+      <c r="K15" s="273"/>
+      <c r="L15" s="287" t="s">
+        <v>238</v>
+      </c>
+      <c r="M15" s="287"/>
+      <c r="N15" s="287"/>
+      <c r="O15" s="287"/>
+      <c r="P15" s="269"/>
+      <c r="Q15" s="269"/>
+      <c r="R15" s="269"/>
+      <c r="S15" s="269"/>
       <c r="T15" s="116"/>
       <c r="U15" s="74"/>
     </row>
     <row r="16" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B16" s="73"/>
       <c r="C16" s="115"/>
-      <c r="D16" s="286" t="s">
-        <v>237</v>
-      </c>
-      <c r="E16" s="287"/>
-      <c r="F16" s="288"/>
-      <c r="G16" s="324"/>
-      <c r="H16" s="325"/>
-      <c r="I16" s="325"/>
-      <c r="J16" s="325"/>
-      <c r="K16" s="326"/>
+      <c r="D16" s="284" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" s="285"/>
+      <c r="F16" s="286"/>
+      <c r="G16" s="322"/>
+      <c r="H16" s="323"/>
+      <c r="I16" s="323"/>
+      <c r="J16" s="323"/>
+      <c r="K16" s="324"/>
       <c r="L16" s="127"/>
       <c r="M16" s="127"/>
       <c r="N16" s="127"/>
@@ -6691,126 +6522,126 @@
     <row r="18" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B18" s="73"/>
       <c r="C18" s="115"/>
-      <c r="D18" s="301" t="s">
-        <v>243</v>
-      </c>
-      <c r="E18" s="301"/>
-      <c r="F18" s="301"/>
-      <c r="G18" s="330"/>
-      <c r="H18" s="330"/>
-      <c r="I18" s="330"/>
-      <c r="J18" s="330"/>
-      <c r="K18" s="330"/>
-      <c r="L18" s="330"/>
-      <c r="M18" s="330"/>
-      <c r="N18" s="330"/>
-      <c r="O18" s="330"/>
-      <c r="P18" s="330"/>
-      <c r="Q18" s="330"/>
-      <c r="R18" s="330"/>
-      <c r="S18" s="330"/>
+      <c r="D18" s="299" t="s">
+        <v>242</v>
+      </c>
+      <c r="E18" s="299"/>
+      <c r="F18" s="299"/>
+      <c r="G18" s="336"/>
+      <c r="H18" s="336"/>
+      <c r="I18" s="336"/>
+      <c r="J18" s="336"/>
+      <c r="K18" s="336"/>
+      <c r="L18" s="336"/>
+      <c r="M18" s="336"/>
+      <c r="N18" s="336"/>
+      <c r="O18" s="336"/>
+      <c r="P18" s="336"/>
+      <c r="Q18" s="336"/>
+      <c r="R18" s="336"/>
+      <c r="S18" s="336"/>
       <c r="T18" s="116"/>
       <c r="U18" s="74"/>
     </row>
     <row r="19" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B19" s="73"/>
       <c r="C19" s="115"/>
-      <c r="D19" s="302" t="s">
+      <c r="D19" s="300" t="s">
         <v>207</v>
       </c>
-      <c r="E19" s="302"/>
-      <c r="F19" s="302"/>
-      <c r="G19" s="302"/>
-      <c r="H19" s="302"/>
-      <c r="I19" s="302"/>
-      <c r="J19" s="302"/>
-      <c r="K19" s="302"/>
-      <c r="L19" s="302"/>
-      <c r="M19" s="302"/>
-      <c r="N19" s="302"/>
-      <c r="O19" s="302"/>
-      <c r="P19" s="302"/>
-      <c r="Q19" s="302"/>
-      <c r="R19" s="302"/>
-      <c r="S19" s="302"/>
+      <c r="E19" s="300"/>
+      <c r="F19" s="300"/>
+      <c r="G19" s="300"/>
+      <c r="H19" s="300"/>
+      <c r="I19" s="300"/>
+      <c r="J19" s="300"/>
+      <c r="K19" s="300"/>
+      <c r="L19" s="300"/>
+      <c r="M19" s="300"/>
+      <c r="N19" s="300"/>
+      <c r="O19" s="300"/>
+      <c r="P19" s="300"/>
+      <c r="Q19" s="300"/>
+      <c r="R19" s="300"/>
+      <c r="S19" s="300"/>
       <c r="T19" s="116"/>
       <c r="U19" s="74"/>
     </row>
     <row r="20" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B20" s="73"/>
       <c r="C20" s="115"/>
-      <c r="D20" s="286" t="s">
-        <v>232</v>
-      </c>
-      <c r="E20" s="287"/>
-      <c r="F20" s="288"/>
-      <c r="G20" s="298"/>
-      <c r="H20" s="299"/>
-      <c r="I20" s="299"/>
-      <c r="J20" s="299"/>
-      <c r="K20" s="300"/>
-      <c r="L20" s="286" t="s">
-        <v>235</v>
-      </c>
-      <c r="M20" s="287"/>
-      <c r="N20" s="287"/>
-      <c r="O20" s="288"/>
-      <c r="P20" s="298"/>
-      <c r="Q20" s="299"/>
-      <c r="R20" s="299"/>
-      <c r="S20" s="300"/>
+      <c r="D20" s="284" t="s">
+        <v>231</v>
+      </c>
+      <c r="E20" s="285"/>
+      <c r="F20" s="286"/>
+      <c r="G20" s="296"/>
+      <c r="H20" s="297"/>
+      <c r="I20" s="297"/>
+      <c r="J20" s="297"/>
+      <c r="K20" s="298"/>
+      <c r="L20" s="284" t="s">
+        <v>234</v>
+      </c>
+      <c r="M20" s="285"/>
+      <c r="N20" s="285"/>
+      <c r="O20" s="286"/>
+      <c r="P20" s="296"/>
+      <c r="Q20" s="297"/>
+      <c r="R20" s="297"/>
+      <c r="S20" s="298"/>
       <c r="T20" s="116"/>
       <c r="U20" s="74"/>
     </row>
     <row r="21" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B21" s="73"/>
       <c r="C21" s="115"/>
-      <c r="D21" s="286" t="s">
-        <v>233</v>
-      </c>
-      <c r="E21" s="287"/>
-      <c r="F21" s="288"/>
-      <c r="G21" s="298"/>
-      <c r="H21" s="299"/>
-      <c r="I21" s="299"/>
-      <c r="J21" s="299"/>
-      <c r="K21" s="300"/>
-      <c r="L21" s="286" t="s">
-        <v>236</v>
-      </c>
-      <c r="M21" s="287"/>
-      <c r="N21" s="287"/>
-      <c r="O21" s="288"/>
-      <c r="P21" s="298"/>
-      <c r="Q21" s="299"/>
-      <c r="R21" s="299"/>
-      <c r="S21" s="300"/>
+      <c r="D21" s="284" t="s">
+        <v>232</v>
+      </c>
+      <c r="E21" s="285"/>
+      <c r="F21" s="286"/>
+      <c r="G21" s="296"/>
+      <c r="H21" s="297"/>
+      <c r="I21" s="297"/>
+      <c r="J21" s="297"/>
+      <c r="K21" s="298"/>
+      <c r="L21" s="284" t="s">
+        <v>235</v>
+      </c>
+      <c r="M21" s="285"/>
+      <c r="N21" s="285"/>
+      <c r="O21" s="286"/>
+      <c r="P21" s="296"/>
+      <c r="Q21" s="297"/>
+      <c r="R21" s="297"/>
+      <c r="S21" s="298"/>
       <c r="T21" s="116"/>
       <c r="U21" s="74"/>
     </row>
     <row r="22" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B22" s="73"/>
       <c r="C22" s="115"/>
-      <c r="D22" s="286" t="s">
-        <v>234</v>
-      </c>
-      <c r="E22" s="287"/>
-      <c r="F22" s="288"/>
-      <c r="G22" s="298"/>
-      <c r="H22" s="299"/>
-      <c r="I22" s="299"/>
-      <c r="J22" s="299"/>
-      <c r="K22" s="300"/>
-      <c r="L22" s="286" t="s">
-        <v>237</v>
-      </c>
-      <c r="M22" s="287"/>
-      <c r="N22" s="287"/>
-      <c r="O22" s="288"/>
-      <c r="P22" s="298"/>
-      <c r="Q22" s="299"/>
-      <c r="R22" s="299"/>
-      <c r="S22" s="300"/>
+      <c r="D22" s="284" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" s="285"/>
+      <c r="F22" s="286"/>
+      <c r="G22" s="296"/>
+      <c r="H22" s="297"/>
+      <c r="I22" s="297"/>
+      <c r="J22" s="297"/>
+      <c r="K22" s="298"/>
+      <c r="L22" s="284" t="s">
+        <v>236</v>
+      </c>
+      <c r="M22" s="285"/>
+      <c r="N22" s="285"/>
+      <c r="O22" s="286"/>
+      <c r="P22" s="296"/>
+      <c r="Q22" s="297"/>
+      <c r="R22" s="297"/>
+      <c r="S22" s="298"/>
       <c r="T22" s="116"/>
       <c r="U22" s="74"/>
     </row>
@@ -6839,22 +6670,22 @@
     <row r="24" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B24" s="73"/>
       <c r="C24" s="115"/>
-      <c r="D24" s="327" t="s">
+      <c r="D24" s="333" t="s">
         <v>192</v>
       </c>
-      <c r="E24" s="328"/>
-      <c r="F24" s="328"/>
-      <c r="G24" s="328"/>
-      <c r="H24" s="328"/>
-      <c r="I24" s="328"/>
-      <c r="J24" s="328"/>
-      <c r="K24" s="328"/>
-      <c r="L24" s="328"/>
-      <c r="M24" s="328"/>
-      <c r="N24" s="328"/>
-      <c r="O24" s="328"/>
-      <c r="P24" s="328"/>
-      <c r="Q24" s="329"/>
+      <c r="E24" s="334"/>
+      <c r="F24" s="334"/>
+      <c r="G24" s="334"/>
+      <c r="H24" s="334"/>
+      <c r="I24" s="334"/>
+      <c r="J24" s="334"/>
+      <c r="K24" s="334"/>
+      <c r="L24" s="334"/>
+      <c r="M24" s="334"/>
+      <c r="N24" s="334"/>
+      <c r="O24" s="334"/>
+      <c r="P24" s="334"/>
+      <c r="Q24" s="335"/>
       <c r="R24" s="142"/>
       <c r="S24" s="142"/>
       <c r="T24" s="116"/>
@@ -6863,26 +6694,26 @@
     <row r="25" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B25" s="73"/>
       <c r="C25" s="115"/>
-      <c r="D25" s="297" t="s">
-        <v>337</v>
-      </c>
-      <c r="E25" s="297"/>
-      <c r="F25" s="297"/>
-      <c r="G25" s="297"/>
-      <c r="H25" s="272" t="s">
+      <c r="D25" s="295" t="s">
+        <v>332</v>
+      </c>
+      <c r="E25" s="295"/>
+      <c r="F25" s="295"/>
+      <c r="G25" s="295"/>
+      <c r="H25" s="270" t="s">
         <v>193</v>
       </c>
-      <c r="I25" s="273"/>
-      <c r="J25" s="273"/>
-      <c r="K25" s="273"/>
-      <c r="L25" s="273"/>
-      <c r="M25" s="274"/>
-      <c r="N25" s="297" t="s">
+      <c r="I25" s="271"/>
+      <c r="J25" s="271"/>
+      <c r="K25" s="271"/>
+      <c r="L25" s="271"/>
+      <c r="M25" s="272"/>
+      <c r="N25" s="295" t="s">
         <v>194</v>
       </c>
-      <c r="O25" s="297"/>
-      <c r="P25" s="297"/>
-      <c r="Q25" s="297"/>
+      <c r="O25" s="295"/>
+      <c r="P25" s="295"/>
+      <c r="Q25" s="295"/>
       <c r="R25" s="142"/>
       <c r="S25" s="142"/>
       <c r="T25" s="116"/>
@@ -6906,7 +6737,7 @@
 (m3/h)</v>
       </c>
       <c r="G26" s="108" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H26" s="106" t="str">
         <f>IF($D$40="Clapet","Angle lu (°)","Hauteur lue (mm)")</f>
@@ -6918,24 +6749,24 @@
 Hauteur lue (mm)</v>
       </c>
       <c r="J26" s="107" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K26" s="107" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="L26" s="107" t="str">
         <f>IF($D$40="Clapet","Débit attendu / Angle lu (m3/h)","Débit attendu / Hauteur lue (m3/h)")</f>
         <v>Débit attendu / Hauteur lue (m3/h)</v>
       </c>
       <c r="M26" s="108" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N26" s="106" t="str">
         <f>IF($D$40="Clapet","Angle lu (°)","Hauteur lue (mm)")</f>
         <v>Hauteur lue (mm)</v>
       </c>
       <c r="O26" s="107" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P26" s="107" t="str">
         <f>IF($D$40="Clapet","Écart"&amp;CHAR(10)&amp;"Angle"&amp;CHAR(10)&amp;"(°)","Écart"&amp;CHAR(10)&amp;"Hauteur"&amp;CHAR(10)&amp;"(mm)")</f>
@@ -6944,20 +6775,20 @@
 (mm)</v>
       </c>
       <c r="Q26" s="108" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R26" s="142"/>
       <c r="S26" s="142"/>
       <c r="T26" s="116"/>
       <c r="U26" s="74"/>
-      <c r="W26" s="236" t="s">
+      <c r="W26" s="233" t="s">
+        <v>213</v>
+      </c>
+      <c r="X26" s="233" t="s">
         <v>214</v>
       </c>
-      <c r="X26" s="236" t="s">
-        <v>215</v>
-      </c>
-      <c r="Y26" s="236" t="s">
-        <v>215</v>
+      <c r="Y26" s="233" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7002,14 +6833,17 @@
       <c r="S27" s="142"/>
       <c r="T27" s="117"/>
       <c r="U27" s="74"/>
-      <c r="W27" s="236">
+      <c r="W27" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P27),ISNUMBER(E27)),IF(ABS(P27)&gt;E27,1,0),0),IF(AND(ISNUMBER(I27),ISNUMBER(E27)),IF(ABS(I27)&gt;E27,1,0),0))</f>
-      </c>
-      <c r="X27" s="236">
+        <v>0</v>
+      </c>
+      <c r="X27" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K27),ISNUMBER(G27)),IF(ABS(K27)&gt;G27,1,0),0))</f>
-      </c>
-      <c r="Y27" s="236">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q27),ISNUMBER(G27)),IF(ABS(Q27)&gt;G27,1,0),0),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7027,17 +6861,17 @@
       </c>
       <c r="H28" s="151"/>
       <c r="I28" s="89" t="str">
-        <f t="shared" ref="I28:I30" si="1">IF(G$18="Mesure comparative en parallèle","-",IF(OR(D28="",H28=""),"",H28-D28))</f>
+        <f t="shared" ref="I28:I30" si="0">IF(G$18="Mesure comparative en parallèle","-",IF(OR(D28="",H28=""),"",H28-D28))</f>
         <v/>
       </c>
       <c r="J28" s="153"/>
       <c r="K28" s="148" t="str">
-        <f t="shared" ref="K28:K30" si="2">IF(G$18="Mesure comparative en parallèle","-",IF(OR(F28="",J28="",D28=0),IF(D28=0, "-",""),(J28-AVERAGE(J28,F28))/AVERAGE(J28,F28)))</f>
+        <f t="shared" ref="K28:K30" si="1">IF(G$18="Mesure comparative en parallèle","-",IF(OR(F28="",J28="",D28=0),IF(D28=0, "-",""),(J28-AVERAGE(J28,F28))/AVERAGE(J28,F28)))</f>
         <v>-</v>
       </c>
       <c r="L28" s="155"/>
       <c r="M28" s="137" t="str">
-        <f t="shared" ref="M28:M30" si="3">IF(OR(D28=0,D28="",L28="",J28=""),IF(D28=0,"-",""),(J28-AVERAGE(J28,L28))/AVERAGE(J28,L28))</f>
+        <f t="shared" ref="M28:M30" si="2">IF(OR(D28=0,D28="",L28="",J28=""),IF(D28=0,"-",""),(J28-AVERAGE(J28,L28))/AVERAGE(J28,L28))</f>
         <v>-</v>
       </c>
       <c r="N28" s="151"/>
@@ -7054,14 +6888,17 @@
       <c r="S28" s="142"/>
       <c r="T28" s="116"/>
       <c r="U28" s="74"/>
-      <c r="W28" s="236">
+      <c r="W28" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P28),ISNUMBER(E28)),IF(ABS(P28)&gt;E28,1,0),0),IF(AND(ISNUMBER(I28),ISNUMBER(E28)),IF(ABS(I28)&gt;E28,1,0),0))</f>
-      </c>
-      <c r="X28" s="236">
+        <v>0</v>
+      </c>
+      <c r="X28" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K28),ISNUMBER(G28)),IF(ABS(K28)&gt;G28,1,0),0))</f>
-      </c>
-      <c r="Y28" s="236">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q28),ISNUMBER(G28)),IF(ABS(Q28)&gt;G28,1,0),0),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7079,17 +6916,17 @@
       </c>
       <c r="H29" s="151"/>
       <c r="I29" s="89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J29" s="153"/>
       <c r="K29" s="148" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="L29" s="155"/>
       <c r="M29" s="137" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="N29" s="151"/>
@@ -7106,14 +6943,17 @@
       <c r="S29" s="142"/>
       <c r="T29" s="116"/>
       <c r="U29" s="74"/>
-      <c r="W29" s="236">
+      <c r="W29" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P29),ISNUMBER(E29)),IF(ABS(P29)&gt;E29,1,0),0),IF(AND(ISNUMBER(I29),ISNUMBER(E29)),IF(ABS(I29)&gt;E29,1,0),0))</f>
-      </c>
-      <c r="X29" s="236">
+        <v>0</v>
+      </c>
+      <c r="X29" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K29),ISNUMBER(G29)),IF(ABS(K29)&gt;G29,1,0),0))</f>
-      </c>
-      <c r="Y29" s="236">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q29),ISNUMBER(G29)),IF(ABS(Q29)&gt;G29,1,0),0),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7131,17 +6971,17 @@
       </c>
       <c r="H30" s="152"/>
       <c r="I30" s="129" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J30" s="154"/>
       <c r="K30" s="149" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="L30" s="156"/>
       <c r="M30" s="138" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="N30" s="152"/>
@@ -7158,14 +6998,17 @@
       <c r="S30" s="142"/>
       <c r="T30" s="116"/>
       <c r="U30" s="74"/>
-      <c r="W30" s="236">
+      <c r="W30" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P30),ISNUMBER(E30)),IF(ABS(P30)&gt;E30,1,0),0),IF(AND(ISNUMBER(I30),ISNUMBER(E30)),IF(ABS(I30)&gt;E30,1,0),0))</f>
-      </c>
-      <c r="X30" s="236">
+        <v>0</v>
+      </c>
+      <c r="X30" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K30),ISNUMBER(G30)),IF(ABS(K30)&gt;G30,1,0),0))</f>
-      </c>
-      <c r="Y30" s="236">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="233">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q30),ISNUMBER(G30)),IF(ABS(Q30)&gt;G30,1,0),0),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7189,17 +7032,17 @@
       <c r="S31" s="142"/>
       <c r="T31" s="116"/>
       <c r="U31" s="74"/>
-      <c r="W31" s="236" t="str">
+      <c r="W31" s="233" t="str">
         <f>IF(IF($G$18="Mesure comparative en parallèle",COUNT(P27:P30),COUNT(I27:I30))&gt;0,IF(SUM(W27:W30)&gt;0,"Non validé","Validé"),"Non contrôlé")</f>
-        <v/>
-      </c>
-      <c r="X31" s="236" t="str">
+        <v>Non contrôlé</v>
+      </c>
+      <c r="X31" s="233" t="str">
         <f>IF($G$18="Mesure comparative en parallèle","-",IF(SUMPRODUCT(ISNUMBER(K27:K30)*ISNUMBER(G27:G30))&gt;0,IF(SUM(X27:X30)&gt;0,"Non validé","Validé"),"Non contrôlé"))</f>
-        <v/>
-      </c>
-      <c r="Y31" s="236" t="str">
+        <v>Non contrôlé</v>
+      </c>
+      <c r="Y31" s="233" t="str">
         <f>IF($G$18="Mesure comparative en parallèle",IF(SUMPRODUCT(ISNUMBER(Q27:Q30)*ISNUMBER(G27:G30))&gt;0,IF(SUM(Y27:Y30)&gt;0,"Non validé","Validé"),"Non contrôlé"),"-")</f>
-        <v/>
+        <v>-</v>
       </c>
     </row>
     <row r="32" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7227,53 +7070,53 @@
       <c r="S32" s="142"/>
       <c r="T32" s="116"/>
       <c r="U32" s="74"/>
-      <c r="X32" s="236" t="str">
+      <c r="X32" s="233" t="str">
         <f>IF($G$18="Mesure comparative en parallèle",Y31,X31)</f>
-        <v/>
+        <v>Non contrôlé</v>
       </c>
     </row>
     <row r="33" spans="2:37" s="85" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B33" s="83"/>
       <c r="C33" s="118"/>
-      <c r="D33" s="322" t="s">
-        <v>212</v>
-      </c>
-      <c r="E33" s="323"/>
+      <c r="D33" s="320" t="s">
+        <v>211</v>
+      </c>
+      <c r="E33" s="321"/>
       <c r="F33" s="134" t="s">
         <v>191</v>
       </c>
-      <c r="G33" s="322" t="s">
+      <c r="G33" s="320" t="s">
         <v>193</v>
       </c>
-      <c r="H33" s="323"/>
-      <c r="I33" s="322" t="s">
-        <v>213</v>
-      </c>
-      <c r="J33" s="323"/>
-      <c r="K33" s="319" t="s">
+      <c r="H33" s="321"/>
+      <c r="I33" s="320" t="s">
+        <v>212</v>
+      </c>
+      <c r="J33" s="321"/>
+      <c r="K33" s="317" t="s">
         <v>201</v>
       </c>
-      <c r="L33" s="320"/>
-      <c r="M33" s="321"/>
-      <c r="N33" s="319" t="s">
+      <c r="L33" s="318"/>
+      <c r="M33" s="319"/>
+      <c r="N33" s="317" t="s">
         <v>202</v>
       </c>
-      <c r="O33" s="320"/>
-      <c r="P33" s="321"/>
+      <c r="O33" s="318"/>
+      <c r="P33" s="319"/>
       <c r="Q33" s="96"/>
       <c r="R33" s="142"/>
       <c r="S33" s="143"/>
       <c r="T33" s="119"/>
       <c r="U33" s="84"/>
-      <c r="V33" s="240"/>
-      <c r="W33" s="240"/>
-      <c r="X33" s="240"/>
-      <c r="Y33" s="240"/>
-      <c r="Z33" s="236"/>
-      <c r="AA33" s="240"/>
-      <c r="AB33" s="240"/>
-      <c r="AC33" s="240"/>
-      <c r="AD33" s="240"/>
+      <c r="V33" s="237"/>
+      <c r="W33" s="237"/>
+      <c r="X33" s="237"/>
+      <c r="Y33" s="237"/>
+      <c r="Z33" s="233"/>
+      <c r="AA33" s="237"/>
+      <c r="AB33" s="237"/>
+      <c r="AC33" s="237"/>
+      <c r="AD33" s="237"/>
       <c r="AE33" s="104"/>
       <c r="AF33" s="104"/>
       <c r="AG33" s="104"/>
@@ -7286,29 +7129,29 @@
       <c r="B34" s="86"/>
       <c r="C34" s="120"/>
       <c r="D34" s="106" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E34" s="108" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F34" s="108" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G34" s="106" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H34" s="108" t="s">
-        <v>254</v>
-      </c>
-      <c r="I34" s="317" t="s">
-        <v>248</v>
-      </c>
-      <c r="J34" s="318"/>
+        <v>251</v>
+      </c>
+      <c r="I34" s="315" t="s">
+        <v>246</v>
+      </c>
+      <c r="J34" s="316"/>
       <c r="K34" s="90" t="s">
         <v>196</v>
       </c>
       <c r="L34" s="92" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M34" s="91" t="s">
         <v>195</v>
@@ -7317,7 +7160,7 @@
         <v>196</v>
       </c>
       <c r="O34" s="92" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P34" s="91" t="s">
         <v>195</v>
@@ -7327,15 +7170,15 @@
       <c r="S34" s="144"/>
       <c r="T34" s="121"/>
       <c r="U34" s="87"/>
-      <c r="V34" s="241"/>
-      <c r="W34" s="241"/>
-      <c r="X34" s="241"/>
-      <c r="Y34" s="241"/>
-      <c r="Z34" s="241"/>
-      <c r="AA34" s="241"/>
-      <c r="AB34" s="241"/>
-      <c r="AC34" s="241"/>
-      <c r="AD34" s="241"/>
+      <c r="V34" s="238"/>
+      <c r="W34" s="238"/>
+      <c r="X34" s="238"/>
+      <c r="Y34" s="238"/>
+      <c r="Z34" s="238"/>
+      <c r="AA34" s="238"/>
+      <c r="AB34" s="238"/>
+      <c r="AC34" s="238"/>
+      <c r="AD34" s="238"/>
       <c r="AE34" s="105"/>
       <c r="AF34" s="105"/>
       <c r="AG34" s="105"/>
@@ -7355,8 +7198,8 @@
       </c>
       <c r="G35" s="157"/>
       <c r="H35" s="158"/>
-      <c r="I35" s="315"/>
-      <c r="J35" s="316"/>
+      <c r="I35" s="313"/>
+      <c r="J35" s="314"/>
       <c r="K35" s="94" t="str">
         <f>IF(AND(E35&lt;&gt;"",G35&lt;&gt;"",G18&lt;&gt;"Mesure comparative en parallèle"),(E35+G35)/2,IF(AND(I35&lt;&gt;"",G35&lt;&gt;"",G18="Mesure comparative en parallèle"),(I35+G35)/2,""))</f>
         <v/>
@@ -7386,11 +7229,11 @@
       <c r="S35" s="145"/>
       <c r="T35" s="116"/>
       <c r="U35" s="74"/>
-      <c r="W35" s="236">
+      <c r="W35" s="233">
         <f>IF(M35&lt;&gt;"", IF(ABS(M35)&gt;F35,1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="X35" s="236">
+      <c r="X35" s="233">
         <f>IF(P35&lt;&gt;"", IF(ABS(P35)&gt;F35,1,0),0)</f>
         <v>0</v>
       </c>
@@ -7416,7 +7259,7 @@
       <c r="S36" s="123"/>
       <c r="T36" s="124"/>
       <c r="U36" s="74"/>
-      <c r="W36" s="236" t="str">
+      <c r="W36" s="233" t="str">
         <f>IFERROR(IF((K35+N35)&gt;0,IF((W35+X35)&gt;0,"Non validé","Validé"),"Non contrôlé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
@@ -7445,26 +7288,26 @@
     </row>
     <row r="38" spans="2:37" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B38" s="73"/>
-      <c r="C38" s="242" t="s">
-        <v>241</v>
-      </c>
-      <c r="D38" s="243"/>
-      <c r="E38" s="243"/>
-      <c r="F38" s="243"/>
-      <c r="G38" s="243"/>
-      <c r="H38" s="243"/>
-      <c r="I38" s="243"/>
-      <c r="J38" s="243"/>
-      <c r="K38" s="243"/>
-      <c r="L38" s="243"/>
-      <c r="M38" s="243"/>
-      <c r="N38" s="243"/>
-      <c r="O38" s="243"/>
-      <c r="P38" s="243"/>
-      <c r="Q38" s="243"/>
-      <c r="R38" s="243"/>
-      <c r="S38" s="243"/>
-      <c r="T38" s="244"/>
+      <c r="C38" s="240" t="s">
+        <v>240</v>
+      </c>
+      <c r="D38" s="241"/>
+      <c r="E38" s="241"/>
+      <c r="F38" s="241"/>
+      <c r="G38" s="241"/>
+      <c r="H38" s="241"/>
+      <c r="I38" s="241"/>
+      <c r="J38" s="241"/>
+      <c r="K38" s="241"/>
+      <c r="L38" s="241"/>
+      <c r="M38" s="241"/>
+      <c r="N38" s="241"/>
+      <c r="O38" s="241"/>
+      <c r="P38" s="241"/>
+      <c r="Q38" s="241"/>
+      <c r="R38" s="241"/>
+      <c r="S38" s="241"/>
+      <c r="T38" s="242"/>
       <c r="U38" s="74"/>
     </row>
     <row r="39" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -7492,51 +7335,51 @@
     <row r="40" spans="2:37" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B40" s="73"/>
       <c r="C40" s="115"/>
-      <c r="D40" s="252"/>
-      <c r="E40" s="252"/>
-      <c r="F40" s="252"/>
-      <c r="G40" s="252"/>
-      <c r="H40" s="252"/>
-      <c r="I40" s="252"/>
-      <c r="J40" s="252"/>
-      <c r="K40" s="252"/>
-      <c r="L40" s="252"/>
-      <c r="M40" s="252"/>
-      <c r="N40" s="252"/>
-      <c r="O40" s="252"/>
-      <c r="P40" s="252"/>
-      <c r="Q40" s="252"/>
-      <c r="R40" s="252"/>
-      <c r="S40" s="252"/>
+      <c r="D40" s="250"/>
+      <c r="E40" s="250"/>
+      <c r="F40" s="250"/>
+      <c r="G40" s="250"/>
+      <c r="H40" s="250"/>
+      <c r="I40" s="250"/>
+      <c r="J40" s="250"/>
+      <c r="K40" s="250"/>
+      <c r="L40" s="250"/>
+      <c r="M40" s="250"/>
+      <c r="N40" s="250"/>
+      <c r="O40" s="250"/>
+      <c r="P40" s="250"/>
+      <c r="Q40" s="250"/>
+      <c r="R40" s="250"/>
+      <c r="S40" s="250"/>
       <c r="T40" s="116"/>
       <c r="U40" s="74"/>
-      <c r="W40" s="236" t="s">
+      <c r="W40" s="233" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="41" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B41" s="73"/>
       <c r="C41" s="115"/>
-      <c r="D41" s="253" t="s">
+      <c r="D41" s="251" t="s">
         <v>4</v>
       </c>
-      <c r="E41" s="253"/>
-      <c r="F41" s="253"/>
-      <c r="G41" s="253"/>
-      <c r="H41" s="253"/>
-      <c r="I41" s="253"/>
-      <c r="J41" s="253"/>
-      <c r="K41" s="253" t="s">
+      <c r="E41" s="251"/>
+      <c r="F41" s="251"/>
+      <c r="G41" s="251"/>
+      <c r="H41" s="251"/>
+      <c r="I41" s="251"/>
+      <c r="J41" s="251"/>
+      <c r="K41" s="251" t="s">
         <v>170</v>
       </c>
-      <c r="L41" s="253"/>
-      <c r="M41" s="253"/>
-      <c r="N41" s="253"/>
-      <c r="O41" s="253"/>
-      <c r="P41" s="253" t="s">
+      <c r="L41" s="251"/>
+      <c r="M41" s="251"/>
+      <c r="N41" s="251"/>
+      <c r="O41" s="251"/>
+      <c r="P41" s="251" t="s">
         <v>75</v>
       </c>
-      <c r="Q41" s="253"/>
+      <c r="Q41" s="251"/>
       <c r="R41" s="110" t="s">
         <v>183</v>
       </c>
@@ -7552,25 +7395,25 @@
       <c r="D42" s="109">
         <v>1</v>
       </c>
-      <c r="E42" s="266" t="str">
+      <c r="E42" s="264" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D42+2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F42" s="267"/>
-      <c r="G42" s="267"/>
-      <c r="H42" s="267"/>
-      <c r="I42" s="267"/>
-      <c r="J42" s="268"/>
-      <c r="K42" s="266" t="str">
+      <c r="F42" s="265"/>
+      <c r="G42" s="265"/>
+      <c r="H42" s="265"/>
+      <c r="I42" s="265"/>
+      <c r="J42" s="266"/>
+      <c r="K42" s="264" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D42+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D42+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L42" s="267"/>
-      <c r="M42" s="267"/>
-      <c r="N42" s="267"/>
-      <c r="O42" s="268"/>
-      <c r="P42" s="264"/>
-      <c r="Q42" s="265"/>
+      <c r="L42" s="265"/>
+      <c r="M42" s="265"/>
+      <c r="N42" s="265"/>
+      <c r="O42" s="266"/>
+      <c r="P42" s="262"/>
+      <c r="Q42" s="263"/>
       <c r="R42" s="93">
         <f>IF(OR(P42="Validé",P42="Réserve",P42="Oui",P42="Entre 5 et 10%"),S42,0)</f>
         <v>0</v>
@@ -7581,7 +7424,7 @@
       </c>
       <c r="T42" s="116"/>
       <c r="U42" s="74"/>
-      <c r="W42" s="236" t="str">
+      <c r="W42" s="233" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D42+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
         <v/>
       </c>
@@ -7592,27 +7435,27 @@
       <c r="D43" s="109">
         <v>2</v>
       </c>
-      <c r="E43" s="266" t="str">
+      <c r="E43" s="264" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D43+2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F43" s="267"/>
-      <c r="G43" s="267"/>
-      <c r="H43" s="267"/>
-      <c r="I43" s="267"/>
-      <c r="J43" s="268"/>
-      <c r="K43" s="266" t="str">
+      <c r="F43" s="265"/>
+      <c r="G43" s="265"/>
+      <c r="H43" s="265"/>
+      <c r="I43" s="265"/>
+      <c r="J43" s="266"/>
+      <c r="K43" s="264" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D43+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D43+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L43" s="267"/>
-      <c r="M43" s="267"/>
-      <c r="N43" s="267"/>
-      <c r="O43" s="268"/>
-      <c r="P43" s="264"/>
-      <c r="Q43" s="265"/>
+      <c r="L43" s="265"/>
+      <c r="M43" s="265"/>
+      <c r="N43" s="265"/>
+      <c r="O43" s="266"/>
+      <c r="P43" s="262"/>
+      <c r="Q43" s="263"/>
       <c r="R43" s="93">
-        <f t="shared" ref="R43:R51" si="7">IF(OR(P43="Validé",P43="Réserve",P43="Oui",P43="Entre 5 et 10%"),S43,0)</f>
+        <f t="shared" ref="R43:R51" si="3">IF(OR(P43="Validé",P43="Réserve",P43="Oui",P43="Entre 5 et 10%"),S43,0)</f>
         <v>0</v>
       </c>
       <c r="S43" s="93" t="str">
@@ -7621,7 +7464,7 @@
       </c>
       <c r="T43" s="116"/>
       <c r="U43" s="74"/>
-      <c r="W43" s="236" t="str">
+      <c r="W43" s="233" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D43+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
         <v/>
       </c>
@@ -7632,27 +7475,27 @@
       <c r="D44" s="109">
         <v>3</v>
       </c>
-      <c r="E44" s="266" t="str">
+      <c r="E44" s="264" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D44+2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F44" s="267"/>
-      <c r="G44" s="267"/>
-      <c r="H44" s="267"/>
-      <c r="I44" s="267"/>
-      <c r="J44" s="268"/>
-      <c r="K44" s="266" t="str">
+      <c r="F44" s="265"/>
+      <c r="G44" s="265"/>
+      <c r="H44" s="265"/>
+      <c r="I44" s="265"/>
+      <c r="J44" s="266"/>
+      <c r="K44" s="264" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D44+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D44+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L44" s="267"/>
-      <c r="M44" s="267"/>
-      <c r="N44" s="267"/>
-      <c r="O44" s="268"/>
-      <c r="P44" s="264"/>
-      <c r="Q44" s="265"/>
+      <c r="L44" s="265"/>
+      <c r="M44" s="265"/>
+      <c r="N44" s="265"/>
+      <c r="O44" s="266"/>
+      <c r="P44" s="262"/>
+      <c r="Q44" s="263"/>
       <c r="R44" s="93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S44" s="93" t="str">
@@ -7661,7 +7504,7 @@
       </c>
       <c r="T44" s="116"/>
       <c r="U44" s="74"/>
-      <c r="W44" s="236" t="str">
+      <c r="W44" s="233" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D44+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
         <v/>
       </c>
@@ -7672,27 +7515,27 @@
       <c r="D45" s="109">
         <v>4</v>
       </c>
-      <c r="E45" s="266" t="str">
+      <c r="E45" s="264" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D45+2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F45" s="267"/>
-      <c r="G45" s="267"/>
-      <c r="H45" s="267"/>
-      <c r="I45" s="267"/>
-      <c r="J45" s="268"/>
-      <c r="K45" s="266" t="str">
+      <c r="F45" s="265"/>
+      <c r="G45" s="265"/>
+      <c r="H45" s="265"/>
+      <c r="I45" s="265"/>
+      <c r="J45" s="266"/>
+      <c r="K45" s="264" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D45+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D45+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L45" s="267"/>
-      <c r="M45" s="267"/>
-      <c r="N45" s="267"/>
-      <c r="O45" s="268"/>
-      <c r="P45" s="264"/>
-      <c r="Q45" s="265"/>
+      <c r="L45" s="265"/>
+      <c r="M45" s="265"/>
+      <c r="N45" s="265"/>
+      <c r="O45" s="266"/>
+      <c r="P45" s="262"/>
+      <c r="Q45" s="263"/>
       <c r="R45" s="93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S45" s="93" t="str">
@@ -7701,7 +7544,7 @@
       </c>
       <c r="T45" s="116"/>
       <c r="U45" s="74"/>
-      <c r="W45" s="236" t="str">
+      <c r="W45" s="233" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D45+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
         <v/>
       </c>
@@ -7712,27 +7555,27 @@
       <c r="D46" s="109">
         <v>5</v>
       </c>
-      <c r="E46" s="266" t="str">
+      <c r="E46" s="264" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D46+2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F46" s="267"/>
-      <c r="G46" s="267"/>
-      <c r="H46" s="267"/>
-      <c r="I46" s="267"/>
-      <c r="J46" s="268"/>
-      <c r="K46" s="266" t="str">
+      <c r="F46" s="265"/>
+      <c r="G46" s="265"/>
+      <c r="H46" s="265"/>
+      <c r="I46" s="265"/>
+      <c r="J46" s="266"/>
+      <c r="K46" s="264" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L46" s="267"/>
-      <c r="M46" s="267"/>
-      <c r="N46" s="267"/>
-      <c r="O46" s="268"/>
-      <c r="P46" s="264"/>
-      <c r="Q46" s="265"/>
+      <c r="L46" s="265"/>
+      <c r="M46" s="265"/>
+      <c r="N46" s="265"/>
+      <c r="O46" s="266"/>
+      <c r="P46" s="262"/>
+      <c r="Q46" s="263"/>
       <c r="R46" s="93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S46" s="93" t="str">
@@ -7741,7 +7584,7 @@
       </c>
       <c r="T46" s="116"/>
       <c r="U46" s="74"/>
-      <c r="W46" s="236" t="str">
+      <c r="W46" s="233" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D46+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
         <v/>
       </c>
@@ -7752,27 +7595,27 @@
       <c r="D47" s="109">
         <v>6</v>
       </c>
-      <c r="E47" s="266" t="str">
+      <c r="E47" s="264" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D47+2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F47" s="267"/>
-      <c r="G47" s="267"/>
-      <c r="H47" s="267"/>
-      <c r="I47" s="267"/>
-      <c r="J47" s="268"/>
-      <c r="K47" s="266" t="str">
+      <c r="F47" s="265"/>
+      <c r="G47" s="265"/>
+      <c r="H47" s="265"/>
+      <c r="I47" s="265"/>
+      <c r="J47" s="266"/>
+      <c r="K47" s="264" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L47" s="267"/>
-      <c r="M47" s="267"/>
-      <c r="N47" s="267"/>
-      <c r="O47" s="268"/>
-      <c r="P47" s="264"/>
-      <c r="Q47" s="265"/>
+      <c r="L47" s="265"/>
+      <c r="M47" s="265"/>
+      <c r="N47" s="265"/>
+      <c r="O47" s="266"/>
+      <c r="P47" s="262"/>
+      <c r="Q47" s="263"/>
       <c r="R47" s="93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S47" s="93" t="str">
@@ -7781,7 +7624,7 @@
       </c>
       <c r="T47" s="116"/>
       <c r="U47" s="74"/>
-      <c r="W47" s="236" t="str">
+      <c r="W47" s="233" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D47+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
         <v/>
       </c>
@@ -7792,29 +7635,30 @@
       <c r="D48" s="109">
         <v>7</v>
       </c>
-      <c r="E48" s="266" t="str">
+      <c r="E48" s="264" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D48+2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F48" s="267"/>
-      <c r="G48" s="267"/>
-      <c r="H48" s="267"/>
-      <c r="I48" s="267"/>
-      <c r="J48" s="268"/>
-      <c r="K48" s="266" t="str">
+      <c r="F48" s="265"/>
+      <c r="G48" s="265"/>
+      <c r="H48" s="265"/>
+      <c r="I48" s="265"/>
+      <c r="J48" s="266"/>
+      <c r="K48" s="264" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L48" s="267"/>
-      <c r="M48" s="267"/>
-      <c r="N48" s="267"/>
-      <c r="O48" s="268"/>
-      <c r="P48" s="264" t="str">
+      <c r="L48" s="265"/>
+      <c r="M48" s="265"/>
+      <c r="N48" s="265"/>
+      <c r="O48" s="266"/>
+      <c r="P48" s="262" t="str">
         <f>IF(E48="-","Non applicable",IF(D40="Détecteur de surverse","Non contrôlé",W31))</f>
-      </c>
-      <c r="Q48" s="265"/>
+        <v>Non contrôlé</v>
+      </c>
+      <c r="Q48" s="263"/>
       <c r="R48" s="93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S48" s="93" t="str">
@@ -7823,7 +7667,7 @@
       </c>
       <c r="T48" s="116"/>
       <c r="U48" s="74"/>
-      <c r="W48" s="236" t="str">
+      <c r="W48" s="233" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D48+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
         <v/>
       </c>
@@ -7834,30 +7678,30 @@
       <c r="D49" s="109">
         <v>8</v>
       </c>
-      <c r="E49" s="266" t="str">
+      <c r="E49" s="264" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D49+2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F49" s="267"/>
-      <c r="G49" s="267"/>
-      <c r="H49" s="267"/>
-      <c r="I49" s="267"/>
-      <c r="J49" s="268"/>
-      <c r="K49" s="266" t="str">
+      <c r="F49" s="265"/>
+      <c r="G49" s="265"/>
+      <c r="H49" s="265"/>
+      <c r="I49" s="265"/>
+      <c r="J49" s="266"/>
+      <c r="K49" s="264" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D49+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D49+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L49" s="267"/>
-      <c r="M49" s="267"/>
-      <c r="N49" s="267"/>
-      <c r="O49" s="268"/>
-      <c r="P49" s="264" t="str">
+      <c r="L49" s="265"/>
+      <c r="M49" s="265"/>
+      <c r="N49" s="265"/>
+      <c r="O49" s="266"/>
+      <c r="P49" s="262" t="str">
         <f>IF(E49="-","Non applicable",IF(D40="Détecteur de surverse","Non contrôlé",X32))</f>
-        <v/>
-      </c>
-      <c r="Q49" s="265"/>
+        <v>Non contrôlé</v>
+      </c>
+      <c r="Q49" s="263"/>
       <c r="R49" s="93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S49" s="93" t="str">
@@ -7866,7 +7710,7 @@
       </c>
       <c r="T49" s="116"/>
       <c r="U49" s="74"/>
-      <c r="W49" s="236" t="str">
+      <c r="W49" s="233" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D49+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
         <v/>
       </c>
@@ -7877,30 +7721,30 @@
       <c r="D50" s="109">
         <v>9</v>
       </c>
-      <c r="E50" s="266" t="str">
+      <c r="E50" s="264" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D50+2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F50" s="267"/>
-      <c r="G50" s="267"/>
-      <c r="H50" s="267"/>
-      <c r="I50" s="267"/>
-      <c r="J50" s="268"/>
-      <c r="K50" s="266" t="str">
+      <c r="F50" s="265"/>
+      <c r="G50" s="265"/>
+      <c r="H50" s="265"/>
+      <c r="I50" s="265"/>
+      <c r="J50" s="266"/>
+      <c r="K50" s="264" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D50+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D50+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L50" s="267"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="268"/>
-      <c r="P50" s="264" t="str">
+      <c r="L50" s="265"/>
+      <c r="M50" s="265"/>
+      <c r="N50" s="265"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="262" t="str">
         <f>IF(E50="-","Non applicable",IF(OR(D40=Critères!AX3,D40=Critères!BB3),"Non contrôlé",W36))</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="Q50" s="265"/>
+      <c r="Q50" s="263"/>
       <c r="R50" s="93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S50" s="93" t="str">
@@ -7909,7 +7753,7 @@
       </c>
       <c r="T50" s="116"/>
       <c r="U50" s="74"/>
-      <c r="W50" s="236" t="str">
+      <c r="W50" s="233" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D50+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
         <v/>
       </c>
@@ -7920,27 +7764,27 @@
       <c r="D51" s="109">
         <v>10</v>
       </c>
-      <c r="E51" s="266" t="str">
+      <c r="E51" s="264" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D51+2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F51" s="267"/>
-      <c r="G51" s="267"/>
-      <c r="H51" s="267"/>
-      <c r="I51" s="267"/>
-      <c r="J51" s="268"/>
-      <c r="K51" s="266" t="str">
+      <c r="F51" s="265"/>
+      <c r="G51" s="265"/>
+      <c r="H51" s="265"/>
+      <c r="I51" s="265"/>
+      <c r="J51" s="266"/>
+      <c r="K51" s="264" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D51+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D51+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L51" s="267"/>
-      <c r="M51" s="267"/>
-      <c r="N51" s="267"/>
-      <c r="O51" s="268"/>
-      <c r="P51" s="264"/>
-      <c r="Q51" s="265"/>
+      <c r="L51" s="265"/>
+      <c r="M51" s="265"/>
+      <c r="N51" s="265"/>
+      <c r="O51" s="266"/>
+      <c r="P51" s="262"/>
+      <c r="Q51" s="263"/>
       <c r="R51" s="93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S51" s="93" t="str">
@@ -7949,7 +7793,7 @@
       </c>
       <c r="T51" s="116"/>
       <c r="U51" s="74"/>
-      <c r="W51" s="236" t="str">
+      <c r="W51" s="233" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D51+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
         <v/>
       </c>
@@ -7957,54 +7801,54 @@
     <row r="52" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B52" s="73"/>
       <c r="C52" s="115"/>
-      <c r="D52" s="254" t="s">
+      <c r="D52" s="252" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="255"/>
-      <c r="F52" s="255"/>
-      <c r="G52" s="255"/>
-      <c r="H52" s="255"/>
-      <c r="I52" s="255"/>
-      <c r="J52" s="255"/>
-      <c r="K52" s="255"/>
-      <c r="L52" s="255"/>
-      <c r="M52" s="255"/>
-      <c r="N52" s="255"/>
-      <c r="O52" s="256"/>
-      <c r="P52" s="257"/>
-      <c r="Q52" s="257"/>
-      <c r="R52" s="257" t="s">
+      <c r="E52" s="253"/>
+      <c r="F52" s="253"/>
+      <c r="G52" s="253"/>
+      <c r="H52" s="253"/>
+      <c r="I52" s="253"/>
+      <c r="J52" s="253"/>
+      <c r="K52" s="253"/>
+      <c r="L52" s="253"/>
+      <c r="M52" s="253"/>
+      <c r="N52" s="253"/>
+      <c r="O52" s="254"/>
+      <c r="P52" s="255"/>
+      <c r="Q52" s="255"/>
+      <c r="R52" s="255" t="s">
         <v>6</v>
       </c>
-      <c r="S52" s="257"/>
+      <c r="S52" s="255"/>
       <c r="T52" s="116"/>
       <c r="U52" s="74"/>
     </row>
     <row r="53" spans="2:23" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B53" s="73"/>
       <c r="C53" s="115"/>
-      <c r="D53" s="261"/>
-      <c r="E53" s="262"/>
-      <c r="F53" s="262"/>
-      <c r="G53" s="262"/>
-      <c r="H53" s="262"/>
-      <c r="I53" s="262"/>
-      <c r="J53" s="262"/>
-      <c r="K53" s="262"/>
-      <c r="L53" s="262"/>
-      <c r="M53" s="262"/>
-      <c r="N53" s="262"/>
-      <c r="O53" s="263"/>
-      <c r="P53" s="258" t="str">
+      <c r="D53" s="259"/>
+      <c r="E53" s="260"/>
+      <c r="F53" s="260"/>
+      <c r="G53" s="260"/>
+      <c r="H53" s="260"/>
+      <c r="I53" s="260"/>
+      <c r="J53" s="260"/>
+      <c r="K53" s="260"/>
+      <c r="L53" s="260"/>
+      <c r="M53" s="260"/>
+      <c r="N53" s="260"/>
+      <c r="O53" s="261"/>
+      <c r="P53" s="256" t="str">
         <f>IF(R53&gt;80,"Validé",IF(R53&lt;70,"Non Validé", "Réserve"))</f>
         <v>Non Validé</v>
       </c>
-      <c r="Q53" s="258"/>
-      <c r="R53" s="259">
+      <c r="Q53" s="256"/>
+      <c r="R53" s="257">
         <f>IF(SUM(R42:R51)&gt;100,100,SUM(R42:R51))</f>
         <v>0</v>
       </c>
-      <c r="S53" s="260"/>
+      <c r="S53" s="258"/>
       <c r="T53" s="116"/>
       <c r="U53" s="74"/>
     </row>
@@ -8054,296 +7898,296 @@
     </row>
     <row r="56" spans="2:23" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B56" s="73"/>
-      <c r="C56" s="242" t="s">
-        <v>242</v>
-      </c>
-      <c r="D56" s="243"/>
-      <c r="E56" s="243"/>
-      <c r="F56" s="243"/>
-      <c r="G56" s="243"/>
-      <c r="H56" s="243"/>
-      <c r="I56" s="243"/>
-      <c r="J56" s="243"/>
-      <c r="K56" s="243"/>
-      <c r="L56" s="243"/>
-      <c r="M56" s="243"/>
-      <c r="N56" s="243"/>
-      <c r="O56" s="243"/>
-      <c r="P56" s="243"/>
-      <c r="Q56" s="243"/>
-      <c r="R56" s="243"/>
-      <c r="S56" s="243"/>
-      <c r="T56" s="244"/>
+      <c r="C56" s="240" t="s">
+        <v>241</v>
+      </c>
+      <c r="D56" s="241"/>
+      <c r="E56" s="241"/>
+      <c r="F56" s="241"/>
+      <c r="G56" s="241"/>
+      <c r="H56" s="241"/>
+      <c r="I56" s="241"/>
+      <c r="J56" s="241"/>
+      <c r="K56" s="241"/>
+      <c r="L56" s="241"/>
+      <c r="M56" s="241"/>
+      <c r="N56" s="241"/>
+      <c r="O56" s="241"/>
+      <c r="P56" s="241"/>
+      <c r="Q56" s="241"/>
+      <c r="R56" s="241"/>
+      <c r="S56" s="241"/>
+      <c r="T56" s="242"/>
       <c r="U56" s="74"/>
     </row>
     <row r="57" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B57" s="73"/>
-      <c r="C57" s="245" t="s">
+      <c r="C57" s="243" t="s">
         <v>197</v>
       </c>
-      <c r="D57" s="246"/>
-      <c r="E57" s="246"/>
-      <c r="F57" s="246"/>
-      <c r="G57" s="246"/>
-      <c r="H57" s="246"/>
-      <c r="I57" s="246"/>
-      <c r="J57" s="246"/>
-      <c r="K57" s="246"/>
-      <c r="L57" s="246"/>
-      <c r="M57" s="246"/>
-      <c r="N57" s="246"/>
-      <c r="O57" s="246"/>
-      <c r="P57" s="246"/>
-      <c r="Q57" s="246"/>
-      <c r="R57" s="246"/>
-      <c r="S57" s="246"/>
-      <c r="T57" s="247"/>
+      <c r="D57" s="244"/>
+      <c r="E57" s="244"/>
+      <c r="F57" s="244"/>
+      <c r="G57" s="244"/>
+      <c r="H57" s="244"/>
+      <c r="I57" s="244"/>
+      <c r="J57" s="244"/>
+      <c r="K57" s="244"/>
+      <c r="L57" s="244"/>
+      <c r="M57" s="244"/>
+      <c r="N57" s="244"/>
+      <c r="O57" s="244"/>
+      <c r="P57" s="244"/>
+      <c r="Q57" s="244"/>
+      <c r="R57" s="244"/>
+      <c r="S57" s="244"/>
+      <c r="T57" s="245"/>
       <c r="U57" s="74"/>
     </row>
     <row r="58" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B58" s="73"/>
-      <c r="C58" s="248"/>
-      <c r="D58" s="246"/>
-      <c r="E58" s="246"/>
-      <c r="F58" s="246"/>
-      <c r="G58" s="246"/>
-      <c r="H58" s="246"/>
-      <c r="I58" s="246"/>
-      <c r="J58" s="246"/>
-      <c r="K58" s="246"/>
-      <c r="L58" s="246"/>
-      <c r="M58" s="246"/>
-      <c r="N58" s="246"/>
-      <c r="O58" s="246"/>
-      <c r="P58" s="246"/>
-      <c r="Q58" s="246"/>
-      <c r="R58" s="246"/>
-      <c r="S58" s="246"/>
-      <c r="T58" s="247"/>
+      <c r="C58" s="246"/>
+      <c r="D58" s="244"/>
+      <c r="E58" s="244"/>
+      <c r="F58" s="244"/>
+      <c r="G58" s="244"/>
+      <c r="H58" s="244"/>
+      <c r="I58" s="244"/>
+      <c r="J58" s="244"/>
+      <c r="K58" s="244"/>
+      <c r="L58" s="244"/>
+      <c r="M58" s="244"/>
+      <c r="N58" s="244"/>
+      <c r="O58" s="244"/>
+      <c r="P58" s="244"/>
+      <c r="Q58" s="244"/>
+      <c r="R58" s="244"/>
+      <c r="S58" s="244"/>
+      <c r="T58" s="245"/>
       <c r="U58" s="74"/>
     </row>
     <row r="59" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B59" s="73"/>
-      <c r="C59" s="248"/>
-      <c r="D59" s="246"/>
-      <c r="E59" s="246"/>
-      <c r="F59" s="246"/>
-      <c r="G59" s="246"/>
-      <c r="H59" s="246"/>
-      <c r="I59" s="246"/>
-      <c r="J59" s="246"/>
-      <c r="K59" s="246"/>
-      <c r="L59" s="246"/>
-      <c r="M59" s="246"/>
-      <c r="N59" s="246"/>
-      <c r="O59" s="246"/>
-      <c r="P59" s="246"/>
-      <c r="Q59" s="246"/>
-      <c r="R59" s="246"/>
-      <c r="S59" s="246"/>
-      <c r="T59" s="247"/>
+      <c r="C59" s="246"/>
+      <c r="D59" s="244"/>
+      <c r="E59" s="244"/>
+      <c r="F59" s="244"/>
+      <c r="G59" s="244"/>
+      <c r="H59" s="244"/>
+      <c r="I59" s="244"/>
+      <c r="J59" s="244"/>
+      <c r="K59" s="244"/>
+      <c r="L59" s="244"/>
+      <c r="M59" s="244"/>
+      <c r="N59" s="244"/>
+      <c r="O59" s="244"/>
+      <c r="P59" s="244"/>
+      <c r="Q59" s="244"/>
+      <c r="R59" s="244"/>
+      <c r="S59" s="244"/>
+      <c r="T59" s="245"/>
       <c r="U59" s="74"/>
     </row>
     <row r="60" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B60" s="73"/>
-      <c r="C60" s="248"/>
-      <c r="D60" s="246"/>
-      <c r="E60" s="246"/>
-      <c r="F60" s="246"/>
-      <c r="G60" s="246"/>
-      <c r="H60" s="246"/>
-      <c r="I60" s="246"/>
-      <c r="J60" s="246"/>
-      <c r="K60" s="246"/>
-      <c r="L60" s="246"/>
-      <c r="M60" s="246"/>
-      <c r="N60" s="246"/>
-      <c r="O60" s="246"/>
-      <c r="P60" s="246"/>
-      <c r="Q60" s="246"/>
-      <c r="R60" s="246"/>
-      <c r="S60" s="246"/>
-      <c r="T60" s="247"/>
+      <c r="C60" s="246"/>
+      <c r="D60" s="244"/>
+      <c r="E60" s="244"/>
+      <c r="F60" s="244"/>
+      <c r="G60" s="244"/>
+      <c r="H60" s="244"/>
+      <c r="I60" s="244"/>
+      <c r="J60" s="244"/>
+      <c r="K60" s="244"/>
+      <c r="L60" s="244"/>
+      <c r="M60" s="244"/>
+      <c r="N60" s="244"/>
+      <c r="O60" s="244"/>
+      <c r="P60" s="244"/>
+      <c r="Q60" s="244"/>
+      <c r="R60" s="244"/>
+      <c r="S60" s="244"/>
+      <c r="T60" s="245"/>
       <c r="U60" s="74"/>
     </row>
     <row r="61" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B61" s="73"/>
-      <c r="C61" s="249"/>
-      <c r="D61" s="250"/>
-      <c r="E61" s="250"/>
-      <c r="F61" s="250"/>
-      <c r="G61" s="250"/>
-      <c r="H61" s="250"/>
-      <c r="I61" s="250"/>
-      <c r="J61" s="250"/>
-      <c r="K61" s="250"/>
-      <c r="L61" s="250"/>
-      <c r="M61" s="250"/>
-      <c r="N61" s="250"/>
-      <c r="O61" s="250"/>
-      <c r="P61" s="250"/>
-      <c r="Q61" s="250"/>
-      <c r="R61" s="250"/>
-      <c r="S61" s="250"/>
-      <c r="T61" s="251"/>
+      <c r="C61" s="247"/>
+      <c r="D61" s="248"/>
+      <c r="E61" s="248"/>
+      <c r="F61" s="248"/>
+      <c r="G61" s="248"/>
+      <c r="H61" s="248"/>
+      <c r="I61" s="248"/>
+      <c r="J61" s="248"/>
+      <c r="K61" s="248"/>
+      <c r="L61" s="248"/>
+      <c r="M61" s="248"/>
+      <c r="N61" s="248"/>
+      <c r="O61" s="248"/>
+      <c r="P61" s="248"/>
+      <c r="Q61" s="248"/>
+      <c r="R61" s="248"/>
+      <c r="S61" s="248"/>
+      <c r="T61" s="249"/>
       <c r="U61" s="74"/>
     </row>
     <row r="62" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B62" s="73"/>
-      <c r="C62" s="333"/>
-      <c r="D62" s="333"/>
-      <c r="E62" s="333"/>
-      <c r="F62" s="333"/>
-      <c r="G62" s="333"/>
-      <c r="H62" s="333"/>
-      <c r="I62" s="333"/>
-      <c r="J62" s="333"/>
-      <c r="K62" s="333"/>
-      <c r="L62" s="333"/>
-      <c r="M62" s="333"/>
-      <c r="N62" s="333"/>
-      <c r="O62" s="333"/>
-      <c r="P62" s="333"/>
-      <c r="Q62" s="333"/>
-      <c r="R62" s="333"/>
-      <c r="S62" s="333"/>
-      <c r="T62" s="333"/>
+      <c r="C62" s="239"/>
+      <c r="D62" s="239"/>
+      <c r="E62" s="239"/>
+      <c r="F62" s="239"/>
+      <c r="G62" s="239"/>
+      <c r="H62" s="239"/>
+      <c r="I62" s="239"/>
+      <c r="J62" s="239"/>
+      <c r="K62" s="239"/>
+      <c r="L62" s="239"/>
+      <c r="M62" s="239"/>
+      <c r="N62" s="239"/>
+      <c r="O62" s="239"/>
+      <c r="P62" s="239"/>
+      <c r="Q62" s="239"/>
+      <c r="R62" s="239"/>
+      <c r="S62" s="239"/>
+      <c r="T62" s="239"/>
       <c r="U62" s="74"/>
     </row>
     <row r="63" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B63" s="73"/>
-      <c r="C63" s="242" t="s">
-        <v>350</v>
-      </c>
-      <c r="D63" s="243"/>
-      <c r="E63" s="243"/>
-      <c r="F63" s="243"/>
-      <c r="G63" s="243"/>
-      <c r="H63" s="243"/>
-      <c r="I63" s="243"/>
-      <c r="J63" s="243"/>
-      <c r="K63" s="243"/>
-      <c r="L63" s="243"/>
-      <c r="M63" s="243"/>
-      <c r="N63" s="243"/>
-      <c r="O63" s="243"/>
-      <c r="P63" s="243"/>
-      <c r="Q63" s="243"/>
-      <c r="R63" s="243"/>
-      <c r="S63" s="243"/>
-      <c r="T63" s="244"/>
+      <c r="C63" s="240" t="s">
+        <v>333</v>
+      </c>
+      <c r="D63" s="241"/>
+      <c r="E63" s="241"/>
+      <c r="F63" s="241"/>
+      <c r="G63" s="241"/>
+      <c r="H63" s="241"/>
+      <c r="I63" s="241"/>
+      <c r="J63" s="241"/>
+      <c r="K63" s="241"/>
+      <c r="L63" s="241"/>
+      <c r="M63" s="241"/>
+      <c r="N63" s="241"/>
+      <c r="O63" s="241"/>
+      <c r="P63" s="241"/>
+      <c r="Q63" s="241"/>
+      <c r="R63" s="241"/>
+      <c r="S63" s="241"/>
+      <c r="T63" s="242"/>
       <c r="U63" s="74"/>
     </row>
     <row r="64" spans="2:23" ht="20.7" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B64" s="73"/>
-      <c r="C64" s="334" t="s">
-        <v>351</v>
-      </c>
-      <c r="D64" s="335"/>
-      <c r="E64" s="335"/>
-      <c r="F64" s="335"/>
-      <c r="G64" s="335"/>
-      <c r="H64" s="335"/>
-      <c r="I64" s="335"/>
-      <c r="J64" s="335"/>
-      <c r="K64" s="335"/>
-      <c r="L64" s="335"/>
-      <c r="M64" s="335"/>
-      <c r="N64" s="335"/>
-      <c r="O64" s="335"/>
-      <c r="P64" s="335"/>
-      <c r="Q64" s="335"/>
-      <c r="R64" s="335"/>
-      <c r="S64" s="335"/>
-      <c r="T64" s="336"/>
+      <c r="C64" s="325" t="s">
+        <v>334</v>
+      </c>
+      <c r="D64" s="326"/>
+      <c r="E64" s="326"/>
+      <c r="F64" s="326"/>
+      <c r="G64" s="326"/>
+      <c r="H64" s="326"/>
+      <c r="I64" s="326"/>
+      <c r="J64" s="326"/>
+      <c r="K64" s="326"/>
+      <c r="L64" s="326"/>
+      <c r="M64" s="326"/>
+      <c r="N64" s="326"/>
+      <c r="O64" s="326"/>
+      <c r="P64" s="326"/>
+      <c r="Q64" s="326"/>
+      <c r="R64" s="326"/>
+      <c r="S64" s="326"/>
+      <c r="T64" s="327"/>
       <c r="U64" s="74"/>
     </row>
     <row r="65" spans="2:21" ht="20.7" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B65" s="73"/>
-      <c r="C65" s="245"/>
-      <c r="D65" s="337"/>
-      <c r="E65" s="337"/>
-      <c r="F65" s="337"/>
-      <c r="G65" s="337"/>
-      <c r="H65" s="337"/>
-      <c r="I65" s="337"/>
-      <c r="J65" s="337"/>
-      <c r="K65" s="337"/>
-      <c r="L65" s="337"/>
-      <c r="M65" s="337"/>
-      <c r="N65" s="337"/>
-      <c r="O65" s="337"/>
-      <c r="P65" s="337"/>
-      <c r="Q65" s="337"/>
-      <c r="R65" s="337"/>
-      <c r="S65" s="337"/>
-      <c r="T65" s="338"/>
+      <c r="C65" s="243"/>
+      <c r="D65" s="328"/>
+      <c r="E65" s="328"/>
+      <c r="F65" s="328"/>
+      <c r="G65" s="328"/>
+      <c r="H65" s="328"/>
+      <c r="I65" s="328"/>
+      <c r="J65" s="328"/>
+      <c r="K65" s="328"/>
+      <c r="L65" s="328"/>
+      <c r="M65" s="328"/>
+      <c r="N65" s="328"/>
+      <c r="O65" s="328"/>
+      <c r="P65" s="328"/>
+      <c r="Q65" s="328"/>
+      <c r="R65" s="328"/>
+      <c r="S65" s="328"/>
+      <c r="T65" s="329"/>
       <c r="U65" s="74"/>
     </row>
     <row r="66" spans="2:21" ht="20.7" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B66" s="73"/>
-      <c r="C66" s="245"/>
-      <c r="D66" s="337"/>
-      <c r="E66" s="337"/>
-      <c r="F66" s="337"/>
-      <c r="G66" s="337"/>
-      <c r="H66" s="337"/>
-      <c r="I66" s="337"/>
-      <c r="J66" s="337"/>
-      <c r="K66" s="337"/>
-      <c r="L66" s="337"/>
-      <c r="M66" s="337"/>
-      <c r="N66" s="337"/>
-      <c r="O66" s="337"/>
-      <c r="P66" s="337"/>
-      <c r="Q66" s="337"/>
-      <c r="R66" s="337"/>
-      <c r="S66" s="337"/>
-      <c r="T66" s="338"/>
+      <c r="C66" s="243"/>
+      <c r="D66" s="328"/>
+      <c r="E66" s="328"/>
+      <c r="F66" s="328"/>
+      <c r="G66" s="328"/>
+      <c r="H66" s="328"/>
+      <c r="I66" s="328"/>
+      <c r="J66" s="328"/>
+      <c r="K66" s="328"/>
+      <c r="L66" s="328"/>
+      <c r="M66" s="328"/>
+      <c r="N66" s="328"/>
+      <c r="O66" s="328"/>
+      <c r="P66" s="328"/>
+      <c r="Q66" s="328"/>
+      <c r="R66" s="328"/>
+      <c r="S66" s="328"/>
+      <c r="T66" s="329"/>
       <c r="U66" s="74"/>
     </row>
     <row r="67" spans="2:21" ht="20.7" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B67" s="73"/>
-      <c r="C67" s="245"/>
-      <c r="D67" s="337"/>
-      <c r="E67" s="337"/>
-      <c r="F67" s="337"/>
-      <c r="G67" s="337"/>
-      <c r="H67" s="337"/>
-      <c r="I67" s="337"/>
-      <c r="J67" s="337"/>
-      <c r="K67" s="337"/>
-      <c r="L67" s="337"/>
-      <c r="M67" s="337"/>
-      <c r="N67" s="337"/>
-      <c r="O67" s="337"/>
-      <c r="P67" s="337"/>
-      <c r="Q67" s="337"/>
-      <c r="R67" s="337"/>
-      <c r="S67" s="337"/>
-      <c r="T67" s="338"/>
+      <c r="C67" s="243"/>
+      <c r="D67" s="328"/>
+      <c r="E67" s="328"/>
+      <c r="F67" s="328"/>
+      <c r="G67" s="328"/>
+      <c r="H67" s="328"/>
+      <c r="I67" s="328"/>
+      <c r="J67" s="328"/>
+      <c r="K67" s="328"/>
+      <c r="L67" s="328"/>
+      <c r="M67" s="328"/>
+      <c r="N67" s="328"/>
+      <c r="O67" s="328"/>
+      <c r="P67" s="328"/>
+      <c r="Q67" s="328"/>
+      <c r="R67" s="328"/>
+      <c r="S67" s="328"/>
+      <c r="T67" s="329"/>
       <c r="U67" s="74"/>
     </row>
     <row r="68" spans="2:21" ht="215.35" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B68" s="73"/>
-      <c r="C68" s="339"/>
-      <c r="D68" s="340"/>
-      <c r="E68" s="340"/>
-      <c r="F68" s="340"/>
-      <c r="G68" s="340"/>
-      <c r="H68" s="340"/>
-      <c r="I68" s="340"/>
-      <c r="J68" s="340"/>
-      <c r="K68" s="340"/>
-      <c r="L68" s="340"/>
-      <c r="M68" s="340"/>
-      <c r="N68" s="340"/>
-      <c r="O68" s="340"/>
-      <c r="P68" s="340"/>
-      <c r="Q68" s="340"/>
-      <c r="R68" s="340"/>
-      <c r="S68" s="340"/>
-      <c r="T68" s="341"/>
+      <c r="C68" s="330"/>
+      <c r="D68" s="331"/>
+      <c r="E68" s="331"/>
+      <c r="F68" s="331"/>
+      <c r="G68" s="331"/>
+      <c r="H68" s="331"/>
+      <c r="I68" s="331"/>
+      <c r="J68" s="331"/>
+      <c r="K68" s="331"/>
+      <c r="L68" s="331"/>
+      <c r="M68" s="331"/>
+      <c r="N68" s="331"/>
+      <c r="O68" s="331"/>
+      <c r="P68" s="331"/>
+      <c r="Q68" s="331"/>
+      <c r="R68" s="331"/>
+      <c r="S68" s="331"/>
+      <c r="T68" s="332"/>
       <c r="U68" s="74"/>
     </row>
     <row r="69" spans="2:21" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -8369,7 +8213,7 @@
       <c r="U69" s="77"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bYUKCM01XaHRVWNIJNA8pJXIGm2jIqmzE6AjsO7mWixlE33d6/HE0b/WvgY2Jl1Cm+PLCNKX1VqrjeQVnxKTgQ==" saltValue="39F2TeFkXEVeyDC4bfEWSA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BFMlTZdjdRcw1MHvEUz3nX2YeJDoaAwxfKE+1nLLKbwNHTCHM7uoPBQv5Hjb6nQwM4RJVxlwZiGusBH4LLKoPA==" saltValue="WMe/U4e+mnNAjUR5UMzGow==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="120">
     <mergeCell ref="C63:T63"/>
     <mergeCell ref="C64:T68"/>
@@ -9215,91 +9059,91 @@
       <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:603" ht="37.700000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="216"/>
-      <c r="B2" s="217" t="s">
+      <c r="A2" s="215"/>
+      <c r="B2" s="216" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="218"/>
-      <c r="J2" s="219"/>
-      <c r="K2" s="219"/>
-      <c r="L2" s="220"/>
-      <c r="M2" s="220"/>
-      <c r="N2" s="219"/>
-      <c r="O2" s="219"/>
-      <c r="P2" s="220"/>
-      <c r="Q2" s="220"/>
-      <c r="R2" s="219"/>
-      <c r="S2" s="219"/>
-      <c r="T2" s="220"/>
-      <c r="U2" s="220"/>
-      <c r="V2" s="221" t="s">
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="217"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="217"/>
+      <c r="J2" s="218"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="219"/>
+      <c r="M2" s="219"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="218"/>
+      <c r="P2" s="219"/>
+      <c r="Q2" s="219"/>
+      <c r="R2" s="218"/>
+      <c r="S2" s="218"/>
+      <c r="T2" s="219"/>
+      <c r="U2" s="219"/>
+      <c r="V2" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="W2" s="222"/>
-      <c r="X2" s="223"/>
-      <c r="Y2" s="223"/>
-      <c r="Z2" s="222"/>
-      <c r="AA2" s="222"/>
-      <c r="AB2" s="223"/>
-      <c r="AC2" s="223"/>
-      <c r="AD2" s="222"/>
-      <c r="AE2" s="222"/>
-      <c r="AF2" s="223"/>
-      <c r="AG2" s="223"/>
-      <c r="AH2" s="222"/>
-      <c r="AI2" s="222"/>
-      <c r="AJ2" s="223"/>
-      <c r="AK2" s="223"/>
-      <c r="AL2" s="222"/>
-      <c r="AM2" s="222"/>
-      <c r="AN2" s="223"/>
-      <c r="AO2" s="223"/>
-      <c r="AP2" s="222"/>
-      <c r="AQ2" s="222"/>
-      <c r="AR2" s="223"/>
-      <c r="AS2" s="223"/>
-      <c r="AT2" s="222"/>
-      <c r="AU2" s="222"/>
-      <c r="AV2" s="223"/>
-      <c r="AW2" s="223"/>
-      <c r="AX2" s="222"/>
-      <c r="AY2" s="222"/>
-      <c r="AZ2" s="223"/>
-      <c r="BA2" s="223"/>
-      <c r="BB2" s="222"/>
-      <c r="BC2" s="222"/>
-      <c r="BD2" s="223"/>
-      <c r="BE2" s="223"/>
-      <c r="BF2" s="224" t="s">
-        <v>333</v>
-      </c>
-      <c r="BG2" s="225"/>
-      <c r="BH2" s="225"/>
-      <c r="BI2" s="225"/>
-      <c r="BJ2" s="225"/>
-      <c r="BK2" s="225"/>
-      <c r="BL2" s="225"/>
-      <c r="BM2" s="225"/>
-      <c r="BN2" s="225"/>
-      <c r="BO2" s="225"/>
-      <c r="BP2" s="225"/>
-      <c r="BQ2" s="225"/>
-      <c r="BR2" s="226" t="s">
-        <v>334</v>
-      </c>
-      <c r="BS2" s="227"/>
-      <c r="BT2" s="227"/>
-      <c r="BU2" s="227"/>
-      <c r="BV2" s="227"/>
-      <c r="BW2" s="227"/>
-      <c r="BX2" s="227"/>
-      <c r="BY2" s="227"/>
+      <c r="W2" s="221"/>
+      <c r="X2" s="222"/>
+      <c r="Y2" s="222"/>
+      <c r="Z2" s="221"/>
+      <c r="AA2" s="221"/>
+      <c r="AB2" s="222"/>
+      <c r="AC2" s="222"/>
+      <c r="AD2" s="221"/>
+      <c r="AE2" s="221"/>
+      <c r="AF2" s="222"/>
+      <c r="AG2" s="222"/>
+      <c r="AH2" s="221"/>
+      <c r="AI2" s="221"/>
+      <c r="AJ2" s="222"/>
+      <c r="AK2" s="222"/>
+      <c r="AL2" s="221"/>
+      <c r="AM2" s="221"/>
+      <c r="AN2" s="222"/>
+      <c r="AO2" s="222"/>
+      <c r="AP2" s="221"/>
+      <c r="AQ2" s="221"/>
+      <c r="AR2" s="222"/>
+      <c r="AS2" s="222"/>
+      <c r="AT2" s="221"/>
+      <c r="AU2" s="221"/>
+      <c r="AV2" s="222"/>
+      <c r="AW2" s="222"/>
+      <c r="AX2" s="221"/>
+      <c r="AY2" s="221"/>
+      <c r="AZ2" s="222"/>
+      <c r="BA2" s="222"/>
+      <c r="BB2" s="221"/>
+      <c r="BC2" s="221"/>
+      <c r="BD2" s="222"/>
+      <c r="BE2" s="222"/>
+      <c r="BF2" s="223" t="s">
+        <v>328</v>
+      </c>
+      <c r="BG2" s="224"/>
+      <c r="BH2" s="224"/>
+      <c r="BI2" s="224"/>
+      <c r="BJ2" s="224"/>
+      <c r="BK2" s="224"/>
+      <c r="BL2" s="224"/>
+      <c r="BM2" s="224"/>
+      <c r="BN2" s="224"/>
+      <c r="BO2" s="224"/>
+      <c r="BP2" s="224"/>
+      <c r="BQ2" s="224"/>
+      <c r="BR2" s="225" t="s">
+        <v>329</v>
+      </c>
+      <c r="BS2" s="226"/>
+      <c r="BT2" s="226"/>
+      <c r="BU2" s="226"/>
+      <c r="BV2" s="226"/>
+      <c r="BW2" s="226"/>
+      <c r="BX2" s="226"/>
+      <c r="BY2" s="226"/>
       <c r="LK2" s="19"/>
       <c r="MD2" s="19"/>
       <c r="MT2" s="19"/>
@@ -9349,7 +9193,7 @@
       <c r="H3" s="28"/>
       <c r="I3" s="29"/>
       <c r="J3" s="27" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="K3" s="27"/>
       <c r="L3" s="28"/>
@@ -9361,7 +9205,7 @@
       <c r="P3" s="28"/>
       <c r="Q3" s="29"/>
       <c r="R3" s="27" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="S3" s="27"/>
       <c r="T3" s="28"/>
@@ -9385,7 +9229,7 @@
       <c r="AF3" s="33"/>
       <c r="AG3" s="34"/>
       <c r="AH3" s="31" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AI3" s="32"/>
       <c r="AJ3" s="33"/>
@@ -9690,7 +9534,7 @@
         <v>119</v>
       </c>
       <c r="C5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D5" s="180">
         <v>10</v>
@@ -9702,7 +9546,7 @@
         <v>119</v>
       </c>
       <c r="G5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H5" s="180">
         <v>10</v>
@@ -9714,7 +9558,7 @@
         <v>119</v>
       </c>
       <c r="K5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="L5" s="180">
         <v>10</v>
@@ -9726,7 +9570,7 @@
         <v>119</v>
       </c>
       <c r="O5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P5" s="180">
         <v>10</v>
@@ -9738,7 +9582,7 @@
         <v>119</v>
       </c>
       <c r="S5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="T5" s="180">
         <v>10</v>
@@ -9750,7 +9594,7 @@
         <v>119</v>
       </c>
       <c r="W5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="X5" s="180">
         <v>10</v>
@@ -9762,7 +9606,7 @@
         <v>119</v>
       </c>
       <c r="AA5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AB5" s="180">
         <v>10</v>
@@ -9774,7 +9618,7 @@
         <v>119</v>
       </c>
       <c r="AE5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AF5" s="180">
         <v>10</v>
@@ -9786,7 +9630,7 @@
         <v>119</v>
       </c>
       <c r="AI5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AJ5" s="180">
         <v>10</v>
@@ -9798,7 +9642,7 @@
         <v>119</v>
       </c>
       <c r="AM5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AN5" s="180">
         <v>10</v>
@@ -9810,7 +9654,7 @@
         <v>119</v>
       </c>
       <c r="AQ5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AR5" s="180">
         <v>10</v>
@@ -9822,7 +9666,7 @@
         <v>119</v>
       </c>
       <c r="AU5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AV5" s="180">
         <v>10</v>
@@ -9834,7 +9678,7 @@
         <v>119</v>
       </c>
       <c r="AY5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AZ5" s="180">
         <v>10</v>
@@ -9846,7 +9690,7 @@
         <v>119</v>
       </c>
       <c r="BC5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="BD5" s="180">
         <v>10</v>
@@ -9858,7 +9702,7 @@
         <v>119</v>
       </c>
       <c r="BG5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="BH5" s="180">
         <v>10</v>
@@ -9870,7 +9714,7 @@
         <v>119</v>
       </c>
       <c r="BK5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="BL5" s="180">
         <v>10</v>
@@ -9882,7 +9726,7 @@
         <v>119</v>
       </c>
       <c r="BO5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="BP5" s="180">
         <v>10</v>
@@ -9894,7 +9738,7 @@
         <v>119</v>
       </c>
       <c r="BS5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="BT5" s="180">
         <v>10</v>
@@ -9906,7 +9750,7 @@
         <v>119</v>
       </c>
       <c r="BW5" s="179" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="BX5" s="180">
         <v>10</v>
@@ -9915,7 +9759,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:603" s="46" customFormat="1" ht="50.7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:603" s="46" customFormat="1" ht="114" x14ac:dyDescent="0.4">
       <c r="A6" s="39">
         <v>2</v>
       </c>
@@ -9923,7 +9767,7 @@
         <v>120</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D6" s="42">
         <v>10</v>
@@ -9935,7 +9779,7 @@
         <v>120</v>
       </c>
       <c r="G6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H6" s="42">
         <v>10</v>
@@ -9947,7 +9791,7 @@
         <v>120</v>
       </c>
       <c r="K6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L6" s="42">
         <v>10</v>
@@ -9959,7 +9803,7 @@
         <v>120</v>
       </c>
       <c r="O6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="P6" s="42">
         <v>10</v>
@@ -9971,7 +9815,7 @@
         <v>120</v>
       </c>
       <c r="S6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="T6" s="42">
         <v>10</v>
@@ -9983,7 +9827,7 @@
         <v>121</v>
       </c>
       <c r="W6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="X6" s="42">
         <v>10</v>
@@ -9995,7 +9839,7 @@
         <v>121</v>
       </c>
       <c r="AA6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AB6" s="42">
         <v>10</v>
@@ -10007,7 +9851,7 @@
         <v>24</v>
       </c>
       <c r="AE6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AF6" s="42">
         <v>10</v>
@@ -10016,7 +9860,7 @@
         <v>40</v>
       </c>
       <c r="AH6" s="40" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AI6" s="45"/>
       <c r="AJ6" s="42">
@@ -10026,7 +9870,7 @@
         <v>40</v>
       </c>
       <c r="AL6" s="40" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AM6" s="45"/>
       <c r="AN6" s="42">
@@ -10039,7 +9883,7 @@
         <v>120</v>
       </c>
       <c r="AQ6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AR6" s="42">
         <v>10</v>
@@ -10051,7 +9895,7 @@
         <v>122</v>
       </c>
       <c r="AU6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AV6" s="42">
         <v>10</v>
@@ -10060,22 +9904,22 @@
         <v>40</v>
       </c>
       <c r="AX6" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="AY6" s="41" t="s">
-        <v>271</v>
+        <v>258</v>
+      </c>
+      <c r="AY6" s="45" t="s">
+        <v>266</v>
       </c>
       <c r="AZ6" s="42">
         <v>10</v>
       </c>
       <c r="BA6" s="43" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB6" s="40" t="s">
         <v>123</v>
       </c>
       <c r="BC6" s="45" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BD6" s="42">
         <v>20</v>
@@ -10087,7 +9931,7 @@
         <v>25</v>
       </c>
       <c r="BG6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BH6" s="42">
         <v>15</v>
@@ -10109,7 +9953,7 @@
         <v>27</v>
       </c>
       <c r="BO6" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BP6" s="42">
         <v>20</v>
@@ -10150,7 +9994,7 @@
         <v>124</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D7" s="187">
         <v>10</v>
@@ -10162,7 +10006,7 @@
         <v>124</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H7" s="187">
         <v>10</v>
@@ -10174,7 +10018,7 @@
         <v>124</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L7" s="187">
         <v>10</v>
@@ -10186,7 +10030,7 @@
         <v>124</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="P7" s="187">
         <v>10</v>
@@ -10198,7 +10042,7 @@
         <v>124</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="T7" s="187">
         <v>10</v>
@@ -10207,7 +10051,7 @@
         <v>40</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="W7" s="25" t="s">
         <v>125</v>
@@ -10219,7 +10063,7 @@
         <v>40</v>
       </c>
       <c r="Z7" s="24" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AA7" s="25" t="s">
         <v>125</v>
@@ -10231,10 +10075,10 @@
         <v>40</v>
       </c>
       <c r="AD7" s="24" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AE7" s="25" t="s">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="AF7" s="187">
         <v>10</v>
@@ -10243,14 +10087,14 @@
         <v>40</v>
       </c>
       <c r="AH7" s="24" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AI7" s="25"/>
       <c r="AJ7" s="187">
         <v>10</v>
       </c>
       <c r="AK7" s="188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AL7" s="24" t="s">
         <v>126</v>
@@ -10260,13 +10104,13 @@
         <v>10</v>
       </c>
       <c r="AO7" s="188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AP7" s="24" t="s">
         <v>127</v>
       </c>
       <c r="AQ7" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AR7" s="187">
         <v>10</v>
@@ -10278,7 +10122,7 @@
         <v>128</v>
       </c>
       <c r="AU7" s="189" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AV7" s="187">
         <v>10</v>
@@ -10287,28 +10131,28 @@
         <v>40</v>
       </c>
       <c r="AX7" s="24" t="s">
-        <v>343</v>
+        <v>129</v>
       </c>
       <c r="AY7" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AZ7" s="187">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BA7" s="188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BB7" s="24" t="s">
         <v>130</v>
       </c>
       <c r="BC7" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BD7" s="187">
         <v>20</v>
       </c>
       <c r="BE7" s="188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BF7" s="24" t="s">
         <v>131</v>
@@ -10338,7 +10182,7 @@
         <v>133</v>
       </c>
       <c r="BO7" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BP7" s="187">
         <v>30</v>
@@ -10362,7 +10206,7 @@
         <v>180</v>
       </c>
       <c r="BW7" s="25" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="BX7" s="187">
         <v>20</v>
@@ -10397,7 +10241,7 @@
         <v>40</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="J8" s="40" t="s">
         <v>134</v>
@@ -10529,13 +10373,13 @@
         <v>10</v>
       </c>
       <c r="BA8" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BB8" s="40" t="s">
         <v>139</v>
       </c>
       <c r="BC8" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BD8" s="42">
         <v>20</v>
@@ -10547,7 +10391,7 @@
         <v>28</v>
       </c>
       <c r="BG8" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BH8" s="42">
         <v>5</v>
@@ -10581,7 +10425,7 @@
         <v>181</v>
       </c>
       <c r="BS8" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BT8" s="42">
         <v>30</v>
@@ -10602,7 +10446,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:603" s="23" customFormat="1" ht="139.35" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:603" s="23" customFormat="1" ht="114.7" x14ac:dyDescent="0.4">
       <c r="A9" s="186">
         <v>5</v>
       </c>
@@ -10616,7 +10460,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="193" t="s">
         <v>143</v>
@@ -10628,7 +10472,7 @@
         <v>20</v>
       </c>
       <c r="I9" s="196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" s="193" t="s">
         <v>141</v>
@@ -10640,7 +10484,7 @@
         <v>20</v>
       </c>
       <c r="M9" s="196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N9" s="193" t="s">
         <v>141</v>
@@ -10652,7 +10496,7 @@
         <v>20</v>
       </c>
       <c r="Q9" s="196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R9" s="193" t="s">
         <v>141</v>
@@ -10664,13 +10508,13 @@
         <v>20</v>
       </c>
       <c r="U9" s="196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="W9" s="25" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="X9" s="187">
         <v>10</v>
@@ -10682,7 +10526,7 @@
         <v>34</v>
       </c>
       <c r="AA9" s="25" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="AB9" s="187">
         <v>10</v>
@@ -10694,7 +10538,7 @@
         <v>34</v>
       </c>
       <c r="AE9" s="25" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AF9" s="187">
         <v>10</v>
@@ -10706,7 +10550,7 @@
         <v>144</v>
       </c>
       <c r="AI9" s="25" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AJ9" s="187">
         <v>10</v>
@@ -10718,7 +10562,7 @@
         <v>144</v>
       </c>
       <c r="AM9" s="25" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AN9" s="187">
         <v>10</v>
@@ -10730,7 +10574,7 @@
         <v>144</v>
       </c>
       <c r="AQ9" s="25" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="AR9" s="187">
         <v>10</v>
@@ -10742,7 +10586,7 @@
         <v>145</v>
       </c>
       <c r="AU9" s="197" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AV9" s="187">
         <v>10</v>
@@ -10754,7 +10598,7 @@
         <v>146</v>
       </c>
       <c r="AY9" s="197" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AZ9" s="187">
         <v>10</v>
@@ -10766,7 +10610,7 @@
         <v>147</v>
       </c>
       <c r="BC9" s="189" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BD9" s="187">
         <v>20</v>
@@ -10784,7 +10628,7 @@
         <v>5</v>
       </c>
       <c r="BI9" s="190" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BJ9" s="191" t="s">
         <v>148</v>
@@ -10796,13 +10640,13 @@
         <v>5</v>
       </c>
       <c r="BM9" s="192" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BN9" s="193" t="s">
         <v>150</v>
       </c>
       <c r="BO9" s="194" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BP9" s="195">
         <v>20</v>
@@ -10811,20 +10655,20 @@
         <v>40</v>
       </c>
       <c r="BR9" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BS9" s="194" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BT9" s="195"/>
-      <c r="BU9" s="208" t="s">
-        <v>272</v>
+      <c r="BU9" s="207" t="s">
+        <v>267</v>
       </c>
       <c r="BV9" s="10" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="BW9" s="194" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BX9" s="187">
         <v>30</v>
@@ -10833,75 +10677,75 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:603" s="46" customFormat="1" ht="114" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:603" s="46" customFormat="1" ht="101.35" x14ac:dyDescent="0.4">
       <c r="A10" s="39">
         <v>6</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D10" s="49">
         <v>20</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="G10" s="48" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H10" s="49">
         <v>20</v>
       </c>
       <c r="I10" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J10" s="47" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="K10" s="48" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L10" s="49">
         <v>20</v>
       </c>
       <c r="M10" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N10" s="47" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="O10" s="48" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="P10" s="49">
         <v>20</v>
       </c>
       <c r="Q10" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R10" s="47" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="S10" s="48" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="T10" s="49">
         <v>20</v>
       </c>
       <c r="U10" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V10" s="44" t="s">
         <v>151</v>
       </c>
       <c r="W10" s="45" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="X10" s="42">
         <v>10</v>
@@ -10913,7 +10757,7 @@
         <v>152</v>
       </c>
       <c r="AA10" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AB10" s="42">
         <v>10</v>
@@ -10922,10 +10766,10 @@
         <v>40</v>
       </c>
       <c r="AD10" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="AE10" s="41" t="s">
         <v>266</v>
-      </c>
-      <c r="AE10" s="41" t="s">
-        <v>271</v>
       </c>
       <c r="AF10" s="42">
         <v>10</v>
@@ -10934,7 +10778,7 @@
         <v>40</v>
       </c>
       <c r="AH10" s="40" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AI10" s="41"/>
       <c r="AJ10" s="42">
@@ -10944,7 +10788,7 @@
         <v>40</v>
       </c>
       <c r="AL10" s="40" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AM10" s="41"/>
       <c r="AN10" s="42">
@@ -10954,10 +10798,10 @@
         <v>40</v>
       </c>
       <c r="AP10" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="AQ10" s="45" t="s">
         <v>266</v>
-      </c>
-      <c r="AQ10" s="45" t="s">
-        <v>271</v>
       </c>
       <c r="AR10" s="42">
         <v>10</v>
@@ -10966,10 +10810,10 @@
         <v>40</v>
       </c>
       <c r="AT10" s="40" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AU10" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AV10" s="42">
         <v>10</v>
@@ -10978,13 +10822,13 @@
         <v>40</v>
       </c>
       <c r="AX10" s="40" t="s">
-        <v>263</v>
-      </c>
-      <c r="AY10" s="45" t="s">
-        <v>271</v>
+        <v>153</v>
+      </c>
+      <c r="AY10" s="41" t="s">
+        <v>266</v>
       </c>
       <c r="AZ10" s="42">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BA10" s="43" t="s">
         <v>40</v>
@@ -10993,13 +10837,13 @@
         <v>154</v>
       </c>
       <c r="BC10" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BD10" s="42">
         <v>5</v>
       </c>
       <c r="BE10" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BF10" s="40" t="s">
         <v>35</v>
@@ -11011,13 +10855,13 @@
         <v>5</v>
       </c>
       <c r="BI10" s="165" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BJ10" s="166" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BK10" s="41" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="BL10" s="42">
         <v>0</v>
@@ -11026,211 +10870,213 @@
         <v>40</v>
       </c>
       <c r="BN10" s="40" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BO10" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BP10" s="42"/>
-      <c r="BQ10" s="209" t="s">
-        <v>272</v>
+      <c r="BQ10" s="208" t="s">
+        <v>267</v>
       </c>
       <c r="BR10" s="44" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BS10" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BT10" s="42"/>
       <c r="BU10" s="43" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="BV10" s="44" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BW10" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BX10" s="42"/>
-      <c r="BY10" s="209" t="s">
-        <v>272</v>
+      <c r="BY10" s="208" t="s">
+        <v>267</v>
       </c>
     </row>
-    <row r="11" spans="1:603" s="23" customFormat="1" ht="88.7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:603" s="23" customFormat="1" ht="140.35" x14ac:dyDescent="0.4">
       <c r="A11" s="186">
         <v>7</v>
       </c>
       <c r="B11" s="193" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C11" s="194" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D11" s="195">
         <v>20</v>
       </c>
       <c r="E11" s="196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="193" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G11" s="194" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H11" s="195">
         <v>20</v>
       </c>
       <c r="I11" s="196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J11" s="193" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="K11" s="194" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L11" s="195">
         <v>20</v>
       </c>
       <c r="M11" s="196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N11" s="193" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="O11" s="194" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="P11" s="195">
         <v>20</v>
       </c>
       <c r="Q11" s="196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R11" s="193" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="S11" s="194" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="T11" s="195">
         <v>20</v>
       </c>
       <c r="U11" s="196" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V11" s="10" t="s">
         <v>156</v>
       </c>
       <c r="W11" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="X11" s="187">
         <v>10</v>
       </c>
       <c r="Y11" s="188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z11" s="10" t="s">
         <v>156</v>
       </c>
       <c r="AA11" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AB11" s="187">
         <v>10</v>
       </c>
       <c r="AC11" s="188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD11" s="10" t="s">
         <v>156</v>
       </c>
       <c r="AE11" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AF11" s="187">
         <v>10</v>
       </c>
       <c r="AG11" s="188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH11" s="10" t="s">
         <v>156</v>
       </c>
       <c r="AI11" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AJ11" s="187">
         <v>10</v>
       </c>
       <c r="AK11" s="188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AL11" s="10" t="s">
         <v>156</v>
       </c>
       <c r="AM11" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AN11" s="187">
         <v>10</v>
       </c>
       <c r="AO11" s="188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AP11" s="10" t="s">
         <v>156</v>
       </c>
       <c r="AQ11" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AR11" s="187">
         <v>10</v>
       </c>
       <c r="AS11" s="188" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AT11" s="24" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AU11" s="189" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AV11" s="187">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AW11" s="188" t="s">
-        <v>41</v>
-      </c>
-      <c r="AX11" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="AY11" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="AZ11" s="42">
-        <v>10</v>
-      </c>
-      <c r="BA11" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="AX11" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="AY11" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ11" s="187">
+        <v>20</v>
+      </c>
+      <c r="BA11" s="188" t="s">
+        <v>40</v>
       </c>
       <c r="BB11" s="24" t="s">
-        <v>271</v>
+        <v>157</v>
       </c>
       <c r="BC11" s="25" t="s">
-        <v>271</v>
-      </c>
-      <c r="BD11" s="187"/>
+        <v>266</v>
+      </c>
+      <c r="BD11" s="187">
+        <v>5</v>
+      </c>
       <c r="BE11" s="188" t="s">
-        <v>272</v>
+        <v>40</v>
       </c>
       <c r="BF11" s="24" t="s">
         <v>155</v>
       </c>
       <c r="BG11" s="25" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="BH11" s="187">
         <v>10</v>
@@ -11238,47 +11084,47 @@
       <c r="BI11" s="190" t="s">
         <v>40</v>
       </c>
-      <c r="BJ11" s="228" t="s">
-        <v>336</v>
-      </c>
-      <c r="BK11" s="229" t="s">
-        <v>268</v>
-      </c>
-      <c r="BL11" s="230">
+      <c r="BJ11" s="227" t="s">
+        <v>331</v>
+      </c>
+      <c r="BK11" s="228" t="s">
+        <v>263</v>
+      </c>
+      <c r="BL11" s="229">
         <v>10</v>
       </c>
-      <c r="BM11" s="231" t="s">
-        <v>41</v>
+      <c r="BM11" s="192" t="s">
+        <v>40</v>
       </c>
       <c r="BN11" s="24" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BO11" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BP11" s="187"/>
       <c r="BQ11" s="15" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="BR11" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BS11" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BT11" s="187"/>
-      <c r="BU11" s="210" t="s">
-        <v>272</v>
+      <c r="BU11" s="209" t="s">
+        <v>267</v>
       </c>
       <c r="BV11" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BW11" s="25" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BX11" s="187"/>
       <c r="BY11" s="188" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:603" s="46" customFormat="1" ht="178.35" x14ac:dyDescent="0.4">
@@ -11295,7 +11141,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12" s="40" t="s">
         <v>158</v>
@@ -11307,7 +11153,7 @@
         <v>10</v>
       </c>
       <c r="I12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J12" s="51" t="s">
         <v>158</v>
@@ -11319,7 +11165,7 @@
         <v>10</v>
       </c>
       <c r="M12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N12" s="51" t="s">
         <v>158</v>
@@ -11331,7 +11177,7 @@
         <v>10</v>
       </c>
       <c r="Q12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R12" s="51" t="s">
         <v>158</v>
@@ -11343,166 +11189,170 @@
         <v>10</v>
       </c>
       <c r="U12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V12" s="44" t="s">
         <v>160</v>
       </c>
       <c r="W12" s="41" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="X12" s="42">
         <v>10</v>
       </c>
       <c r="Y12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z12" s="44" t="s">
         <v>160</v>
       </c>
       <c r="AA12" s="41" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AB12" s="42">
         <v>10</v>
       </c>
       <c r="AC12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD12" s="44" t="s">
         <v>160</v>
       </c>
       <c r="AE12" s="41" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AF12" s="42">
         <v>10</v>
       </c>
       <c r="AG12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH12" s="44" t="s">
         <v>160</v>
       </c>
       <c r="AI12" s="41" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AJ12" s="42">
         <v>10</v>
       </c>
       <c r="AK12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AL12" s="44" t="s">
         <v>160</v>
       </c>
       <c r="AM12" s="41" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="AN12" s="42">
         <v>10</v>
       </c>
       <c r="AO12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AP12" s="44" t="s">
-        <v>345</v>
-      </c>
-      <c r="AQ12" s="41"/>
+        <v>160</v>
+      </c>
+      <c r="AQ12" s="41" t="s">
+        <v>315</v>
+      </c>
       <c r="AR12" s="42">
         <v>10</v>
       </c>
       <c r="AS12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AT12" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="AU12" s="41"/>
+        <v>325</v>
+      </c>
+      <c r="AU12" s="41" t="s">
+        <v>344</v>
+      </c>
       <c r="AV12" s="42">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AW12" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="AX12" s="44" t="s">
-        <v>341</v>
-      </c>
-      <c r="AY12" s="41" t="s">
-        <v>342</v>
-      </c>
-      <c r="AZ12" s="42">
-        <v>10</v>
+        <v>40</v>
+      </c>
+      <c r="AX12" s="47" t="s">
+        <v>345</v>
+      </c>
+      <c r="AY12" s="48" t="s">
+        <v>346</v>
+      </c>
+      <c r="AZ12" s="49">
+        <v>20</v>
       </c>
       <c r="BA12" s="43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BB12" s="40" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BC12" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BD12" s="42"/>
       <c r="BE12" s="43" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="BF12" s="40" t="s">
         <v>36</v>
       </c>
       <c r="BG12" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BH12" s="42">
         <v>5</v>
       </c>
       <c r="BI12" s="165" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BJ12" s="166" t="s">
         <v>36</v>
       </c>
       <c r="BK12" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BL12" s="42">
         <v>5</v>
       </c>
       <c r="BM12" s="167" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BN12" s="40" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BO12" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BP12" s="42"/>
-      <c r="BQ12" s="211" t="s">
-        <v>272</v>
+      <c r="BQ12" s="210" t="s">
+        <v>267</v>
       </c>
       <c r="BR12" s="44" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BS12" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BT12" s="42"/>
-      <c r="BU12" s="209" t="s">
-        <v>272</v>
+      <c r="BU12" s="208" t="s">
+        <v>267</v>
       </c>
       <c r="BV12" s="44" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BW12" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BX12" s="42"/>
-      <c r="BY12" s="212" t="s">
-        <v>272</v>
+      <c r="BY12" s="211" t="s">
+        <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:603" s="23" customFormat="1" ht="114" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:603" s="23" customFormat="1" ht="93.35" x14ac:dyDescent="0.4">
       <c r="A13" s="198">
         <v>9</v>
       </c>
@@ -11510,7 +11360,7 @@
         <v>37</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D13" s="14">
         <v>20</v>
@@ -11522,7 +11372,7 @@
         <v>37</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H13" s="14">
         <v>20</v>
@@ -11534,7 +11384,7 @@
         <v>37</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L13" s="14">
         <v>20</v>
@@ -11546,7 +11396,7 @@
         <v>37</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="P13" s="14">
         <v>20</v>
@@ -11555,10 +11405,10 @@
         <v>39</v>
       </c>
       <c r="R13" s="12" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="S13" s="13" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="T13" s="14">
         <v>20</v>
@@ -11576,7 +11426,7 @@
         <v>10</v>
       </c>
       <c r="Y13" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z13" s="199" t="s">
         <v>162</v>
@@ -11588,7 +11438,7 @@
         <v>10</v>
       </c>
       <c r="AC13" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD13" s="199" t="s">
         <v>162</v>
@@ -11600,7 +11450,7 @@
         <v>10</v>
       </c>
       <c r="AG13" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH13" s="199" t="s">
         <v>162</v>
@@ -11612,7 +11462,7 @@
         <v>10</v>
       </c>
       <c r="AK13" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AL13" s="199" t="s">
         <v>162</v>
@@ -11624,7 +11474,7 @@
         <v>10</v>
       </c>
       <c r="AO13" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AP13" s="199" t="s">
         <v>162</v>
@@ -11636,95 +11486,95 @@
         <v>10</v>
       </c>
       <c r="AS13" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="AT13" s="199" t="s">
-        <v>162</v>
+        <v>40</v>
+      </c>
+      <c r="AT13" s="12" t="s">
+        <v>266</v>
       </c>
       <c r="AU13" s="13" t="s">
-        <v>163</v>
+        <v>330</v>
       </c>
       <c r="AV13" s="14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW13" s="15" t="s">
-        <v>41</v>
+        <v>267</v>
       </c>
       <c r="AX13" s="200" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AY13" s="201" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AZ13" s="202">
         <v>20</v>
       </c>
-      <c r="BA13" s="203" t="s">
-        <v>41</v>
+      <c r="BA13" s="188" t="s">
+        <v>40</v>
       </c>
       <c r="BB13" s="24" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BC13" s="13" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BD13" s="14"/>
       <c r="BE13" s="15" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="BF13" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="BG13" s="204" t="s">
-        <v>271</v>
+      <c r="BG13" s="203" t="s">
+        <v>266</v>
       </c>
       <c r="BH13" s="14">
         <v>15</v>
       </c>
-      <c r="BI13" s="205" t="s">
-        <v>41</v>
-      </c>
-      <c r="BJ13" s="232" t="s">
+      <c r="BI13" s="204" t="s">
+        <v>40</v>
+      </c>
+      <c r="BJ13" s="230" t="s">
         <v>161</v>
       </c>
-      <c r="BK13" s="233" t="s">
-        <v>271</v>
-      </c>
-      <c r="BL13" s="234">
+      <c r="BK13" s="231" t="s">
+        <v>266</v>
+      </c>
+      <c r="BL13" s="232">
         <v>15</v>
       </c>
-      <c r="BM13" s="235" t="s">
-        <v>41</v>
+      <c r="BM13" s="192" t="s">
+        <v>40</v>
       </c>
       <c r="BN13" s="12" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BO13" s="13" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BP13" s="14"/>
-      <c r="BQ13" s="210" t="s">
-        <v>272</v>
+      <c r="BQ13" s="209" t="s">
+        <v>267</v>
       </c>
       <c r="BR13" s="199" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BS13" s="13" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BT13" s="14"/>
       <c r="BU13" s="188" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="BV13" s="199" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BW13" s="13" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BX13" s="14"/>
       <c r="BY13" s="188" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:603" s="46" customFormat="1" ht="38.35" thickBot="1" x14ac:dyDescent="0.45">
@@ -11732,60 +11582,60 @@
         <v>10</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D14" s="55"/>
       <c r="E14" s="56" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H14" s="55"/>
       <c r="I14" s="56" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="K14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L14" s="55"/>
       <c r="M14" s="56" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="N14" s="53" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="O14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="P14" s="55"/>
       <c r="Q14" s="56" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="R14" s="53" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="S14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="T14" s="55"/>
       <c r="U14" s="56" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="V14" s="57" t="s">
         <v>164</v>
       </c>
       <c r="W14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="X14" s="55">
         <v>10</v>
@@ -11797,7 +11647,7 @@
         <v>164</v>
       </c>
       <c r="AA14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AB14" s="55">
         <v>10</v>
@@ -11809,7 +11659,7 @@
         <v>164</v>
       </c>
       <c r="AE14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AF14" s="55">
         <v>10</v>
@@ -11821,7 +11671,7 @@
         <v>164</v>
       </c>
       <c r="AI14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AJ14" s="55">
         <v>10</v>
@@ -11833,7 +11683,7 @@
         <v>164</v>
       </c>
       <c r="AM14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AN14" s="55">
         <v>10</v>
@@ -11845,7 +11695,7 @@
         <v>164</v>
       </c>
       <c r="AQ14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AR14" s="55">
         <v>10</v>
@@ -11854,22 +11704,22 @@
         <v>39</v>
       </c>
       <c r="AT14" s="53" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AU14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AV14" s="55">
         <v>10</v>
       </c>
       <c r="AW14" s="56" t="s">
-        <v>272</v>
+        <v>39</v>
       </c>
       <c r="AX14" s="53" t="s">
         <v>165</v>
       </c>
       <c r="AY14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AZ14" s="55">
         <v>10</v>
@@ -11878,70 +11728,68 @@
         <v>39</v>
       </c>
       <c r="BB14" s="53" t="s">
-        <v>157</v>
+        <v>266</v>
       </c>
       <c r="BC14" s="54" t="s">
-        <v>271</v>
-      </c>
-      <c r="BD14" s="55">
-        <v>5</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="BD14" s="55"/>
       <c r="BE14" s="56" t="s">
-        <v>41</v>
+        <v>267</v>
       </c>
       <c r="BF14" s="53" t="s">
         <v>38</v>
       </c>
       <c r="BG14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BH14" s="55">
         <v>25</v>
       </c>
       <c r="BI14" s="168" t="s">
-        <v>41</v>
-      </c>
-      <c r="BJ14" s="213" t="s">
+        <v>40</v>
+      </c>
+      <c r="BJ14" s="212" t="s">
         <v>38</v>
       </c>
       <c r="BK14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BL14" s="55">
         <v>30</v>
       </c>
-      <c r="BM14" s="214" t="s">
-        <v>272</v>
+      <c r="BM14" s="213" t="s">
+        <v>40</v>
       </c>
       <c r="BN14" s="53" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BO14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BP14" s="55"/>
       <c r="BQ14" s="56" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="BR14" s="57" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BS14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BT14" s="55"/>
-      <c r="BU14" s="215" t="s">
-        <v>272</v>
+      <c r="BU14" s="214" t="s">
+        <v>267</v>
       </c>
       <c r="BV14" s="57" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BW14" s="54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="BX14" s="55"/>
-      <c r="BY14" s="215" t="s">
-        <v>272</v>
+      <c r="BY14" s="214" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:603" s="11" customFormat="1" x14ac:dyDescent="0.4">
@@ -12034,7 +11882,7 @@
       <c r="AY15" s="19"/>
       <c r="AZ15" s="19">
         <f>SUM(AZ5:AZ14)</f>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="BA15" s="20"/>
       <c r="BB15" s="19"/>
@@ -19867,7 +19715,7 @@
       <c r="WE27" s="19"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TBZFpWpTWOMy6YNA8gI2un674ktUlW67QeXysGhqo9ZuiordOcA8vzZz3Zbm0QxhKKwDsYHQSalCyGDFV0+wWA==" saltValue="2BKU1ww9d1MXuCpHhNH9uQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="GegGxFSobJaNpcNThmR3jcEMn1avPH0/lu92LgpFbG/V3ihCpq7eDMHn6OV9KYYVWuVhMLa1nkoV5MraiGtDSA==" saltValue="Xo/z0it/3ENw8HLmwcKpBg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19913,10 +19761,10 @@
       <c r="H3" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="331" t="s">
-        <v>275</v>
-      </c>
-      <c r="J3" s="332"/>
+      <c r="I3" s="337" t="s">
+        <v>270</v>
+      </c>
+      <c r="J3" s="338"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
@@ -19947,7 +19795,7 @@
         <v>49</v>
       </c>
       <c r="J4" s="170" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
@@ -19979,7 +19827,7 @@
         <v>46</v>
       </c>
       <c r="J5" s="170" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
@@ -20005,7 +19853,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="171" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.4">
@@ -20013,7 +19861,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>57</v>
@@ -20025,7 +19873,7 @@
         <v>57</v>
       </c>
       <c r="J7" s="171" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
@@ -20043,12 +19891,12 @@
         <v>60</v>
       </c>
       <c r="J8" s="171" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>61</v>
@@ -20061,7 +19909,7 @@
         <v>62</v>
       </c>
       <c r="J9" s="170" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
@@ -20076,7 +19924,7 @@
         <v>64</v>
       </c>
       <c r="J10" s="170" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.4">
@@ -20090,7 +19938,7 @@
         <v>47</v>
       </c>
       <c r="J11" s="170" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.4">
@@ -20104,7 +19952,7 @@
         <v>56</v>
       </c>
       <c r="J12" s="170" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
@@ -20118,7 +19966,7 @@
         <v>65</v>
       </c>
       <c r="J13" s="170" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.4">
@@ -20132,7 +19980,7 @@
         <v>68</v>
       </c>
       <c r="J14" s="170" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.4">
@@ -20146,7 +19994,7 @@
         <v>66</v>
       </c>
       <c r="J15" s="170" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
@@ -20154,10 +20002,10 @@
         <v>50</v>
       </c>
       <c r="I16" s="172" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="J16" s="173" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
@@ -20165,10 +20013,10 @@
         <v>52</v>
       </c>
       <c r="I17" s="172" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="J17" s="173" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
@@ -20176,10 +20024,10 @@
         <v>64</v>
       </c>
       <c r="I18" s="172" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="J18" s="173" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
@@ -20187,10 +20035,10 @@
         <v>71</v>
       </c>
       <c r="I19" s="172" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="J19" s="173" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
@@ -20211,14 +20059,16 @@
         <v>42</v>
       </c>
       <c r="G20" s="58" t="s">
-        <v>272</v>
-      </c>
-      <c r="H20" s="1"/>
+        <v>267</v>
+      </c>
+      <c r="H20" s="339" t="s">
+        <v>335</v>
+      </c>
       <c r="I20" s="172" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="J20" s="173" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
@@ -20231,21 +20081,23 @@
       <c r="C21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G21" t="s">
-        <v>273</v>
-      </c>
-      <c r="H21" s="1"/>
+        <v>268</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="I21" s="172" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J21" s="173" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
@@ -20258,23 +20110,25 @@
       <c r="C22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>12</v>
+      <c r="D22" s="3" t="s">
+        <v>336</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H22" s="1"/>
+      <c r="H22" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="I22" s="172" t="s">
         <v>67</v>
       </c>
       <c r="J22" s="173" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>11</v>
@@ -20282,78 +20136,76 @@
       <c r="C23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>11</v>
+      <c r="D23" s="3" t="s">
+        <v>337</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H23" s="1"/>
+      <c r="H23" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="I23" s="169" t="s">
         <v>70</v>
       </c>
       <c r="J23" s="170" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B24" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="172" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="J24" s="173" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>59</v>
+        <v>268</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I25" s="172" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="J25" s="173" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="D26" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="D26" s="1"/>
       <c r="I26" s="169" t="s">
         <v>63</v>
       </c>
       <c r="J26" s="170" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="D27" s="1" t="s">
-        <v>273</v>
-      </c>
+      <c r="D27" s="1"/>
       <c r="I27" s="172" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="J27" s="173" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
@@ -20363,10 +20215,10 @@
       <c r="B28" s="58"/>
       <c r="C28" s="58"/>
       <c r="I28" s="172" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="J28" s="173" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
@@ -20379,17 +20231,17 @@
       <c r="C29" s="61" t="s">
         <v>186</v>
       </c>
-      <c r="D29" s="206" t="s">
-        <v>321</v>
+      <c r="D29" s="205" t="s">
+        <v>316</v>
       </c>
       <c r="E29" s="61" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I29" s="169" t="s">
         <v>71</v>
       </c>
       <c r="J29" s="170" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
@@ -20402,8 +20254,8 @@
       <c r="C30" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="207" t="s">
-        <v>323</v>
+      <c r="D30" s="206" t="s">
+        <v>318</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>15</v>
@@ -20412,7 +20264,7 @@
         <v>50</v>
       </c>
       <c r="J30" s="174" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
@@ -20425,19 +20277,19 @@
       <c r="C31" t="s">
         <v>184</v>
       </c>
-      <c r="D31" s="207" t="s">
-        <v>324</v>
+      <c r="D31" s="206" t="s">
+        <v>319</v>
       </c>
       <c r="I31" s="169" t="s">
         <v>52</v>
       </c>
       <c r="J31" s="170" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32" s="8" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>2</v>
@@ -20445,14 +20297,14 @@
       <c r="C32" t="s">
         <v>185</v>
       </c>
-      <c r="D32" s="207" t="s">
-        <v>325</v>
+      <c r="D32" s="206" t="s">
+        <v>320</v>
       </c>
       <c r="I32" s="169" t="s">
         <v>55</v>
       </c>
       <c r="J32" s="170" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.4">
@@ -20460,18 +20312,18 @@
         <v>89</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I33" s="175" t="s">
         <v>58</v>
       </c>
       <c r="J33" s="176" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A34" s="8" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>18</v>
@@ -20656,16 +20508,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="y750j4nL3fLU9NK3huUb6XPRMLt/n+y0wlwXz/JP9+pFGTGXvihGrRlrf3LkCvHeCRvnhnBL6W/Oh6ivEPMLqA==" saltValue="0zrNGggqAvE8CxdXr1JWTQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="MvDF01oprvy2o3aqHpFq4NzRrZOEl4Q7ILsJRnpQT6F6zuJ3G0lJdbWy1F3BUsCTUCdiwPgN2KNoK7JwZ7yJ7g==" saltValue="nGK/2OIXEm3K5JNx6wsJOg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H21:H27">
     <sortCondition ref="H21:H27"/>
   </sortState>
@@ -20674,36 +20526,41 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A21:A23">
-    <cfRule type="expression" priority="12">
+    <cfRule type="expression" priority="13">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:D9">
-    <cfRule type="expression" priority="13">
+    <cfRule type="expression" priority="14">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:G5 E6:G12">
-    <cfRule type="expression" priority="86">
+    <cfRule type="expression" priority="87">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30:I33">
+    <cfRule type="expression" priority="3">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:J5 I6:I8 I9:J13 I15:J21">
+    <cfRule type="expression" priority="4">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23:J29">
+    <cfRule type="expression" priority="5">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J31:J33">
     <cfRule type="expression" priority="2">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:J5 I6:I8 I9:J13 I15:J21">
-    <cfRule type="expression" priority="3">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I23:J29">
-    <cfRule type="expression" priority="4">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J31:J33">
+  <conditionalFormatting sqref="H21:H22">
     <cfRule type="expression" priority="1">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>

--- a/AutosurveillanceTemplates/Q_GRAV.xlsx
+++ b/AutosurveillanceTemplates/Q_GRAV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF4C9D0-9B07-40CD-9BBA-5046A49604E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B5D2E8-495C-4B07-8517-6E24D002562E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20595" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-8205" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Q_GRAV" sheetId="50" r:id="rId1"/>
@@ -62,8 +62,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="348">
   <si>
     <t>Code</t>
   </si>
@@ -2243,12 +2265,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode=";;;"/>
   </numFmts>
-  <fonts count="49" x14ac:knownFonts="1">
+  <fonts count="50" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4157,27 +4186,27 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="340">
+  <cellXfs count="350">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4206,10 +4235,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4233,46 +4262,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4290,28 +4319,28 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4329,37 +4358,43 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4368,115 +4403,121 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="27" fillId="12" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="12" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="26" fillId="12" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="12" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4484,166 +4525,154 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="71" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="26" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="12" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="26" fillId="12" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="26" fillId="13" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="26" fillId="13" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="71" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="27" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="12" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="27" fillId="12" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="27" fillId="13" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="27" fillId="13" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="12" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="27" fillId="12" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="12" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="26" fillId="12" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="27" fillId="12" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="26" fillId="12" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="27" fillId="12" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="91" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4658,29 +4687,29 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="95" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4707,7 +4736,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4716,7 +4745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4728,44 +4757,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="94" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -4793,7 +4822,7 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4805,7 +4834,7 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4814,13 +4843,13 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4844,368 +4873,398 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="30" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="32" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="31" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="33" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="30" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="34" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="30" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="31" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="30" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="31" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="110" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="97" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="25" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="26" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="25" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="25" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="167" fontId="25" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="110" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="11" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="11" borderId="97" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5970,8 +6029,10 @@
     <col min="1" max="2" width="2.703125" style="63" customWidth="1"/>
     <col min="3" max="20" width="11.703125" style="63" customWidth="1"/>
     <col min="21" max="21" width="2.703125" style="63" customWidth="1"/>
-    <col min="22" max="22" width="2.703125" style="233" customWidth="1"/>
-    <col min="23" max="30" width="10.703125" style="233"/>
+    <col min="22" max="22" width="2.703125" style="339" customWidth="1"/>
+    <col min="23" max="28" width="10.703125" style="339"/>
+    <col min="29" max="29" width="10.703125" style="345"/>
+    <col min="30" max="30" width="10.703125" style="233"/>
     <col min="31" max="37" width="10.703125" style="97"/>
     <col min="38" max="16384" width="10.703125" style="63"/>
   </cols>
@@ -6000,63 +6061,63 @@
     </row>
     <row r="2" spans="2:37" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="78"/>
-      <c r="C2" s="292" t="s">
+      <c r="C2" s="286" t="s">
         <v>269</v>
       </c>
-      <c r="D2" s="293"/>
-      <c r="E2" s="293"/>
-      <c r="F2" s="293"/>
-      <c r="G2" s="293"/>
-      <c r="H2" s="293"/>
-      <c r="I2" s="293"/>
-      <c r="J2" s="293"/>
-      <c r="K2" s="293"/>
-      <c r="L2" s="293"/>
-      <c r="M2" s="293"/>
-      <c r="N2" s="293"/>
-      <c r="O2" s="293"/>
-      <c r="P2" s="293"/>
-      <c r="Q2" s="293"/>
-      <c r="R2" s="293"/>
-      <c r="S2" s="293"/>
-      <c r="T2" s="294"/>
+      <c r="D2" s="287"/>
+      <c r="E2" s="287"/>
+      <c r="F2" s="287"/>
+      <c r="G2" s="287"/>
+      <c r="H2" s="287"/>
+      <c r="I2" s="287"/>
+      <c r="J2" s="287"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="287"/>
+      <c r="M2" s="287"/>
+      <c r="N2" s="287"/>
+      <c r="O2" s="287"/>
+      <c r="P2" s="287"/>
+      <c r="Q2" s="287"/>
+      <c r="R2" s="287"/>
+      <c r="S2" s="287"/>
+      <c r="T2" s="288"/>
       <c r="U2" s="80"/>
     </row>
     <row r="3" spans="2:37" s="65" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="79"/>
-      <c r="C3" s="288" t="s">
+      <c r="C3" s="278" t="s">
         <v>219</v>
       </c>
-      <c r="D3" s="289"/>
-      <c r="E3" s="267"/>
-      <c r="F3" s="267"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="274" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="301"/>
+      <c r="F3" s="301"/>
+      <c r="G3" s="301"/>
+      <c r="H3" s="307" t="s">
         <v>215</v>
       </c>
-      <c r="I3" s="275"/>
-      <c r="J3" s="278"/>
-      <c r="K3" s="279"/>
-      <c r="L3" s="279"/>
-      <c r="M3" s="279"/>
-      <c r="N3" s="280"/>
-      <c r="O3" s="289" t="s">
+      <c r="I3" s="308"/>
+      <c r="J3" s="311"/>
+      <c r="K3" s="312"/>
+      <c r="L3" s="312"/>
+      <c r="M3" s="312"/>
+      <c r="N3" s="313"/>
+      <c r="O3" s="252" t="s">
         <v>220</v>
       </c>
-      <c r="P3" s="289"/>
-      <c r="Q3" s="289"/>
-      <c r="R3" s="301"/>
-      <c r="S3" s="301"/>
-      <c r="T3" s="302"/>
+      <c r="P3" s="252"/>
+      <c r="Q3" s="252"/>
+      <c r="R3" s="292"/>
+      <c r="S3" s="292"/>
+      <c r="T3" s="293"/>
       <c r="U3" s="81"/>
-      <c r="V3" s="234"/>
-      <c r="W3" s="234"/>
-      <c r="X3" s="234"/>
-      <c r="Y3" s="234"/>
-      <c r="Z3" s="234"/>
-      <c r="AA3" s="234"/>
-      <c r="AB3" s="234"/>
-      <c r="AC3" s="234"/>
+      <c r="V3" s="340"/>
+      <c r="W3" s="340"/>
+      <c r="X3" s="340"/>
+      <c r="Y3" s="340"/>
+      <c r="Z3" s="340"/>
+      <c r="AA3" s="340"/>
+      <c r="AB3" s="340"/>
+      <c r="AC3" s="346"/>
       <c r="AD3" s="234"/>
       <c r="AE3" s="102"/>
       <c r="AF3" s="102"/>
@@ -6068,39 +6129,39 @@
     </row>
     <row r="4" spans="2:37" s="65" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="79"/>
-      <c r="C4" s="288" t="s">
+      <c r="C4" s="278" t="s">
         <v>216</v>
       </c>
-      <c r="D4" s="289"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="267"/>
-      <c r="H4" s="274" t="s">
+      <c r="D4" s="252"/>
+      <c r="E4" s="301"/>
+      <c r="F4" s="301"/>
+      <c r="G4" s="301"/>
+      <c r="H4" s="307" t="s">
         <v>222</v>
       </c>
-      <c r="I4" s="275"/>
-      <c r="J4" s="278"/>
-      <c r="K4" s="279"/>
-      <c r="L4" s="279"/>
-      <c r="M4" s="279"/>
-      <c r="N4" s="280"/>
-      <c r="O4" s="289" t="s">
+      <c r="I4" s="308"/>
+      <c r="J4" s="311"/>
+      <c r="K4" s="312"/>
+      <c r="L4" s="312"/>
+      <c r="M4" s="312"/>
+      <c r="N4" s="313"/>
+      <c r="O4" s="252" t="s">
         <v>225</v>
       </c>
-      <c r="P4" s="289"/>
-      <c r="Q4" s="289"/>
-      <c r="R4" s="301"/>
-      <c r="S4" s="301"/>
-      <c r="T4" s="302"/>
+      <c r="P4" s="252"/>
+      <c r="Q4" s="252"/>
+      <c r="R4" s="292"/>
+      <c r="S4" s="292"/>
+      <c r="T4" s="293"/>
       <c r="U4" s="81"/>
-      <c r="V4" s="234"/>
-      <c r="W4" s="234"/>
-      <c r="X4" s="234"/>
-      <c r="Y4" s="234"/>
-      <c r="Z4" s="234"/>
-      <c r="AA4" s="234"/>
-      <c r="AB4" s="234"/>
-      <c r="AC4" s="234"/>
+      <c r="V4" s="340"/>
+      <c r="W4" s="340"/>
+      <c r="X4" s="340"/>
+      <c r="Y4" s="340"/>
+      <c r="Z4" s="340"/>
+      <c r="AA4" s="340"/>
+      <c r="AB4" s="340"/>
+      <c r="AC4" s="346"/>
       <c r="AD4" s="234"/>
       <c r="AE4" s="102"/>
       <c r="AF4" s="102"/>
@@ -6112,39 +6173,39 @@
     </row>
     <row r="5" spans="2:37" s="65" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="79"/>
-      <c r="C5" s="288" t="s">
+      <c r="C5" s="278" t="s">
         <v>217</v>
       </c>
-      <c r="D5" s="289"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="274" t="s">
+      <c r="D5" s="252"/>
+      <c r="E5" s="301"/>
+      <c r="F5" s="301"/>
+      <c r="G5" s="301"/>
+      <c r="H5" s="307" t="s">
         <v>223</v>
       </c>
-      <c r="I5" s="275"/>
-      <c r="J5" s="278"/>
-      <c r="K5" s="279"/>
-      <c r="L5" s="279"/>
-      <c r="M5" s="279"/>
-      <c r="N5" s="280"/>
-      <c r="O5" s="289" t="s">
+      <c r="I5" s="308"/>
+      <c r="J5" s="311"/>
+      <c r="K5" s="312"/>
+      <c r="L5" s="312"/>
+      <c r="M5" s="312"/>
+      <c r="N5" s="313"/>
+      <c r="O5" s="252" t="s">
         <v>221</v>
       </c>
-      <c r="P5" s="289"/>
-      <c r="Q5" s="289"/>
-      <c r="R5" s="303"/>
-      <c r="S5" s="303"/>
-      <c r="T5" s="304"/>
+      <c r="P5" s="252"/>
+      <c r="Q5" s="252"/>
+      <c r="R5" s="294"/>
+      <c r="S5" s="294"/>
+      <c r="T5" s="295"/>
       <c r="U5" s="81"/>
-      <c r="V5" s="234"/>
-      <c r="W5" s="234"/>
-      <c r="X5" s="234"/>
-      <c r="Y5" s="234"/>
-      <c r="Z5" s="234"/>
-      <c r="AA5" s="234"/>
-      <c r="AB5" s="234"/>
-      <c r="AC5" s="234"/>
+      <c r="V5" s="340"/>
+      <c r="W5" s="340"/>
+      <c r="X5" s="340"/>
+      <c r="Y5" s="340"/>
+      <c r="Z5" s="340"/>
+      <c r="AA5" s="340"/>
+      <c r="AB5" s="340"/>
+      <c r="AC5" s="346"/>
       <c r="AD5" s="234"/>
       <c r="AE5" s="102"/>
       <c r="AF5" s="102"/>
@@ -6156,42 +6217,42 @@
     </row>
     <row r="6" spans="2:37" s="65" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="79"/>
-      <c r="C6" s="290" t="s">
+      <c r="C6" s="317" t="s">
         <v>218</v>
       </c>
-      <c r="D6" s="291"/>
-      <c r="E6" s="268"/>
-      <c r="F6" s="268"/>
-      <c r="G6" s="268"/>
-      <c r="H6" s="276" t="s">
+      <c r="D6" s="318"/>
+      <c r="E6" s="302"/>
+      <c r="F6" s="302"/>
+      <c r="G6" s="302"/>
+      <c r="H6" s="309" t="s">
         <v>224</v>
       </c>
-      <c r="I6" s="277"/>
-      <c r="J6" s="281">
+      <c r="I6" s="310"/>
+      <c r="J6" s="314" t="str">
         <f>D40</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="282"/>
-      <c r="L6" s="282"/>
-      <c r="M6" s="282"/>
-      <c r="N6" s="283"/>
-      <c r="O6" s="291" t="s">
+        <v>Caisson</v>
+      </c>
+      <c r="K6" s="315"/>
+      <c r="L6" s="315"/>
+      <c r="M6" s="315"/>
+      <c r="N6" s="316"/>
+      <c r="O6" s="318" t="s">
         <v>226</v>
       </c>
-      <c r="P6" s="291"/>
-      <c r="Q6" s="291"/>
-      <c r="R6" s="305"/>
-      <c r="S6" s="305"/>
-      <c r="T6" s="306"/>
+      <c r="P6" s="318"/>
+      <c r="Q6" s="318"/>
+      <c r="R6" s="296"/>
+      <c r="S6" s="296"/>
+      <c r="T6" s="297"/>
       <c r="U6" s="81"/>
-      <c r="V6" s="234"/>
-      <c r="W6" s="234"/>
-      <c r="X6" s="234"/>
-      <c r="Y6" s="234"/>
-      <c r="Z6" s="234"/>
-      <c r="AA6" s="234"/>
-      <c r="AB6" s="234"/>
-      <c r="AC6" s="234"/>
+      <c r="V6" s="340"/>
+      <c r="W6" s="340"/>
+      <c r="X6" s="340"/>
+      <c r="Y6" s="340"/>
+      <c r="Z6" s="340"/>
+      <c r="AA6" s="340"/>
+      <c r="AB6" s="340"/>
+      <c r="AC6" s="346"/>
       <c r="AD6" s="234"/>
       <c r="AE6" s="102"/>
       <c r="AF6" s="102"/>
@@ -6222,14 +6283,14 @@
       <c r="S7" s="66"/>
       <c r="T7" s="66"/>
       <c r="U7" s="72"/>
-      <c r="V7" s="235"/>
-      <c r="W7" s="235"/>
-      <c r="X7" s="235"/>
-      <c r="Y7" s="235"/>
-      <c r="Z7" s="235"/>
-      <c r="AA7" s="235"/>
-      <c r="AB7" s="235"/>
-      <c r="AC7" s="235"/>
+      <c r="V7" s="341"/>
+      <c r="W7" s="341"/>
+      <c r="X7" s="341"/>
+      <c r="Y7" s="341"/>
+      <c r="Z7" s="341"/>
+      <c r="AA7" s="341"/>
+      <c r="AB7" s="341"/>
+      <c r="AC7" s="347"/>
       <c r="AD7" s="235"/>
       <c r="AE7" s="103"/>
       <c r="AF7" s="103"/>
@@ -6262,14 +6323,14 @@
       <c r="S8" s="241"/>
       <c r="T8" s="242"/>
       <c r="U8" s="72"/>
-      <c r="V8" s="235"/>
-      <c r="W8" s="235"/>
-      <c r="X8" s="235"/>
-      <c r="Y8" s="235"/>
-      <c r="Z8" s="235"/>
-      <c r="AA8" s="235"/>
-      <c r="AB8" s="235"/>
-      <c r="AC8" s="235"/>
+      <c r="V8" s="341"/>
+      <c r="W8" s="341"/>
+      <c r="X8" s="341"/>
+      <c r="Y8" s="341"/>
+      <c r="Z8" s="341"/>
+      <c r="AA8" s="341"/>
+      <c r="AB8" s="341"/>
+      <c r="AC8" s="347"/>
       <c r="AD8" s="235"/>
       <c r="AE8" s="103"/>
       <c r="AF8" s="103"/>
@@ -6300,14 +6361,14 @@
       <c r="S9" s="66"/>
       <c r="T9" s="112"/>
       <c r="U9" s="72"/>
-      <c r="V9" s="235"/>
-      <c r="W9" s="235"/>
-      <c r="X9" s="235"/>
-      <c r="Y9" s="235"/>
-      <c r="Z9" s="235"/>
-      <c r="AA9" s="235"/>
-      <c r="AB9" s="235"/>
-      <c r="AC9" s="235"/>
+      <c r="V9" s="341"/>
+      <c r="W9" s="341"/>
+      <c r="X9" s="341"/>
+      <c r="Y9" s="341"/>
+      <c r="Z9" s="341"/>
+      <c r="AA9" s="341"/>
+      <c r="AB9" s="341"/>
+      <c r="AC9" s="347"/>
       <c r="AD9" s="235"/>
       <c r="AE9" s="103"/>
       <c r="AF9" s="103"/>
@@ -6320,172 +6381,172 @@
     <row r="10" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B10" s="73"/>
       <c r="C10" s="113"/>
-      <c r="D10" s="307" t="s">
+      <c r="D10" s="298" t="s">
         <v>206</v>
       </c>
-      <c r="E10" s="308"/>
-      <c r="F10" s="308"/>
-      <c r="G10" s="308"/>
-      <c r="H10" s="308"/>
-      <c r="I10" s="308"/>
-      <c r="J10" s="308"/>
-      <c r="K10" s="308"/>
-      <c r="L10" s="308"/>
-      <c r="M10" s="308"/>
-      <c r="N10" s="308"/>
-      <c r="O10" s="308"/>
-      <c r="P10" s="308"/>
-      <c r="Q10" s="308"/>
-      <c r="R10" s="308"/>
-      <c r="S10" s="309"/>
+      <c r="E10" s="299"/>
+      <c r="F10" s="299"/>
+      <c r="G10" s="299"/>
+      <c r="H10" s="299"/>
+      <c r="I10" s="299"/>
+      <c r="J10" s="299"/>
+      <c r="K10" s="299"/>
+      <c r="L10" s="299"/>
+      <c r="M10" s="299"/>
+      <c r="N10" s="299"/>
+      <c r="O10" s="299"/>
+      <c r="P10" s="299"/>
+      <c r="Q10" s="299"/>
+      <c r="R10" s="299"/>
+      <c r="S10" s="300"/>
       <c r="T10" s="114"/>
       <c r="U10" s="74"/>
     </row>
     <row r="11" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B11" s="73"/>
       <c r="C11" s="115"/>
-      <c r="D11" s="284" t="s">
+      <c r="D11" s="256" t="s">
         <v>227</v>
       </c>
-      <c r="E11" s="285"/>
-      <c r="F11" s="286"/>
-      <c r="G11" s="310"/>
-      <c r="H11" s="311"/>
-      <c r="I11" s="311"/>
-      <c r="J11" s="311"/>
-      <c r="K11" s="312"/>
-      <c r="L11" s="284" t="s">
+      <c r="E11" s="257"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="269"/>
+      <c r="H11" s="270"/>
+      <c r="I11" s="270"/>
+      <c r="J11" s="270"/>
+      <c r="K11" s="271"/>
+      <c r="L11" s="256" t="s">
         <v>190</v>
       </c>
-      <c r="M11" s="285"/>
-      <c r="N11" s="285"/>
-      <c r="O11" s="286"/>
-      <c r="P11" s="296"/>
-      <c r="Q11" s="297"/>
-      <c r="R11" s="297"/>
-      <c r="S11" s="298"/>
+      <c r="M11" s="257"/>
+      <c r="N11" s="257"/>
+      <c r="O11" s="258"/>
+      <c r="P11" s="272"/>
+      <c r="Q11" s="273"/>
+      <c r="R11" s="273"/>
+      <c r="S11" s="274"/>
       <c r="T11" s="116"/>
       <c r="U11" s="74"/>
     </row>
     <row r="12" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B12" s="73"/>
       <c r="C12" s="115"/>
-      <c r="D12" s="284" t="s">
+      <c r="D12" s="256" t="s">
         <v>228</v>
       </c>
-      <c r="E12" s="285"/>
-      <c r="F12" s="286"/>
-      <c r="G12" s="310"/>
-      <c r="H12" s="311"/>
-      <c r="I12" s="311"/>
-      <c r="J12" s="311"/>
-      <c r="K12" s="312"/>
-      <c r="L12" s="284" t="s">
+      <c r="E12" s="257"/>
+      <c r="F12" s="258"/>
+      <c r="G12" s="269"/>
+      <c r="H12" s="270"/>
+      <c r="I12" s="270"/>
+      <c r="J12" s="270"/>
+      <c r="K12" s="271"/>
+      <c r="L12" s="256" t="s">
         <v>237</v>
       </c>
-      <c r="M12" s="285"/>
-      <c r="N12" s="285"/>
-      <c r="O12" s="286"/>
-      <c r="P12" s="296"/>
-      <c r="Q12" s="297"/>
-      <c r="R12" s="297"/>
-      <c r="S12" s="298"/>
+      <c r="M12" s="257"/>
+      <c r="N12" s="257"/>
+      <c r="O12" s="258"/>
+      <c r="P12" s="272"/>
+      <c r="Q12" s="273"/>
+      <c r="R12" s="273"/>
+      <c r="S12" s="274"/>
       <c r="T12" s="116"/>
       <c r="U12" s="74"/>
-      <c r="X12" s="236"/>
-      <c r="Y12" s="236"/>
+      <c r="X12" s="342"/>
+      <c r="Y12" s="342"/>
     </row>
     <row r="13" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B13" s="73"/>
       <c r="C13" s="115"/>
-      <c r="D13" s="284" t="s">
+      <c r="D13" s="256" t="s">
         <v>244</v>
       </c>
-      <c r="E13" s="285"/>
-      <c r="F13" s="286"/>
-      <c r="G13" s="296"/>
-      <c r="H13" s="297"/>
-      <c r="I13" s="297"/>
-      <c r="J13" s="297"/>
-      <c r="K13" s="298"/>
-      <c r="L13" s="287" t="s">
+      <c r="E13" s="257"/>
+      <c r="F13" s="258"/>
+      <c r="G13" s="272"/>
+      <c r="H13" s="273"/>
+      <c r="I13" s="273"/>
+      <c r="J13" s="273"/>
+      <c r="K13" s="274"/>
+      <c r="L13" s="266" t="s">
         <v>229</v>
       </c>
-      <c r="M13" s="287"/>
-      <c r="N13" s="287"/>
-      <c r="O13" s="287"/>
-      <c r="P13" s="273"/>
-      <c r="Q13" s="273"/>
-      <c r="R13" s="273"/>
-      <c r="S13" s="273"/>
+      <c r="M13" s="266"/>
+      <c r="N13" s="266"/>
+      <c r="O13" s="266"/>
+      <c r="P13" s="268"/>
+      <c r="Q13" s="268"/>
+      <c r="R13" s="268"/>
+      <c r="S13" s="268"/>
       <c r="T13" s="116"/>
       <c r="U13" s="74"/>
     </row>
     <row r="14" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B14" s="73"/>
       <c r="C14" s="115"/>
-      <c r="D14" s="284" t="s">
+      <c r="D14" s="256" t="s">
         <v>188</v>
       </c>
-      <c r="E14" s="285"/>
-      <c r="F14" s="286"/>
-      <c r="G14" s="273"/>
-      <c r="H14" s="273"/>
-      <c r="I14" s="273"/>
-      <c r="J14" s="273"/>
-      <c r="K14" s="273"/>
-      <c r="L14" s="287" t="s">
+      <c r="E14" s="257"/>
+      <c r="F14" s="258"/>
+      <c r="G14" s="268"/>
+      <c r="H14" s="268"/>
+      <c r="I14" s="268"/>
+      <c r="J14" s="268"/>
+      <c r="K14" s="268"/>
+      <c r="L14" s="266" t="s">
         <v>230</v>
       </c>
-      <c r="M14" s="287"/>
-      <c r="N14" s="287"/>
-      <c r="O14" s="287"/>
-      <c r="P14" s="273"/>
-      <c r="Q14" s="273"/>
-      <c r="R14" s="273"/>
-      <c r="S14" s="273"/>
+      <c r="M14" s="266"/>
+      <c r="N14" s="266"/>
+      <c r="O14" s="266"/>
+      <c r="P14" s="268"/>
+      <c r="Q14" s="268"/>
+      <c r="R14" s="268"/>
+      <c r="S14" s="268"/>
       <c r="T14" s="116"/>
       <c r="U14" s="74"/>
     </row>
     <row r="15" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B15" s="73"/>
       <c r="C15" s="115"/>
-      <c r="D15" s="284" t="s">
+      <c r="D15" s="256" t="s">
         <v>189</v>
       </c>
-      <c r="E15" s="285"/>
-      <c r="F15" s="286"/>
-      <c r="G15" s="273"/>
-      <c r="H15" s="273"/>
-      <c r="I15" s="273"/>
-      <c r="J15" s="273"/>
-      <c r="K15" s="273"/>
-      <c r="L15" s="287" t="s">
+      <c r="E15" s="257"/>
+      <c r="F15" s="258"/>
+      <c r="G15" s="268"/>
+      <c r="H15" s="268"/>
+      <c r="I15" s="268"/>
+      <c r="J15" s="268"/>
+      <c r="K15" s="268"/>
+      <c r="L15" s="266" t="s">
         <v>238</v>
       </c>
-      <c r="M15" s="287"/>
-      <c r="N15" s="287"/>
-      <c r="O15" s="287"/>
-      <c r="P15" s="269"/>
-      <c r="Q15" s="269"/>
-      <c r="R15" s="269"/>
-      <c r="S15" s="269"/>
+      <c r="M15" s="266"/>
+      <c r="N15" s="266"/>
+      <c r="O15" s="266"/>
+      <c r="P15" s="303"/>
+      <c r="Q15" s="303"/>
+      <c r="R15" s="303"/>
+      <c r="S15" s="303"/>
       <c r="T15" s="116"/>
       <c r="U15" s="74"/>
     </row>
     <row r="16" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B16" s="73"/>
       <c r="C16" s="115"/>
-      <c r="D16" s="284" t="s">
+      <c r="D16" s="256" t="s">
         <v>236</v>
       </c>
-      <c r="E16" s="285"/>
-      <c r="F16" s="286"/>
-      <c r="G16" s="322"/>
-      <c r="H16" s="323"/>
-      <c r="I16" s="323"/>
-      <c r="J16" s="323"/>
-      <c r="K16" s="324"/>
+      <c r="E16" s="257"/>
+      <c r="F16" s="258"/>
+      <c r="G16" s="283"/>
+      <c r="H16" s="284"/>
+      <c r="I16" s="284"/>
+      <c r="J16" s="284"/>
+      <c r="K16" s="285"/>
       <c r="L16" s="127"/>
       <c r="M16" s="127"/>
       <c r="N16" s="127"/>
@@ -6522,126 +6583,126 @@
     <row r="18" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B18" s="73"/>
       <c r="C18" s="115"/>
-      <c r="D18" s="299" t="s">
+      <c r="D18" s="290" t="s">
         <v>242</v>
       </c>
-      <c r="E18" s="299"/>
-      <c r="F18" s="299"/>
-      <c r="G18" s="336"/>
-      <c r="H18" s="336"/>
-      <c r="I18" s="336"/>
-      <c r="J18" s="336"/>
-      <c r="K18" s="336"/>
-      <c r="L18" s="336"/>
-      <c r="M18" s="336"/>
-      <c r="N18" s="336"/>
-      <c r="O18" s="336"/>
-      <c r="P18" s="336"/>
-      <c r="Q18" s="336"/>
-      <c r="R18" s="336"/>
-      <c r="S18" s="336"/>
+      <c r="E18" s="290"/>
+      <c r="F18" s="290"/>
+      <c r="G18" s="267"/>
+      <c r="H18" s="267"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="267"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="267"/>
+      <c r="M18" s="267"/>
+      <c r="N18" s="267"/>
+      <c r="O18" s="267"/>
+      <c r="P18" s="267"/>
+      <c r="Q18" s="267"/>
+      <c r="R18" s="267"/>
+      <c r="S18" s="267"/>
       <c r="T18" s="116"/>
       <c r="U18" s="74"/>
     </row>
     <row r="19" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B19" s="73"/>
       <c r="C19" s="115"/>
-      <c r="D19" s="300" t="s">
+      <c r="D19" s="291" t="s">
         <v>207</v>
       </c>
-      <c r="E19" s="300"/>
-      <c r="F19" s="300"/>
-      <c r="G19" s="300"/>
-      <c r="H19" s="300"/>
-      <c r="I19" s="300"/>
-      <c r="J19" s="300"/>
-      <c r="K19" s="300"/>
-      <c r="L19" s="300"/>
-      <c r="M19" s="300"/>
-      <c r="N19" s="300"/>
-      <c r="O19" s="300"/>
-      <c r="P19" s="300"/>
-      <c r="Q19" s="300"/>
-      <c r="R19" s="300"/>
-      <c r="S19" s="300"/>
+      <c r="E19" s="291"/>
+      <c r="F19" s="291"/>
+      <c r="G19" s="291"/>
+      <c r="H19" s="291"/>
+      <c r="I19" s="291"/>
+      <c r="J19" s="291"/>
+      <c r="K19" s="291"/>
+      <c r="L19" s="291"/>
+      <c r="M19" s="291"/>
+      <c r="N19" s="291"/>
+      <c r="O19" s="291"/>
+      <c r="P19" s="291"/>
+      <c r="Q19" s="291"/>
+      <c r="R19" s="291"/>
+      <c r="S19" s="291"/>
       <c r="T19" s="116"/>
       <c r="U19" s="74"/>
     </row>
     <row r="20" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B20" s="73"/>
       <c r="C20" s="115"/>
-      <c r="D20" s="284" t="s">
+      <c r="D20" s="256" t="s">
         <v>231</v>
       </c>
-      <c r="E20" s="285"/>
-      <c r="F20" s="286"/>
-      <c r="G20" s="296"/>
-      <c r="H20" s="297"/>
-      <c r="I20" s="297"/>
-      <c r="J20" s="297"/>
-      <c r="K20" s="298"/>
-      <c r="L20" s="284" t="s">
+      <c r="E20" s="257"/>
+      <c r="F20" s="258"/>
+      <c r="G20" s="272"/>
+      <c r="H20" s="273"/>
+      <c r="I20" s="273"/>
+      <c r="J20" s="273"/>
+      <c r="K20" s="274"/>
+      <c r="L20" s="256" t="s">
         <v>234</v>
       </c>
-      <c r="M20" s="285"/>
-      <c r="N20" s="285"/>
-      <c r="O20" s="286"/>
-      <c r="P20" s="296"/>
-      <c r="Q20" s="297"/>
-      <c r="R20" s="297"/>
-      <c r="S20" s="298"/>
+      <c r="M20" s="257"/>
+      <c r="N20" s="257"/>
+      <c r="O20" s="258"/>
+      <c r="P20" s="272"/>
+      <c r="Q20" s="273"/>
+      <c r="R20" s="273"/>
+      <c r="S20" s="274"/>
       <c r="T20" s="116"/>
       <c r="U20" s="74"/>
     </row>
     <row r="21" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B21" s="73"/>
       <c r="C21" s="115"/>
-      <c r="D21" s="284" t="s">
+      <c r="D21" s="256" t="s">
         <v>232</v>
       </c>
-      <c r="E21" s="285"/>
-      <c r="F21" s="286"/>
-      <c r="G21" s="296"/>
-      <c r="H21" s="297"/>
-      <c r="I21" s="297"/>
-      <c r="J21" s="297"/>
-      <c r="K21" s="298"/>
-      <c r="L21" s="284" t="s">
+      <c r="E21" s="257"/>
+      <c r="F21" s="258"/>
+      <c r="G21" s="272"/>
+      <c r="H21" s="273"/>
+      <c r="I21" s="273"/>
+      <c r="J21" s="273"/>
+      <c r="K21" s="274"/>
+      <c r="L21" s="256" t="s">
         <v>235</v>
       </c>
-      <c r="M21" s="285"/>
-      <c r="N21" s="285"/>
-      <c r="O21" s="286"/>
-      <c r="P21" s="296"/>
-      <c r="Q21" s="297"/>
-      <c r="R21" s="297"/>
-      <c r="S21" s="298"/>
+      <c r="M21" s="257"/>
+      <c r="N21" s="257"/>
+      <c r="O21" s="258"/>
+      <c r="P21" s="272"/>
+      <c r="Q21" s="273"/>
+      <c r="R21" s="273"/>
+      <c r="S21" s="274"/>
       <c r="T21" s="116"/>
       <c r="U21" s="74"/>
     </row>
     <row r="22" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B22" s="73"/>
       <c r="C22" s="115"/>
-      <c r="D22" s="284" t="s">
+      <c r="D22" s="256" t="s">
         <v>233</v>
       </c>
-      <c r="E22" s="285"/>
-      <c r="F22" s="286"/>
-      <c r="G22" s="296"/>
-      <c r="H22" s="297"/>
-      <c r="I22" s="297"/>
-      <c r="J22" s="297"/>
-      <c r="K22" s="298"/>
-      <c r="L22" s="284" t="s">
+      <c r="E22" s="257"/>
+      <c r="F22" s="258"/>
+      <c r="G22" s="272"/>
+      <c r="H22" s="273"/>
+      <c r="I22" s="273"/>
+      <c r="J22" s="273"/>
+      <c r="K22" s="274"/>
+      <c r="L22" s="256" t="s">
         <v>236</v>
       </c>
-      <c r="M22" s="285"/>
-      <c r="N22" s="285"/>
-      <c r="O22" s="286"/>
-      <c r="P22" s="296"/>
-      <c r="Q22" s="297"/>
-      <c r="R22" s="297"/>
-      <c r="S22" s="298"/>
+      <c r="M22" s="257"/>
+      <c r="N22" s="257"/>
+      <c r="O22" s="258"/>
+      <c r="P22" s="272"/>
+      <c r="Q22" s="273"/>
+      <c r="R22" s="273"/>
+      <c r="S22" s="274"/>
       <c r="T22" s="116"/>
       <c r="U22" s="74"/>
     </row>
@@ -6670,22 +6731,22 @@
     <row r="24" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B24" s="73"/>
       <c r="C24" s="115"/>
-      <c r="D24" s="333" t="s">
+      <c r="D24" s="253" t="s">
         <v>192</v>
       </c>
-      <c r="E24" s="334"/>
-      <c r="F24" s="334"/>
-      <c r="G24" s="334"/>
-      <c r="H24" s="334"/>
-      <c r="I24" s="334"/>
-      <c r="J24" s="334"/>
-      <c r="K24" s="334"/>
-      <c r="L24" s="334"/>
-      <c r="M24" s="334"/>
-      <c r="N24" s="334"/>
-      <c r="O24" s="334"/>
-      <c r="P24" s="334"/>
-      <c r="Q24" s="335"/>
+      <c r="E24" s="254"/>
+      <c r="F24" s="254"/>
+      <c r="G24" s="254"/>
+      <c r="H24" s="254"/>
+      <c r="I24" s="254"/>
+      <c r="J24" s="254"/>
+      <c r="K24" s="254"/>
+      <c r="L24" s="254"/>
+      <c r="M24" s="254"/>
+      <c r="N24" s="254"/>
+      <c r="O24" s="254"/>
+      <c r="P24" s="254"/>
+      <c r="Q24" s="255"/>
       <c r="R24" s="142"/>
       <c r="S24" s="142"/>
       <c r="T24" s="116"/>
@@ -6694,26 +6755,26 @@
     <row r="25" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B25" s="73"/>
       <c r="C25" s="115"/>
-      <c r="D25" s="295" t="s">
+      <c r="D25" s="289" t="s">
         <v>332</v>
       </c>
-      <c r="E25" s="295"/>
-      <c r="F25" s="295"/>
-      <c r="G25" s="295"/>
-      <c r="H25" s="270" t="s">
+      <c r="E25" s="289"/>
+      <c r="F25" s="289"/>
+      <c r="G25" s="289"/>
+      <c r="H25" s="304" t="s">
         <v>193</v>
       </c>
-      <c r="I25" s="271"/>
-      <c r="J25" s="271"/>
-      <c r="K25" s="271"/>
-      <c r="L25" s="271"/>
-      <c r="M25" s="272"/>
-      <c r="N25" s="295" t="s">
+      <c r="I25" s="305"/>
+      <c r="J25" s="305"/>
+      <c r="K25" s="305"/>
+      <c r="L25" s="305"/>
+      <c r="M25" s="306"/>
+      <c r="N25" s="289" t="s">
         <v>194</v>
       </c>
-      <c r="O25" s="295"/>
-      <c r="P25" s="295"/>
-      <c r="Q25" s="295"/>
+      <c r="O25" s="289"/>
+      <c r="P25" s="289"/>
+      <c r="Q25" s="289"/>
       <c r="R25" s="142"/>
       <c r="S25" s="142"/>
       <c r="T25" s="116"/>
@@ -6781,13 +6842,13 @@
       <c r="S26" s="142"/>
       <c r="T26" s="116"/>
       <c r="U26" s="74"/>
-      <c r="W26" s="233" t="s">
+      <c r="W26" s="339" t="s">
         <v>213</v>
       </c>
-      <c r="X26" s="233" t="s">
+      <c r="X26" s="339" t="s">
         <v>214</v>
       </c>
-      <c r="Y26" s="233" t="s">
+      <c r="Y26" s="339" t="s">
         <v>214</v>
       </c>
     </row>
@@ -6833,15 +6894,15 @@
       <c r="S27" s="142"/>
       <c r="T27" s="117"/>
       <c r="U27" s="74"/>
-      <c r="W27" s="233">
+      <c r="W27" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P27),ISNUMBER(E27)),IF(ABS(P27)&gt;E27,1,0),0),IF(AND(ISNUMBER(I27),ISNUMBER(E27)),IF(ABS(I27)&gt;E27,1,0),0))</f>
         <v>0</v>
       </c>
-      <c r="X27" s="233">
+      <c r="X27" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K27),ISNUMBER(G27)),IF(ABS(K27)&gt;G27,1,0),0))</f>
         <v>0</v>
       </c>
-      <c r="Y27" s="233">
+      <c r="Y27" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q27),ISNUMBER(G27)),IF(ABS(Q27)&gt;G27,1,0),0),0)</f>
         <v>0</v>
       </c>
@@ -6888,15 +6949,15 @@
       <c r="S28" s="142"/>
       <c r="T28" s="116"/>
       <c r="U28" s="74"/>
-      <c r="W28" s="233">
+      <c r="W28" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P28),ISNUMBER(E28)),IF(ABS(P28)&gt;E28,1,0),0),IF(AND(ISNUMBER(I28),ISNUMBER(E28)),IF(ABS(I28)&gt;E28,1,0),0))</f>
         <v>0</v>
       </c>
-      <c r="X28" s="233">
+      <c r="X28" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K28),ISNUMBER(G28)),IF(ABS(K28)&gt;G28,1,0),0))</f>
         <v>0</v>
       </c>
-      <c r="Y28" s="233">
+      <c r="Y28" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q28),ISNUMBER(G28)),IF(ABS(Q28)&gt;G28,1,0),0),0)</f>
         <v>0</v>
       </c>
@@ -6943,15 +7004,15 @@
       <c r="S29" s="142"/>
       <c r="T29" s="116"/>
       <c r="U29" s="74"/>
-      <c r="W29" s="233">
+      <c r="W29" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P29),ISNUMBER(E29)),IF(ABS(P29)&gt;E29,1,0),0),IF(AND(ISNUMBER(I29),ISNUMBER(E29)),IF(ABS(I29)&gt;E29,1,0),0))</f>
         <v>0</v>
       </c>
-      <c r="X29" s="233">
+      <c r="X29" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K29),ISNUMBER(G29)),IF(ABS(K29)&gt;G29,1,0),0))</f>
         <v>0</v>
       </c>
-      <c r="Y29" s="233">
+      <c r="Y29" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q29),ISNUMBER(G29)),IF(ABS(Q29)&gt;G29,1,0),0),0)</f>
         <v>0</v>
       </c>
@@ -6998,15 +7059,15 @@
       <c r="S30" s="142"/>
       <c r="T30" s="116"/>
       <c r="U30" s="74"/>
-      <c r="W30" s="233">
+      <c r="W30" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(P30),ISNUMBER(E30)),IF(ABS(P30)&gt;E30,1,0),0),IF(AND(ISNUMBER(I30),ISNUMBER(E30)),IF(ABS(I30)&gt;E30,1,0),0))</f>
         <v>0</v>
       </c>
-      <c r="X30" s="233">
+      <c r="X30" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",0,IF(AND(ISNUMBER(K30),ISNUMBER(G30)),IF(ABS(K30)&gt;G30,1,0),0))</f>
         <v>0</v>
       </c>
-      <c r="Y30" s="233">
+      <c r="Y30" s="339">
         <f>IF($G$18="Mesure comparative en parallèle",IF(AND(ISNUMBER(Q30),ISNUMBER(G30)),IF(ABS(Q30)&gt;G30,1,0),0),0)</f>
         <v>0</v>
       </c>
@@ -7032,15 +7093,15 @@
       <c r="S31" s="142"/>
       <c r="T31" s="116"/>
       <c r="U31" s="74"/>
-      <c r="W31" s="233" t="str">
+      <c r="W31" s="339" t="str">
         <f>IF(IF($G$18="Mesure comparative en parallèle",COUNT(P27:P30),COUNT(I27:I30))&gt;0,IF(SUM(W27:W30)&gt;0,"Non validé","Validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="X31" s="233" t="str">
+      <c r="X31" s="339" t="str">
         <f>IF($G$18="Mesure comparative en parallèle","-",IF(SUMPRODUCT(ISNUMBER(K27:K30)*ISNUMBER(G27:G30))&gt;0,IF(SUM(X27:X30)&gt;0,"Non validé","Validé"),"Non contrôlé"))</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="Y31" s="233" t="str">
+      <c r="Y31" s="339" t="str">
         <f>IF($G$18="Mesure comparative en parallèle",IF(SUMPRODUCT(ISNUMBER(Q27:Q30)*ISNUMBER(G27:G30))&gt;0,IF(SUM(Y27:Y30)&gt;0,"Non validé","Validé"),"Non contrôlé"),"-")</f>
         <v>-</v>
       </c>
@@ -7070,7 +7131,7 @@
       <c r="S32" s="142"/>
       <c r="T32" s="116"/>
       <c r="U32" s="74"/>
-      <c r="X32" s="233" t="str">
+      <c r="X32" s="339" t="str">
         <f>IF($G$18="Mesure comparative en parallèle",Y31,X31)</f>
         <v>Non contrôlé</v>
       </c>
@@ -7078,45 +7139,45 @@
     <row r="33" spans="2:37" s="85" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B33" s="83"/>
       <c r="C33" s="118"/>
-      <c r="D33" s="320" t="s">
+      <c r="D33" s="264" t="s">
         <v>211</v>
       </c>
-      <c r="E33" s="321"/>
+      <c r="E33" s="265"/>
       <c r="F33" s="134" t="s">
         <v>191</v>
       </c>
-      <c r="G33" s="320" t="s">
+      <c r="G33" s="264" t="s">
         <v>193</v>
       </c>
-      <c r="H33" s="321"/>
-      <c r="I33" s="320" t="s">
+      <c r="H33" s="265"/>
+      <c r="I33" s="264" t="s">
         <v>212</v>
       </c>
-      <c r="J33" s="321"/>
-      <c r="K33" s="317" t="s">
+      <c r="J33" s="265"/>
+      <c r="K33" s="261" t="s">
         <v>201</v>
       </c>
-      <c r="L33" s="318"/>
-      <c r="M33" s="319"/>
-      <c r="N33" s="317" t="s">
+      <c r="L33" s="262"/>
+      <c r="M33" s="263"/>
+      <c r="N33" s="261" t="s">
         <v>202</v>
       </c>
-      <c r="O33" s="318"/>
-      <c r="P33" s="319"/>
+      <c r="O33" s="262"/>
+      <c r="P33" s="263"/>
       <c r="Q33" s="96"/>
       <c r="R33" s="142"/>
       <c r="S33" s="143"/>
       <c r="T33" s="119"/>
       <c r="U33" s="84"/>
-      <c r="V33" s="237"/>
-      <c r="W33" s="237"/>
-      <c r="X33" s="237"/>
-      <c r="Y33" s="237"/>
-      <c r="Z33" s="233"/>
-      <c r="AA33" s="237"/>
-      <c r="AB33" s="237"/>
-      <c r="AC33" s="237"/>
-      <c r="AD33" s="237"/>
+      <c r="V33" s="343"/>
+      <c r="W33" s="343"/>
+      <c r="X33" s="343"/>
+      <c r="Y33" s="343"/>
+      <c r="Z33" s="339"/>
+      <c r="AA33" s="343"/>
+      <c r="AB33" s="343"/>
+      <c r="AC33" s="348"/>
+      <c r="AD33" s="236"/>
       <c r="AE33" s="104"/>
       <c r="AF33" s="104"/>
       <c r="AG33" s="104"/>
@@ -7143,10 +7204,10 @@
       <c r="H34" s="108" t="s">
         <v>251</v>
       </c>
-      <c r="I34" s="315" t="s">
+      <c r="I34" s="281" t="s">
         <v>246</v>
       </c>
-      <c r="J34" s="316"/>
+      <c r="J34" s="282"/>
       <c r="K34" s="90" t="s">
         <v>196</v>
       </c>
@@ -7170,15 +7231,15 @@
       <c r="S34" s="144"/>
       <c r="T34" s="121"/>
       <c r="U34" s="87"/>
-      <c r="V34" s="238"/>
-      <c r="W34" s="238"/>
-      <c r="X34" s="238"/>
-      <c r="Y34" s="238"/>
-      <c r="Z34" s="238"/>
-      <c r="AA34" s="238"/>
-      <c r="AB34" s="238"/>
-      <c r="AC34" s="238"/>
-      <c r="AD34" s="238"/>
+      <c r="V34" s="344"/>
+      <c r="W34" s="344"/>
+      <c r="X34" s="344"/>
+      <c r="Y34" s="344"/>
+      <c r="Z34" s="344"/>
+      <c r="AA34" s="344"/>
+      <c r="AB34" s="344"/>
+      <c r="AC34" s="349"/>
+      <c r="AD34" s="237"/>
       <c r="AE34" s="105"/>
       <c r="AF34" s="105"/>
       <c r="AG34" s="105"/>
@@ -7198,8 +7259,8 @@
       </c>
       <c r="G35" s="157"/>
       <c r="H35" s="158"/>
-      <c r="I35" s="313"/>
-      <c r="J35" s="314"/>
+      <c r="I35" s="279"/>
+      <c r="J35" s="280"/>
       <c r="K35" s="94" t="str">
         <f>IF(AND(E35&lt;&gt;"",G35&lt;&gt;"",G18&lt;&gt;"Mesure comparative en parallèle"),(E35+G35)/2,IF(AND(I35&lt;&gt;"",G35&lt;&gt;"",G18="Mesure comparative en parallèle"),(I35+G35)/2,""))</f>
         <v/>
@@ -7229,11 +7290,11 @@
       <c r="S35" s="145"/>
       <c r="T35" s="116"/>
       <c r="U35" s="74"/>
-      <c r="W35" s="233">
+      <c r="W35" s="339">
         <f>IF(M35&lt;&gt;"", IF(ABS(M35)&gt;F35,1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="X35" s="233">
+      <c r="X35" s="339">
         <f>IF(P35&lt;&gt;"", IF(ABS(P35)&gt;F35,1,0),0)</f>
         <v>0</v>
       </c>
@@ -7259,7 +7320,7 @@
       <c r="S36" s="123"/>
       <c r="T36" s="124"/>
       <c r="U36" s="74"/>
-      <c r="W36" s="233" t="str">
+      <c r="W36" s="339" t="str">
         <f>IFERROR(IF((K35+N35)&gt;0,IF((W35+X35)&gt;0,"Non validé","Validé"),"Non contrôlé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
@@ -7335,51 +7396,53 @@
     <row r="40" spans="2:37" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B40" s="73"/>
       <c r="C40" s="115"/>
-      <c r="D40" s="250"/>
-      <c r="E40" s="250"/>
-      <c r="F40" s="250"/>
-      <c r="G40" s="250"/>
-      <c r="H40" s="250"/>
-      <c r="I40" s="250"/>
-      <c r="J40" s="250"/>
-      <c r="K40" s="250"/>
-      <c r="L40" s="250"/>
-      <c r="M40" s="250"/>
-      <c r="N40" s="250"/>
-      <c r="O40" s="250"/>
-      <c r="P40" s="250"/>
-      <c r="Q40" s="250"/>
-      <c r="R40" s="250"/>
-      <c r="S40" s="250"/>
+      <c r="D40" s="325" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="325"/>
+      <c r="F40" s="325"/>
+      <c r="G40" s="325"/>
+      <c r="H40" s="325"/>
+      <c r="I40" s="325"/>
+      <c r="J40" s="325"/>
+      <c r="K40" s="325"/>
+      <c r="L40" s="325"/>
+      <c r="M40" s="325"/>
+      <c r="N40" s="325"/>
+      <c r="O40" s="325"/>
+      <c r="P40" s="325"/>
+      <c r="Q40" s="325"/>
+      <c r="R40" s="325"/>
+      <c r="S40" s="325"/>
       <c r="T40" s="116"/>
       <c r="U40" s="74"/>
-      <c r="W40" s="233" t="s">
+      <c r="W40" s="339" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="41" spans="2:37" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B41" s="73"/>
       <c r="C41" s="115"/>
-      <c r="D41" s="251" t="s">
+      <c r="D41" s="326" t="s">
         <v>4</v>
       </c>
-      <c r="E41" s="251"/>
-      <c r="F41" s="251"/>
-      <c r="G41" s="251"/>
-      <c r="H41" s="251"/>
-      <c r="I41" s="251"/>
-      <c r="J41" s="251"/>
-      <c r="K41" s="251" t="s">
+      <c r="E41" s="326"/>
+      <c r="F41" s="326"/>
+      <c r="G41" s="326"/>
+      <c r="H41" s="326"/>
+      <c r="I41" s="326"/>
+      <c r="J41" s="326"/>
+      <c r="K41" s="326" t="s">
         <v>170</v>
       </c>
-      <c r="L41" s="251"/>
-      <c r="M41" s="251"/>
-      <c r="N41" s="251"/>
-      <c r="O41" s="251"/>
-      <c r="P41" s="251" t="s">
+      <c r="L41" s="326"/>
+      <c r="M41" s="326"/>
+      <c r="N41" s="326"/>
+      <c r="O41" s="326"/>
+      <c r="P41" s="326" t="s">
         <v>75</v>
       </c>
-      <c r="Q41" s="251"/>
+      <c r="Q41" s="326"/>
       <c r="R41" s="110" t="s">
         <v>183</v>
       </c>
@@ -7395,38 +7458,38 @@
       <c r="D42" s="109">
         <v>1</v>
       </c>
-      <c r="E42" s="264" t="str">
+      <c r="E42" s="275" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D42+2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="265"/>
-      <c r="G42" s="265"/>
-      <c r="H42" s="265"/>
-      <c r="I42" s="265"/>
-      <c r="J42" s="266"/>
-      <c r="K42" s="264" t="str">
+        <v>L'accès à l'ouvrage et aux équipements de mesure se fait-il en toute sécurité pour les agents en charge des opérations de contrôles et d'entretien ?</v>
+      </c>
+      <c r="F42" s="276"/>
+      <c r="G42" s="276"/>
+      <c r="H42" s="276"/>
+      <c r="I42" s="276"/>
+      <c r="J42" s="277"/>
+      <c r="K42" s="275" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D42+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D42+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="L42" s="265"/>
-      <c r="M42" s="265"/>
-      <c r="N42" s="265"/>
-      <c r="O42" s="266"/>
-      <c r="P42" s="262"/>
-      <c r="Q42" s="263"/>
+        <v>En cas d'accès nécessitant des équipements de protection individuels renforcés (ARI par exemple) ou d'intervenir à 2 personnes, retenir "Validé avec réserve"</v>
+      </c>
+      <c r="L42" s="276"/>
+      <c r="M42" s="276"/>
+      <c r="N42" s="276"/>
+      <c r="O42" s="277"/>
+      <c r="P42" s="259"/>
+      <c r="Q42" s="260"/>
       <c r="R42" s="93">
         <f>IF(OR(P42="Validé",P42="Réserve",P42="Oui",P42="Entre 5 et 10%"),S42,0)</f>
         <v>0</v>
       </c>
-      <c r="S42" s="93" t="str">
+      <c r="S42" s="93">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D42+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T42" s="116"/>
       <c r="U42" s="74"/>
-      <c r="W42" s="233" t="str">
-        <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D42+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
-        <v/>
+      <c r="W42" s="339" t="str" cm="1">
+        <f t="array" ref="W42">IFERROR(INDEX(Critères!$B$3:$BZ$16, D42+2, MATCH($D$40, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="43" spans="2:37" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7435,38 +7498,38 @@
       <c r="D43" s="109">
         <v>2</v>
       </c>
-      <c r="E43" s="264" t="str">
+      <c r="E43" s="275" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D43+2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="265"/>
-      <c r="G43" s="265"/>
-      <c r="H43" s="265"/>
-      <c r="I43" s="265"/>
-      <c r="J43" s="266"/>
-      <c r="K43" s="264" t="str">
+        <v>Le dimensionnement du caisson et notamment son échancrure de mesure est-elle adaptée vis-à-vis de l'étendue des débits à mesurer ?</v>
+      </c>
+      <c r="F43" s="276"/>
+      <c r="G43" s="276"/>
+      <c r="H43" s="276"/>
+      <c r="I43" s="276"/>
+      <c r="J43" s="277"/>
+      <c r="K43" s="275" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D43+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D43+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="L43" s="265"/>
-      <c r="M43" s="265"/>
-      <c r="N43" s="265"/>
-      <c r="O43" s="266"/>
-      <c r="P43" s="262"/>
-      <c r="Q43" s="263"/>
+        <v>-</v>
+      </c>
+      <c r="L43" s="276"/>
+      <c r="M43" s="276"/>
+      <c r="N43" s="276"/>
+      <c r="O43" s="277"/>
+      <c r="P43" s="259"/>
+      <c r="Q43" s="260"/>
       <c r="R43" s="93">
         <f t="shared" ref="R43:R51" si="3">IF(OR(P43="Validé",P43="Réserve",P43="Oui",P43="Entre 5 et 10%"),S43,0)</f>
         <v>0</v>
       </c>
-      <c r="S43" s="93" t="str">
+      <c r="S43" s="93">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D43+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T43" s="116"/>
       <c r="U43" s="74"/>
-      <c r="W43" s="233" t="str">
-        <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D43+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
-        <v/>
+      <c r="W43" s="339" t="str" cm="1">
+        <f t="array" ref="W43">IFERROR(INDEX(Critères!$B$3:$BZ$16, D43+2, MATCH($D$40, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="44" spans="2:37" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7475,38 +7538,39 @@
       <c r="D44" s="109">
         <v>3</v>
       </c>
-      <c r="E44" s="264" t="str">
+      <c r="E44" s="275" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D44+2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="265"/>
-      <c r="G44" s="265"/>
-      <c r="H44" s="265"/>
-      <c r="I44" s="265"/>
-      <c r="J44" s="266"/>
-      <c r="K44" s="264" t="str">
+        <v>Le caisson et les capteurs associés, sont-ils installés conformément aux prescriptions en vigueur ?
+Le caisson est-il exempt de déformation ayant un impact significatif sur la mesure de débit ?</v>
+      </c>
+      <c r="F44" s="276"/>
+      <c r="G44" s="276"/>
+      <c r="H44" s="276"/>
+      <c r="I44" s="276"/>
+      <c r="J44" s="277"/>
+      <c r="K44" s="275" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D44+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D44+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="L44" s="265"/>
-      <c r="M44" s="265"/>
-      <c r="N44" s="265"/>
-      <c r="O44" s="266"/>
-      <c r="P44" s="262"/>
-      <c r="Q44" s="263"/>
+        <v>-</v>
+      </c>
+      <c r="L44" s="276"/>
+      <c r="M44" s="276"/>
+      <c r="N44" s="276"/>
+      <c r="O44" s="277"/>
+      <c r="P44" s="259"/>
+      <c r="Q44" s="260"/>
       <c r="R44" s="93">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S44" s="93" t="str">
+      <c r="S44" s="93">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D44+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T44" s="116"/>
       <c r="U44" s="74"/>
-      <c r="W44" s="233" t="str">
-        <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D44+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
-        <v/>
+      <c r="W44" s="339" t="str" cm="1">
+        <f t="array" ref="W44">IFERROR(INDEX(Critères!$B$3:$BZ$16, D44+2, MATCH($D$40, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="45" spans="2:37" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7515,38 +7579,39 @@
       <c r="D45" s="109">
         <v>4</v>
       </c>
-      <c r="E45" s="264" t="str">
+      <c r="E45" s="275" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D45+2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="265"/>
-      <c r="G45" s="265"/>
-      <c r="H45" s="265"/>
-      <c r="I45" s="265"/>
-      <c r="J45" s="266"/>
-      <c r="K45" s="264" t="str">
+        <v>L'étanchéité, la propreté et l'état d'entretien du caisson et des capteurs associés sont-ils satisfaisants ?</v>
+      </c>
+      <c r="F45" s="276"/>
+      <c r="G45" s="276"/>
+      <c r="H45" s="276"/>
+      <c r="I45" s="276"/>
+      <c r="J45" s="277"/>
+      <c r="K45" s="275" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D45+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D45+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="L45" s="265"/>
-      <c r="M45" s="265"/>
-      <c r="N45" s="265"/>
-      <c r="O45" s="266"/>
-      <c r="P45" s="262"/>
-      <c r="Q45" s="263"/>
+        <v>Un défaut de propreté et/ou d'entretien ayant un impact immédiat sur la fiabilité de la mesure doit entrainer un jugement à "Non Validé".
+Un défaut de propreté et/ou d'entretien mais n'ayant à priori pas d'impact immédiat sur la fiabilité de la mesure doit avoir un jugement "Validé avec réserve".</v>
+      </c>
+      <c r="L45" s="276"/>
+      <c r="M45" s="276"/>
+      <c r="N45" s="276"/>
+      <c r="O45" s="277"/>
+      <c r="P45" s="259"/>
+      <c r="Q45" s="260"/>
       <c r="R45" s="93">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S45" s="93" t="str">
+      <c r="S45" s="93">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D45+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T45" s="116"/>
       <c r="U45" s="74"/>
-      <c r="W45" s="233" t="str">
-        <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D45+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
-        <v/>
+      <c r="W45" s="339" t="str" cm="1">
+        <f t="array" ref="W45">IFERROR(INDEX(Critères!$B$3:$BZ$16, D45+2, MATCH($D$40, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="46" spans="2:37" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7555,38 +7620,40 @@
       <c r="D46" s="109">
         <v>5</v>
       </c>
-      <c r="E46" s="264" t="str">
+      <c r="E46" s="275" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D46+2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="265"/>
-      <c r="G46" s="265"/>
-      <c r="H46" s="265"/>
-      <c r="I46" s="265"/>
-      <c r="J46" s="266"/>
-      <c r="K46" s="264" t="str">
+        <v xml:space="preserve">Le fonctionnement hydraulique de l'organe de mesure, en amont et en aval, est-il satisfaisant ? </v>
+      </c>
+      <c r="F46" s="276"/>
+      <c r="G46" s="276"/>
+      <c r="H46" s="276"/>
+      <c r="I46" s="276"/>
+      <c r="J46" s="277"/>
+      <c r="K46" s="275" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="L46" s="265"/>
-      <c r="M46" s="265"/>
-      <c r="N46" s="265"/>
-      <c r="O46" s="266"/>
-      <c r="P46" s="262"/>
-      <c r="Q46" s="263"/>
+        <v>Une attention particulière devra être apportée en cas de modification significative des débits, de l'ajout d'un clapet ou d'un filet à l'exutoire, etc...).
+Les traces de mises en charges peuvent être un indice pour évaluer ce critère.
+En l'absence d'écoulement saisir "Non contrôlé".  Cette question n'est pas rédhibitoire et il n'est pas demandé de faire une seconde visite, avec écoulement, pour y répondre</v>
+      </c>
+      <c r="L46" s="276"/>
+      <c r="M46" s="276"/>
+      <c r="N46" s="276"/>
+      <c r="O46" s="277"/>
+      <c r="P46" s="259"/>
+      <c r="Q46" s="260"/>
       <c r="R46" s="93">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S46" s="93" t="str">
+      <c r="S46" s="93">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D46+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T46" s="116"/>
       <c r="U46" s="74"/>
-      <c r="W46" s="233" t="str">
-        <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D46+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
-        <v/>
+      <c r="W46" s="339" t="str" cm="1">
+        <f t="array" ref="W46">IFERROR(INDEX(Critères!$B$3:$BZ$16, D46+2, MATCH($D$40, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="47" spans="2:37" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7595,38 +7662,38 @@
       <c r="D47" s="109">
         <v>6</v>
       </c>
-      <c r="E47" s="264" t="str">
+      <c r="E47" s="275" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D47+2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="265"/>
-      <c r="G47" s="265"/>
-      <c r="H47" s="265"/>
-      <c r="I47" s="265"/>
-      <c r="J47" s="266"/>
-      <c r="K47" s="264" t="str">
+        <v>Le capteur de mesure de hauteur d'eau est-il adapté au type d'effluent et à l'environnement rencontrés (mousses, températures, déchets, etc...) et présente t-il un état de fonctionnement satisfaisant ?</v>
+      </c>
+      <c r="F47" s="276"/>
+      <c r="G47" s="276"/>
+      <c r="H47" s="276"/>
+      <c r="I47" s="276"/>
+      <c r="J47" s="277"/>
+      <c r="K47" s="275" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="L47" s="265"/>
-      <c r="M47" s="265"/>
-      <c r="N47" s="265"/>
-      <c r="O47" s="266"/>
-      <c r="P47" s="262"/>
-      <c r="Q47" s="263"/>
+        <v>-</v>
+      </c>
+      <c r="L47" s="276"/>
+      <c r="M47" s="276"/>
+      <c r="N47" s="276"/>
+      <c r="O47" s="277"/>
+      <c r="P47" s="259"/>
+      <c r="Q47" s="260"/>
       <c r="R47" s="93">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S47" s="93" t="str">
+      <c r="S47" s="93">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D47+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T47" s="116"/>
       <c r="U47" s="74"/>
-      <c r="W47" s="233" t="str">
-        <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D47+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
-        <v/>
+      <c r="W47" s="339" t="str" cm="1">
+        <f t="array" ref="W47">IFERROR(INDEX(Critères!$B$3:$BZ$16, D47+2, MATCH($D$40, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="48" spans="2:37" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7635,41 +7702,41 @@
       <c r="D48" s="109">
         <v>7</v>
       </c>
-      <c r="E48" s="264" t="str">
+      <c r="E48" s="275" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D48+2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="265"/>
-      <c r="G48" s="265"/>
-      <c r="H48" s="265"/>
-      <c r="I48" s="265"/>
-      <c r="J48" s="266"/>
-      <c r="K48" s="264" t="str">
+        <v>Les écarts entre d'une part les résultats de mesure des hauteurs d'eau obtenus à partir des dispositifs en place (si possible sur 3 points représentatifs du fonctionnement habituel, plus le 0 hydraulique) et ceux mesurés par l'organisme de contrôle d'autre part, sont-ils cohérents (EMT ± 10 mm) ?</v>
+      </c>
+      <c r="F48" s="276"/>
+      <c r="G48" s="276"/>
+      <c r="H48" s="276"/>
+      <c r="I48" s="276"/>
+      <c r="J48" s="277"/>
+      <c r="K48" s="275" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="L48" s="265"/>
-      <c r="M48" s="265"/>
-      <c r="N48" s="265"/>
-      <c r="O48" s="266"/>
-      <c r="P48" s="262" t="str">
+        <v>-</v>
+      </c>
+      <c r="L48" s="276"/>
+      <c r="M48" s="276"/>
+      <c r="N48" s="276"/>
+      <c r="O48" s="277"/>
+      <c r="P48" s="259" t="str">
         <f>IF(E48="-","Non applicable",IF(D40="Détecteur de surverse","Non contrôlé",W31))</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="Q48" s="263"/>
+      <c r="Q48" s="260"/>
       <c r="R48" s="93">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S48" s="93" t="str">
+      <c r="S48" s="93">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D48+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T48" s="116"/>
       <c r="U48" s="74"/>
-      <c r="W48" s="233" t="str">
-        <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D48+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
-        <v/>
+      <c r="W48" s="339" t="str" cm="1">
+        <f t="array" ref="W48">IFERROR(INDEX(Critères!$B$3:$BZ$16, D48+2, MATCH($D$40, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="49" spans="2:23" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7678,41 +7745,45 @@
       <c r="D49" s="109">
         <v>8</v>
       </c>
-      <c r="E49" s="264" t="str">
+      <c r="E49" s="275" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D49+2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="265"/>
-      <c r="G49" s="265"/>
-      <c r="H49" s="265"/>
-      <c r="I49" s="265"/>
-      <c r="J49" s="266"/>
-      <c r="K49" s="264" t="str">
+        <v>La loi hydraulique utilisée Q=f(h), est-elle correctement paramétrée et cohérente avec les caractéristiques de l'organe de mesure ?
+Les écarts entre d'une part les résultats de mesure des débits obtenus à partir des dispositifs en place (si possible sur 3 points représentatifs du fonctionnement habituel ≥ 50 mm) et ceux mesurés par l'organisme de contrôle d'autre part (sur la base de la loi hydraulique fournie par le constructeur), sont-ils cohérents ?
+     EMT ± 10% pour une hauteur d'eau comprise entre 50 et 150 mm
+     EMT ± 5% pour une hauteur ≥ 150 mm</v>
+      </c>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
+      <c r="J49" s="277"/>
+      <c r="K49" s="275" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D49+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D49+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="L49" s="265"/>
-      <c r="M49" s="265"/>
-      <c r="N49" s="265"/>
-      <c r="O49" s="266"/>
-      <c r="P49" s="262" t="str">
+        <v>Le contrôle consiste à vérifier le paramétrage exact de la loi telle que décrite dans la norme, ou pour les autres cas, celle indiquée dans le manuel d'autosurveillance.
+Le nombre de points paramétrés de la courbe de conversion doit également être cohérent avec la gamme des valeurs mesurées.</v>
+      </c>
+      <c r="L49" s="276"/>
+      <c r="M49" s="276"/>
+      <c r="N49" s="276"/>
+      <c r="O49" s="277"/>
+      <c r="P49" s="259" t="str">
         <f>IF(E49="-","Non applicable",IF(D40="Détecteur de surverse","Non contrôlé",X32))</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="Q49" s="263"/>
+      <c r="Q49" s="260"/>
       <c r="R49" s="93">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S49" s="93" t="str">
+      <c r="S49" s="93">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D49+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T49" s="116"/>
       <c r="U49" s="74"/>
-      <c r="W49" s="233" t="str">
-        <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D49+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
-        <v/>
+      <c r="W49" s="339" t="str" cm="1">
+        <f t="array" ref="W49">IFERROR(INDEX(Critères!$B$3:$BZ$16, D49+2, MATCH($D$40, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="50" spans="2:23" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7721,41 +7792,44 @@
       <c r="D50" s="109">
         <v>9</v>
       </c>
-      <c r="E50" s="264" t="str">
+      <c r="E50" s="275" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D50+2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="265"/>
-      <c r="G50" s="265"/>
-      <c r="H50" s="265"/>
-      <c r="I50" s="265"/>
-      <c r="J50" s="266"/>
-      <c r="K50" s="264" t="str">
+        <v>Les écarts entre d'une part les résultats de mesure des volumes obtenus à partir des dispositifs en place (y compris le report en supervision) et ceux mesurés par l'organisme de contrôle d'autre part, sont-ils cohérents ?  
+     EMT ± 10% pour un volume &lt; 50 m3
+     EMT ± 5% pour un volume ≥ 50 m3</v>
+      </c>
+      <c r="F50" s="276"/>
+      <c r="G50" s="276"/>
+      <c r="H50" s="276"/>
+      <c r="I50" s="276"/>
+      <c r="J50" s="277"/>
+      <c r="K50" s="275" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D50+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D50+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="L50" s="265"/>
-      <c r="M50" s="265"/>
-      <c r="N50" s="265"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="262" t="str">
+        <v>Calcul de l'écart par rapport à la moyenne des 2 valeurs.
+Pour les volumes &lt; 10 m3, le fonctionnement sera apprécié par l'intervenant.</v>
+      </c>
+      <c r="L50" s="276"/>
+      <c r="M50" s="276"/>
+      <c r="N50" s="276"/>
+      <c r="O50" s="277"/>
+      <c r="P50" s="259" t="str">
         <f>IF(E50="-","Non applicable",IF(OR(D40=Critères!AX3,D40=Critères!BB3),"Non contrôlé",W36))</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="Q50" s="263"/>
+      <c r="Q50" s="260"/>
       <c r="R50" s="93">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S50" s="93" t="str">
+      <c r="S50" s="93">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D50+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T50" s="116"/>
       <c r="U50" s="74"/>
-      <c r="W50" s="233" t="str">
-        <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D50+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
-        <v/>
+      <c r="W50" s="339" t="str" cm="1">
+        <f t="array" ref="W50">IFERROR(INDEX(Critères!$B$3:$BZ$16, D50+2, MATCH($D$40, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="51" spans="2:23" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -7764,91 +7838,91 @@
       <c r="D51" s="109">
         <v>10</v>
       </c>
-      <c r="E51" s="264" t="str">
+      <c r="E51" s="275" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BY$16,D51+2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="265"/>
-      <c r="G51" s="265"/>
-      <c r="H51" s="265"/>
-      <c r="I51" s="265"/>
-      <c r="J51" s="266"/>
-      <c r="K51" s="264" t="str">
+        <v>Existe t-il un dispositif de contrôle adapté et un afficheur de proximité (Hauteur + Débit + Volume) ?</v>
+      </c>
+      <c r="F51" s="276"/>
+      <c r="G51" s="276"/>
+      <c r="H51" s="276"/>
+      <c r="I51" s="276"/>
+      <c r="J51" s="277"/>
+      <c r="K51" s="275" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BY$16, D51+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BY$16, D51+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 1)), "")</f>
-        <v/>
-      </c>
-      <c r="L51" s="265"/>
-      <c r="M51" s="265"/>
-      <c r="N51" s="265"/>
-      <c r="O51" s="266"/>
-      <c r="P51" s="262"/>
-      <c r="Q51" s="263"/>
+        <v>-</v>
+      </c>
+      <c r="L51" s="276"/>
+      <c r="M51" s="276"/>
+      <c r="N51" s="276"/>
+      <c r="O51" s="277"/>
+      <c r="P51" s="259"/>
+      <c r="Q51" s="260"/>
       <c r="R51" s="93">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S51" s="93" t="str">
+      <c r="S51" s="93">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D51+2, MATCH($D$40, Critères!$B$3:$BY$3, 0) + 2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="T51" s="116"/>
       <c r="U51" s="74"/>
-      <c r="W51" s="233" t="str">
-        <f>IFERROR(INDEX(Critères!$B$3:$BE$16, D51+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 3),"")</f>
-        <v/>
+      <c r="W51" s="339" t="str" cm="1">
+        <f t="array" ref="W51">IFERROR(INDEX(Critères!$B$3:$BZ$16, D51+2, MATCH($D$40, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_1</v>
       </c>
     </row>
     <row r="52" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B52" s="73"/>
       <c r="C52" s="115"/>
-      <c r="D52" s="252" t="s">
+      <c r="D52" s="327" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="253"/>
-      <c r="F52" s="253"/>
-      <c r="G52" s="253"/>
-      <c r="H52" s="253"/>
-      <c r="I52" s="253"/>
-      <c r="J52" s="253"/>
-      <c r="K52" s="253"/>
-      <c r="L52" s="253"/>
-      <c r="M52" s="253"/>
-      <c r="N52" s="253"/>
-      <c r="O52" s="254"/>
-      <c r="P52" s="255"/>
-      <c r="Q52" s="255"/>
-      <c r="R52" s="255" t="s">
+      <c r="E52" s="328"/>
+      <c r="F52" s="328"/>
+      <c r="G52" s="328"/>
+      <c r="H52" s="328"/>
+      <c r="I52" s="328"/>
+      <c r="J52" s="328"/>
+      <c r="K52" s="328"/>
+      <c r="L52" s="328"/>
+      <c r="M52" s="328"/>
+      <c r="N52" s="328"/>
+      <c r="O52" s="329"/>
+      <c r="P52" s="330"/>
+      <c r="Q52" s="330"/>
+      <c r="R52" s="330" t="s">
         <v>6</v>
       </c>
-      <c r="S52" s="255"/>
+      <c r="S52" s="330"/>
       <c r="T52" s="116"/>
       <c r="U52" s="74"/>
     </row>
     <row r="53" spans="2:23" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B53" s="73"/>
       <c r="C53" s="115"/>
-      <c r="D53" s="259"/>
-      <c r="E53" s="260"/>
-      <c r="F53" s="260"/>
-      <c r="G53" s="260"/>
-      <c r="H53" s="260"/>
-      <c r="I53" s="260"/>
-      <c r="J53" s="260"/>
-      <c r="K53" s="260"/>
-      <c r="L53" s="260"/>
-      <c r="M53" s="260"/>
-      <c r="N53" s="260"/>
-      <c r="O53" s="261"/>
-      <c r="P53" s="256" t="str">
+      <c r="D53" s="334"/>
+      <c r="E53" s="335"/>
+      <c r="F53" s="335"/>
+      <c r="G53" s="335"/>
+      <c r="H53" s="335"/>
+      <c r="I53" s="335"/>
+      <c r="J53" s="335"/>
+      <c r="K53" s="335"/>
+      <c r="L53" s="335"/>
+      <c r="M53" s="335"/>
+      <c r="N53" s="335"/>
+      <c r="O53" s="336"/>
+      <c r="P53" s="331" t="str">
         <f>IF(R53&gt;80,"Validé",IF(R53&lt;70,"Non Validé", "Réserve"))</f>
         <v>Non Validé</v>
       </c>
-      <c r="Q53" s="256"/>
-      <c r="R53" s="257">
+      <c r="Q53" s="331"/>
+      <c r="R53" s="332">
         <f>IF(SUM(R42:R51)&gt;100,100,SUM(R42:R51))</f>
         <v>0</v>
       </c>
-      <c r="S53" s="258"/>
+      <c r="S53" s="333"/>
       <c r="T53" s="116"/>
       <c r="U53" s="74"/>
     </row>
@@ -7922,136 +7996,136 @@
     </row>
     <row r="57" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B57" s="73"/>
-      <c r="C57" s="243" t="s">
+      <c r="C57" s="246" t="s">
         <v>197</v>
       </c>
-      <c r="D57" s="244"/>
-      <c r="E57" s="244"/>
-      <c r="F57" s="244"/>
-      <c r="G57" s="244"/>
-      <c r="H57" s="244"/>
-      <c r="I57" s="244"/>
-      <c r="J57" s="244"/>
-      <c r="K57" s="244"/>
-      <c r="L57" s="244"/>
-      <c r="M57" s="244"/>
-      <c r="N57" s="244"/>
-      <c r="O57" s="244"/>
-      <c r="P57" s="244"/>
-      <c r="Q57" s="244"/>
-      <c r="R57" s="244"/>
-      <c r="S57" s="244"/>
-      <c r="T57" s="245"/>
+      <c r="D57" s="319"/>
+      <c r="E57" s="319"/>
+      <c r="F57" s="319"/>
+      <c r="G57" s="319"/>
+      <c r="H57" s="319"/>
+      <c r="I57" s="319"/>
+      <c r="J57" s="319"/>
+      <c r="K57" s="319"/>
+      <c r="L57" s="319"/>
+      <c r="M57" s="319"/>
+      <c r="N57" s="319"/>
+      <c r="O57" s="319"/>
+      <c r="P57" s="319"/>
+      <c r="Q57" s="319"/>
+      <c r="R57" s="319"/>
+      <c r="S57" s="319"/>
+      <c r="T57" s="320"/>
       <c r="U57" s="74"/>
     </row>
     <row r="58" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B58" s="73"/>
-      <c r="C58" s="246"/>
-      <c r="D58" s="244"/>
-      <c r="E58" s="244"/>
-      <c r="F58" s="244"/>
-      <c r="G58" s="244"/>
-      <c r="H58" s="244"/>
-      <c r="I58" s="244"/>
-      <c r="J58" s="244"/>
-      <c r="K58" s="244"/>
-      <c r="L58" s="244"/>
-      <c r="M58" s="244"/>
-      <c r="N58" s="244"/>
-      <c r="O58" s="244"/>
-      <c r="P58" s="244"/>
-      <c r="Q58" s="244"/>
-      <c r="R58" s="244"/>
-      <c r="S58" s="244"/>
-      <c r="T58" s="245"/>
+      <c r="C58" s="321"/>
+      <c r="D58" s="319"/>
+      <c r="E58" s="319"/>
+      <c r="F58" s="319"/>
+      <c r="G58" s="319"/>
+      <c r="H58" s="319"/>
+      <c r="I58" s="319"/>
+      <c r="J58" s="319"/>
+      <c r="K58" s="319"/>
+      <c r="L58" s="319"/>
+      <c r="M58" s="319"/>
+      <c r="N58" s="319"/>
+      <c r="O58" s="319"/>
+      <c r="P58" s="319"/>
+      <c r="Q58" s="319"/>
+      <c r="R58" s="319"/>
+      <c r="S58" s="319"/>
+      <c r="T58" s="320"/>
       <c r="U58" s="74"/>
     </row>
     <row r="59" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B59" s="73"/>
-      <c r="C59" s="246"/>
-      <c r="D59" s="244"/>
-      <c r="E59" s="244"/>
-      <c r="F59" s="244"/>
-      <c r="G59" s="244"/>
-      <c r="H59" s="244"/>
-      <c r="I59" s="244"/>
-      <c r="J59" s="244"/>
-      <c r="K59" s="244"/>
-      <c r="L59" s="244"/>
-      <c r="M59" s="244"/>
-      <c r="N59" s="244"/>
-      <c r="O59" s="244"/>
-      <c r="P59" s="244"/>
-      <c r="Q59" s="244"/>
-      <c r="R59" s="244"/>
-      <c r="S59" s="244"/>
-      <c r="T59" s="245"/>
+      <c r="C59" s="321"/>
+      <c r="D59" s="319"/>
+      <c r="E59" s="319"/>
+      <c r="F59" s="319"/>
+      <c r="G59" s="319"/>
+      <c r="H59" s="319"/>
+      <c r="I59" s="319"/>
+      <c r="J59" s="319"/>
+      <c r="K59" s="319"/>
+      <c r="L59" s="319"/>
+      <c r="M59" s="319"/>
+      <c r="N59" s="319"/>
+      <c r="O59" s="319"/>
+      <c r="P59" s="319"/>
+      <c r="Q59" s="319"/>
+      <c r="R59" s="319"/>
+      <c r="S59" s="319"/>
+      <c r="T59" s="320"/>
       <c r="U59" s="74"/>
     </row>
     <row r="60" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B60" s="73"/>
-      <c r="C60" s="246"/>
-      <c r="D60" s="244"/>
-      <c r="E60" s="244"/>
-      <c r="F60" s="244"/>
-      <c r="G60" s="244"/>
-      <c r="H60" s="244"/>
-      <c r="I60" s="244"/>
-      <c r="J60" s="244"/>
-      <c r="K60" s="244"/>
-      <c r="L60" s="244"/>
-      <c r="M60" s="244"/>
-      <c r="N60" s="244"/>
-      <c r="O60" s="244"/>
-      <c r="P60" s="244"/>
-      <c r="Q60" s="244"/>
-      <c r="R60" s="244"/>
-      <c r="S60" s="244"/>
-      <c r="T60" s="245"/>
+      <c r="C60" s="321"/>
+      <c r="D60" s="319"/>
+      <c r="E60" s="319"/>
+      <c r="F60" s="319"/>
+      <c r="G60" s="319"/>
+      <c r="H60" s="319"/>
+      <c r="I60" s="319"/>
+      <c r="J60" s="319"/>
+      <c r="K60" s="319"/>
+      <c r="L60" s="319"/>
+      <c r="M60" s="319"/>
+      <c r="N60" s="319"/>
+      <c r="O60" s="319"/>
+      <c r="P60" s="319"/>
+      <c r="Q60" s="319"/>
+      <c r="R60" s="319"/>
+      <c r="S60" s="319"/>
+      <c r="T60" s="320"/>
       <c r="U60" s="74"/>
     </row>
     <row r="61" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B61" s="73"/>
-      <c r="C61" s="247"/>
-      <c r="D61" s="248"/>
-      <c r="E61" s="248"/>
-      <c r="F61" s="248"/>
-      <c r="G61" s="248"/>
-      <c r="H61" s="248"/>
-      <c r="I61" s="248"/>
-      <c r="J61" s="248"/>
-      <c r="K61" s="248"/>
-      <c r="L61" s="248"/>
-      <c r="M61" s="248"/>
-      <c r="N61" s="248"/>
-      <c r="O61" s="248"/>
-      <c r="P61" s="248"/>
-      <c r="Q61" s="248"/>
-      <c r="R61" s="248"/>
-      <c r="S61" s="248"/>
-      <c r="T61" s="249"/>
+      <c r="C61" s="322"/>
+      <c r="D61" s="323"/>
+      <c r="E61" s="323"/>
+      <c r="F61" s="323"/>
+      <c r="G61" s="323"/>
+      <c r="H61" s="323"/>
+      <c r="I61" s="323"/>
+      <c r="J61" s="323"/>
+      <c r="K61" s="323"/>
+      <c r="L61" s="323"/>
+      <c r="M61" s="323"/>
+      <c r="N61" s="323"/>
+      <c r="O61" s="323"/>
+      <c r="P61" s="323"/>
+      <c r="Q61" s="323"/>
+      <c r="R61" s="323"/>
+      <c r="S61" s="323"/>
+      <c r="T61" s="324"/>
       <c r="U61" s="74"/>
     </row>
     <row r="62" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B62" s="73"/>
-      <c r="C62" s="239"/>
-      <c r="D62" s="239"/>
-      <c r="E62" s="239"/>
-      <c r="F62" s="239"/>
-      <c r="G62" s="239"/>
-      <c r="H62" s="239"/>
-      <c r="I62" s="239"/>
-      <c r="J62" s="239"/>
-      <c r="K62" s="239"/>
-      <c r="L62" s="239"/>
-      <c r="M62" s="239"/>
-      <c r="N62" s="239"/>
-      <c r="O62" s="239"/>
-      <c r="P62" s="239"/>
-      <c r="Q62" s="239"/>
-      <c r="R62" s="239"/>
-      <c r="S62" s="239"/>
-      <c r="T62" s="239"/>
+      <c r="C62" s="238"/>
+      <c r="D62" s="238"/>
+      <c r="E62" s="238"/>
+      <c r="F62" s="238"/>
+      <c r="G62" s="238"/>
+      <c r="H62" s="238"/>
+      <c r="I62" s="238"/>
+      <c r="J62" s="238"/>
+      <c r="K62" s="238"/>
+      <c r="L62" s="238"/>
+      <c r="M62" s="238"/>
+      <c r="N62" s="238"/>
+      <c r="O62" s="238"/>
+      <c r="P62" s="238"/>
+      <c r="Q62" s="238"/>
+      <c r="R62" s="238"/>
+      <c r="S62" s="238"/>
+      <c r="T62" s="238"/>
       <c r="U62" s="74"/>
     </row>
     <row r="63" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -8080,114 +8154,114 @@
     </row>
     <row r="64" spans="2:23" ht="20.7" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B64" s="73"/>
-      <c r="C64" s="325" t="s">
+      <c r="C64" s="243" t="s">
         <v>334</v>
       </c>
-      <c r="D64" s="326"/>
-      <c r="E64" s="326"/>
-      <c r="F64" s="326"/>
-      <c r="G64" s="326"/>
-      <c r="H64" s="326"/>
-      <c r="I64" s="326"/>
-      <c r="J64" s="326"/>
-      <c r="K64" s="326"/>
-      <c r="L64" s="326"/>
-      <c r="M64" s="326"/>
-      <c r="N64" s="326"/>
-      <c r="O64" s="326"/>
-      <c r="P64" s="326"/>
-      <c r="Q64" s="326"/>
-      <c r="R64" s="326"/>
-      <c r="S64" s="326"/>
-      <c r="T64" s="327"/>
+      <c r="D64" s="244"/>
+      <c r="E64" s="244"/>
+      <c r="F64" s="244"/>
+      <c r="G64" s="244"/>
+      <c r="H64" s="244"/>
+      <c r="I64" s="244"/>
+      <c r="J64" s="244"/>
+      <c r="K64" s="244"/>
+      <c r="L64" s="244"/>
+      <c r="M64" s="244"/>
+      <c r="N64" s="244"/>
+      <c r="O64" s="244"/>
+      <c r="P64" s="244"/>
+      <c r="Q64" s="244"/>
+      <c r="R64" s="244"/>
+      <c r="S64" s="244"/>
+      <c r="T64" s="245"/>
       <c r="U64" s="74"/>
     </row>
     <row r="65" spans="2:21" ht="20.7" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B65" s="73"/>
-      <c r="C65" s="243"/>
-      <c r="D65" s="328"/>
-      <c r="E65" s="328"/>
-      <c r="F65" s="328"/>
-      <c r="G65" s="328"/>
-      <c r="H65" s="328"/>
-      <c r="I65" s="328"/>
-      <c r="J65" s="328"/>
-      <c r="K65" s="328"/>
-      <c r="L65" s="328"/>
-      <c r="M65" s="328"/>
-      <c r="N65" s="328"/>
-      <c r="O65" s="328"/>
-      <c r="P65" s="328"/>
-      <c r="Q65" s="328"/>
-      <c r="R65" s="328"/>
-      <c r="S65" s="328"/>
-      <c r="T65" s="329"/>
+      <c r="C65" s="246"/>
+      <c r="D65" s="247"/>
+      <c r="E65" s="247"/>
+      <c r="F65" s="247"/>
+      <c r="G65" s="247"/>
+      <c r="H65" s="247"/>
+      <c r="I65" s="247"/>
+      <c r="J65" s="247"/>
+      <c r="K65" s="247"/>
+      <c r="L65" s="247"/>
+      <c r="M65" s="247"/>
+      <c r="N65" s="247"/>
+      <c r="O65" s="247"/>
+      <c r="P65" s="247"/>
+      <c r="Q65" s="247"/>
+      <c r="R65" s="247"/>
+      <c r="S65" s="247"/>
+      <c r="T65" s="248"/>
       <c r="U65" s="74"/>
     </row>
     <row r="66" spans="2:21" ht="20.7" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B66" s="73"/>
-      <c r="C66" s="243"/>
-      <c r="D66" s="328"/>
-      <c r="E66" s="328"/>
-      <c r="F66" s="328"/>
-      <c r="G66" s="328"/>
-      <c r="H66" s="328"/>
-      <c r="I66" s="328"/>
-      <c r="J66" s="328"/>
-      <c r="K66" s="328"/>
-      <c r="L66" s="328"/>
-      <c r="M66" s="328"/>
-      <c r="N66" s="328"/>
-      <c r="O66" s="328"/>
-      <c r="P66" s="328"/>
-      <c r="Q66" s="328"/>
-      <c r="R66" s="328"/>
-      <c r="S66" s="328"/>
-      <c r="T66" s="329"/>
+      <c r="C66" s="246"/>
+      <c r="D66" s="247"/>
+      <c r="E66" s="247"/>
+      <c r="F66" s="247"/>
+      <c r="G66" s="247"/>
+      <c r="H66" s="247"/>
+      <c r="I66" s="247"/>
+      <c r="J66" s="247"/>
+      <c r="K66" s="247"/>
+      <c r="L66" s="247"/>
+      <c r="M66" s="247"/>
+      <c r="N66" s="247"/>
+      <c r="O66" s="247"/>
+      <c r="P66" s="247"/>
+      <c r="Q66" s="247"/>
+      <c r="R66" s="247"/>
+      <c r="S66" s="247"/>
+      <c r="T66" s="248"/>
       <c r="U66" s="74"/>
     </row>
     <row r="67" spans="2:21" ht="20.7" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B67" s="73"/>
-      <c r="C67" s="243"/>
-      <c r="D67" s="328"/>
-      <c r="E67" s="328"/>
-      <c r="F67" s="328"/>
-      <c r="G67" s="328"/>
-      <c r="H67" s="328"/>
-      <c r="I67" s="328"/>
-      <c r="J67" s="328"/>
-      <c r="K67" s="328"/>
-      <c r="L67" s="328"/>
-      <c r="M67" s="328"/>
-      <c r="N67" s="328"/>
-      <c r="O67" s="328"/>
-      <c r="P67" s="328"/>
-      <c r="Q67" s="328"/>
-      <c r="R67" s="328"/>
-      <c r="S67" s="328"/>
-      <c r="T67" s="329"/>
+      <c r="C67" s="246"/>
+      <c r="D67" s="247"/>
+      <c r="E67" s="247"/>
+      <c r="F67" s="247"/>
+      <c r="G67" s="247"/>
+      <c r="H67" s="247"/>
+      <c r="I67" s="247"/>
+      <c r="J67" s="247"/>
+      <c r="K67" s="247"/>
+      <c r="L67" s="247"/>
+      <c r="M67" s="247"/>
+      <c r="N67" s="247"/>
+      <c r="O67" s="247"/>
+      <c r="P67" s="247"/>
+      <c r="Q67" s="247"/>
+      <c r="R67" s="247"/>
+      <c r="S67" s="247"/>
+      <c r="T67" s="248"/>
       <c r="U67" s="74"/>
     </row>
     <row r="68" spans="2:21" ht="215.35" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B68" s="73"/>
-      <c r="C68" s="330"/>
-      <c r="D68" s="331"/>
-      <c r="E68" s="331"/>
-      <c r="F68" s="331"/>
-      <c r="G68" s="331"/>
-      <c r="H68" s="331"/>
-      <c r="I68" s="331"/>
-      <c r="J68" s="331"/>
-      <c r="K68" s="331"/>
-      <c r="L68" s="331"/>
-      <c r="M68" s="331"/>
-      <c r="N68" s="331"/>
-      <c r="O68" s="331"/>
-      <c r="P68" s="331"/>
-      <c r="Q68" s="331"/>
-      <c r="R68" s="331"/>
-      <c r="S68" s="331"/>
-      <c r="T68" s="332"/>
+      <c r="C68" s="249"/>
+      <c r="D68" s="250"/>
+      <c r="E68" s="250"/>
+      <c r="F68" s="250"/>
+      <c r="G68" s="250"/>
+      <c r="H68" s="250"/>
+      <c r="I68" s="250"/>
+      <c r="J68" s="250"/>
+      <c r="K68" s="250"/>
+      <c r="L68" s="250"/>
+      <c r="M68" s="250"/>
+      <c r="N68" s="250"/>
+      <c r="O68" s="250"/>
+      <c r="P68" s="250"/>
+      <c r="Q68" s="250"/>
+      <c r="R68" s="250"/>
+      <c r="S68" s="250"/>
+      <c r="T68" s="251"/>
       <c r="U68" s="74"/>
     </row>
     <row r="69" spans="2:21" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -8213,8 +8287,104 @@
       <c r="U69" s="77"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="BFMlTZdjdRcw1MHvEUz3nX2YeJDoaAwxfKE+1nLLKbwNHTCHM7uoPBQv5Hjb6nQwM4RJVxlwZiGusBH4LLKoPA==" saltValue="WMe/U4e+mnNAjUR5UMzGow==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="potBASrZz3r6UTRPViDSSp+HYcOliOhQOqXmdntJBonGy+Kdc6ogNrQ3Stn6b40/w0u5LmzMDtOMk3XDeATr+A==" saltValue="BPv0hUGX27uvEVKPU2HJHw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="120">
+    <mergeCell ref="C56:T56"/>
+    <mergeCell ref="C57:T61"/>
+    <mergeCell ref="D40:S40"/>
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="D52:O52"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="D53:O53"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="E51:J51"/>
+    <mergeCell ref="E42:J42"/>
+    <mergeCell ref="E43:J43"/>
+    <mergeCell ref="E44:J44"/>
+    <mergeCell ref="E45:J45"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="P15:S15"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="J4:N4"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="J6:N6"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="L15:O15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="C2:T2"/>
+    <mergeCell ref="N25:Q25"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:S19"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="R5:T5"/>
+    <mergeCell ref="R6:T6"/>
+    <mergeCell ref="C8:T8"/>
+    <mergeCell ref="D10:S10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="K46:O46"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E46:J46"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="P12:S12"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="K51:O51"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="E47:J47"/>
+    <mergeCell ref="E48:J48"/>
+    <mergeCell ref="E49:J49"/>
+    <mergeCell ref="E50:J50"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="K49:O49"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="C38:T38"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="G16:K16"/>
+    <mergeCell ref="D16:F16"/>
     <mergeCell ref="C63:T63"/>
     <mergeCell ref="C64:T68"/>
     <mergeCell ref="O3:Q3"/>
@@ -8239,102 +8409,6 @@
     <mergeCell ref="K43:O43"/>
     <mergeCell ref="K44:O44"/>
     <mergeCell ref="K45:O45"/>
-    <mergeCell ref="K46:O46"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E46:J46"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="P12:S12"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="K51:O51"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="E47:J47"/>
-    <mergeCell ref="E48:J48"/>
-    <mergeCell ref="E49:J49"/>
-    <mergeCell ref="E50:J50"/>
-    <mergeCell ref="K47:O47"/>
-    <mergeCell ref="K48:O48"/>
-    <mergeCell ref="K49:O49"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="C38:T38"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="G16:K16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C2:T2"/>
-    <mergeCell ref="N25:Q25"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="P20:S20"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="P22:S22"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G20:K20"/>
-    <mergeCell ref="G21:K21"/>
-    <mergeCell ref="G22:K22"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:S19"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="R5:T5"/>
-    <mergeCell ref="R6:T6"/>
-    <mergeCell ref="C8:T8"/>
-    <mergeCell ref="D10:S10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="P15:S15"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="J4:N4"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="J6:N6"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="L15:O15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="C56:T56"/>
-    <mergeCell ref="C57:T61"/>
-    <mergeCell ref="D40:S40"/>
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="K41:O41"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="D52:O52"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="D53:O53"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="K42:O42"/>
-    <mergeCell ref="E51:J51"/>
-    <mergeCell ref="E42:J42"/>
-    <mergeCell ref="E43:J43"/>
-    <mergeCell ref="E44:J44"/>
-    <mergeCell ref="E45:J45"/>
   </mergeCells>
   <conditionalFormatting sqref="I27:I30">
     <cfRule type="expression" dxfId="24" priority="20" stopIfTrue="1">
@@ -19715,8 +19789,8 @@
       <c r="WE27" s="19"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="GegGxFSobJaNpcNThmR3jcEMn1avPH0/lu92LgpFbG/V3ihCpq7eDMHn6OV9KYYVWuVhMLa1nkoV5MraiGtDSA==" saltValue="Xo/z0it/3ENw8HLmwcKpBg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OSiZ8Q/igpNCsvsH4QtYL06TxWE2ZMDFi5PNwJ507cWBmAR6KApETuFmJKO1hB5q+cXc5oAyj74+aRsJLicNQQ==" saltValue="MdHCq8VkJ4OotgE12V7Vww==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -20061,7 +20135,7 @@
       <c r="G20" s="58" t="s">
         <v>267</v>
       </c>
-      <c r="H20" s="339" t="s">
+      <c r="H20" s="239" t="s">
         <v>335</v>
       </c>
       <c r="I20" s="172" t="s">
@@ -20517,14 +20591,14 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="MvDF01oprvy2o3aqHpFq4NzRrZOEl4Q7ILsJRnpQT6F6zuJ3G0lJdbWy1F3BUsCTUCdiwPgN2KNoK7JwZ7yJ7g==" saltValue="nGK/2OIXEm3K5JNx6wsJOg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="NEuyIUL+s07ppGt4rXindvpyB+zjOt9Hpj+D7qmCUxoHkQ1Fz+PYesLlh1D79bYp0Xnf5G2SHjKdbsfogoOOTg==" saltValue="K9Xb8Ao+Ij/35KJBhPJTew==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H21:H27">
     <sortCondition ref="H21:H27"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="I3:J3"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A21:A23">
     <cfRule type="expression" priority="13">
       <formula>IF($B$3="Industrie",1,0)</formula>
@@ -20537,6 +20611,11 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:G5 E6:G12">
     <cfRule type="expression" priority="87">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21:H22">
+    <cfRule type="expression" priority="1">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20560,29 +20639,24 @@
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21:H22">
-    <cfRule type="expression" priority="1">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20789,14 +20863,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -20809,6 +20875,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="afd5fb63-b61f-423b-93e7-958e038eacd2"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
